--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570"/>
+    <workbookView windowWidth="18165" windowHeight="12390" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Section1" sheetId="1" r:id="rId1"/>
+    <sheet name="Section01" sheetId="1" r:id="rId1"/>
+    <sheet name="Section02" sheetId="2" r:id="rId2"/>
+    <sheet name="Section03" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="415">
   <si>
     <t>单词/词组</t>
   </si>
@@ -43,7 +45,7 @@
     <t>ad hoc</t>
   </si>
   <si>
-    <t>a.特别的、专设的</t>
+    <t>a.特别的，专设的</t>
   </si>
   <si>
     <t>an ad hoc organization</t>
@@ -52,7 +54,8 @@
     <t>antiquarian</t>
   </si>
   <si>
-    <t>n.古文物研究者 a.古文物的</t>
+    <t>n.古文物研究者 
+a.古文物的</t>
   </si>
   <si>
     <t>anticipate v.预期</t>
@@ -89,7 +92,8 @@
     <t>bias</t>
   </si>
   <si>
-    <t>n.偏见 vt.使某人产生偏见</t>
+    <t>n.偏见 
+vt.使某人产生偏见</t>
   </si>
   <si>
     <t>bias in favor of / against sth</t>
@@ -216,7 +220,9 @@
     <t>counterfeit</t>
   </si>
   <si>
-    <t>a.伪造的 n.伪造品 vt.伪造</t>
+    <t>a.伪造的 
+n.伪造品 
+vt.伪造</t>
   </si>
   <si>
     <t>counterfeit currency 假币</t>
@@ -344,6 +350,992 @@
   </si>
   <si>
     <t>fickleness</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>n.体系，框架</t>
+  </si>
+  <si>
+    <t>legal framework 法律体系</t>
+  </si>
+  <si>
+    <t>framer 制定框架的人（国父）</t>
+  </si>
+  <si>
+    <t>gainsay</t>
+  </si>
+  <si>
+    <t>vt.否认</t>
+  </si>
+  <si>
+    <t>gainsay the fact that + 同位语</t>
+  </si>
+  <si>
+    <t>gain = against</t>
+  </si>
+  <si>
+    <t>haunted</t>
+  </si>
+  <si>
+    <t>a.闹鬼的，焦虑的</t>
+  </si>
+  <si>
+    <t>the problem haunts me</t>
+  </si>
+  <si>
+    <t>haunt vt.闹鬼，纠缠 n.常去的地方
+haunting a.令人难忘的</t>
+  </si>
+  <si>
+    <t>haunt v.萦绕于脑际，使难以忘却
+daunt v.使胆怯；使气馁
+gaunt a.瘦削憔悴的</t>
+  </si>
+  <si>
+    <t>hyperbole</t>
+  </si>
+  <si>
+    <t>n.夸张</t>
+  </si>
+  <si>
+    <t>hyper = beyond</t>
+  </si>
+  <si>
+    <t>overstatement
+exaggeration</t>
+  </si>
+  <si>
+    <t>idealistic</t>
+  </si>
+  <si>
+    <t>a.理想主义的（不切实际）</t>
+  </si>
+  <si>
+    <t>ideal
+idealism</t>
+  </si>
+  <si>
+    <t>practical</t>
+  </si>
+  <si>
+    <t>imminent</t>
+  </si>
+  <si>
+    <t>a.迫近的</t>
+  </si>
+  <si>
+    <t>imminent danger/disaster</t>
+  </si>
+  <si>
+    <t>im = into</t>
+  </si>
+  <si>
+    <t>eminent a.杰出的，非凡的</t>
+  </si>
+  <si>
+    <t>impending</t>
+  </si>
+  <si>
+    <t>a.即将发生的</t>
+  </si>
+  <si>
+    <t>pend = 悬挂</t>
+  </si>
+  <si>
+    <t>indifferent</t>
+  </si>
+  <si>
+    <t>a.冷漠的，平庸的</t>
+  </si>
+  <si>
+    <t>be indifferent to sth
+indifferent movie</t>
+  </si>
+  <si>
+    <t>insular</t>
+  </si>
+  <si>
+    <t>a.与世隔绝的，保守的</t>
+  </si>
+  <si>
+    <t>insular family</t>
+  </si>
+  <si>
+    <t>island</t>
+  </si>
+  <si>
+    <t>insulate v.使孤立，使绝缘</t>
+  </si>
+  <si>
+    <t>isolated</t>
+  </si>
+  <si>
+    <t>peninsular a.半岛的</t>
+  </si>
+  <si>
+    <t>intensify</t>
+  </si>
+  <si>
+    <t>v.加强，加剧</t>
+  </si>
+  <si>
+    <t>intensity n.强度
+intense a. 强烈的</t>
+  </si>
+  <si>
+    <t>intransigent</t>
+  </si>
+  <si>
+    <t>a.顽固的</t>
+  </si>
+  <si>
+    <t>intransigent refusal</t>
+  </si>
+  <si>
+    <t>in = no
+trans = transport = 通过</t>
+  </si>
+  <si>
+    <t>invidious</t>
+  </si>
+  <si>
+    <t>a.令人讨厌的</t>
+  </si>
+  <si>
+    <t>invidious job/comparision不公平比较</t>
+  </si>
+  <si>
+    <t>annoying</t>
+  </si>
+  <si>
+    <t>insidious a.阴险的</t>
+  </si>
+  <si>
+    <t>legitimate</t>
+  </si>
+  <si>
+    <t>a.合法的，合理的</t>
+  </si>
+  <si>
+    <t>legitimate government</t>
+  </si>
+  <si>
+    <t>legal</t>
+  </si>
+  <si>
+    <t>legitimacy n.合法性
+legitimize vt.合法化</t>
+  </si>
+  <si>
+    <t>mercenary</t>
+  </si>
+  <si>
+    <t>n.雇佣兵 
+a.唯利是图的</t>
+  </si>
+  <si>
+    <t>merchant</t>
+  </si>
+  <si>
+    <t>greedy</t>
+  </si>
+  <si>
+    <t>numinous</t>
+  </si>
+  <si>
+    <t>a.精神上的，神圣的，神秘的</t>
+  </si>
+  <si>
+    <t>a numinous power</t>
+  </si>
+  <si>
+    <t>num = nod = 头</t>
+  </si>
+  <si>
+    <t>holy
+supernatural</t>
+  </si>
+  <si>
+    <t>overstatement</t>
+  </si>
+  <si>
+    <t>n.夸大</t>
+  </si>
+  <si>
+    <t>overstate</t>
+  </si>
+  <si>
+    <t>exaggeration
+hyperbole</t>
+  </si>
+  <si>
+    <t>understatement
+n.轻描淡写的</t>
+  </si>
+  <si>
+    <t>paradox</t>
+  </si>
+  <si>
+    <t>n.矛盾，悖论</t>
+  </si>
+  <si>
+    <t>paradoxical</t>
+  </si>
+  <si>
+    <t>dilemma
+contradiction
+conflict
+competing</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>a.部分的，偏心的</t>
+  </si>
+  <si>
+    <t>be parcial to sth/sb</t>
+  </si>
+  <si>
+    <t>part</t>
+  </si>
+  <si>
+    <t>partiality</t>
+  </si>
+  <si>
+    <t>biased</t>
+  </si>
+  <si>
+    <t>prescient</t>
+  </si>
+  <si>
+    <t>a.预知的，有先见之明的</t>
+  </si>
+  <si>
+    <t>pre = 前面
+scie = science = 知道</t>
+  </si>
+  <si>
+    <t>foresighted</t>
+  </si>
+  <si>
+    <t>presumption</t>
+  </si>
+  <si>
+    <t>n.假定，傲慢，自大</t>
+  </si>
+  <si>
+    <t>pre = 前
+sum = assume</t>
+  </si>
+  <si>
+    <t>presume to do sth
+presumptuous a.擅自做主的</t>
+  </si>
+  <si>
+    <t>prophetic</t>
+  </si>
+  <si>
+    <t>a.有预见性的</t>
+  </si>
+  <si>
+    <t>pro = pre = 前
+phet = fate</t>
+  </si>
+  <si>
+    <t>prophet</t>
+  </si>
+  <si>
+    <t>recoil</t>
+  </si>
+  <si>
+    <t>vi.退缩，拒绝</t>
+  </si>
+  <si>
+    <t>recoil from doing sth</t>
+  </si>
+  <si>
+    <t>coil = 底部</t>
+  </si>
+  <si>
+    <t>reconcile v.和解</t>
+  </si>
+  <si>
+    <t>shrink</t>
+  </si>
+  <si>
+    <t>vi.缩水，缩小，避开</t>
+  </si>
+  <si>
+    <t>shrink from sth
+shrink away from sb</t>
+  </si>
+  <si>
+    <t>sonorous</t>
+  </si>
+  <si>
+    <t>a.洪亮的</t>
+  </si>
+  <si>
+    <t>sound</t>
+  </si>
+  <si>
+    <t>spontaneous</t>
+  </si>
+  <si>
+    <t>a.自发的，自然的</t>
+  </si>
+  <si>
+    <t>spontaneous act</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>sporadic a.零星的</t>
+  </si>
+  <si>
+    <t>sterling</t>
+  </si>
+  <si>
+    <t>a.优秀的 
+n.英镑</t>
+  </si>
+  <si>
+    <t>star</t>
+  </si>
+  <si>
+    <t>shilling n.先令 &gt; 便士</t>
+  </si>
+  <si>
+    <t>stern</t>
+  </si>
+  <si>
+    <t>a.严厉的</t>
+  </si>
+  <si>
+    <t>stern warning</t>
+  </si>
+  <si>
+    <t>strict
+rigid
+severe</t>
+  </si>
+  <si>
+    <t>succumb</t>
+  </si>
+  <si>
+    <t>vi.屈服</t>
+  </si>
+  <si>
+    <t>succumb to pressure/temptation</t>
+  </si>
+  <si>
+    <t>suc = sub</t>
+  </si>
+  <si>
+    <t>tedious</t>
+  </si>
+  <si>
+    <t>a.乏味的</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>tedium n.枯燥乏味</t>
+  </si>
+  <si>
+    <t>unambiguous</t>
+  </si>
+  <si>
+    <t>a.清晰的</t>
+  </si>
+  <si>
+    <t>ambiguous a.模糊的
+obscure</t>
+  </si>
+  <si>
+    <t>ambivalent a.矛盾的</t>
+  </si>
+  <si>
+    <t>upheaval</t>
+  </si>
+  <si>
+    <t>n.剧变，动乱</t>
+  </si>
+  <si>
+    <t>a political upheaval</t>
+  </si>
+  <si>
+    <t>uproar n.哗然</t>
+  </si>
+  <si>
+    <t>vague</t>
+  </si>
+  <si>
+    <t>a.模糊的</t>
+  </si>
+  <si>
+    <t>vagueness</t>
+  </si>
+  <si>
+    <t>obscure
+ambiguous</t>
+  </si>
+  <si>
+    <t>vogue n.时尚，风尚</t>
+  </si>
+  <si>
+    <t>verse</t>
+  </si>
+  <si>
+    <t>n.韵文，诗歌</t>
+  </si>
+  <si>
+    <t>versed = expert = practised = 精通的
+be versed at</t>
+  </si>
+  <si>
+    <t>prose n.无韵文，散文</t>
+  </si>
+  <si>
+    <t>yield</t>
+  </si>
+  <si>
+    <t>v.屈服，产生 
+n.产量</t>
+  </si>
+  <si>
+    <t>yield to
+yield control</t>
+  </si>
+  <si>
+    <t>yielding a.顺从的
+unyielding a.固执的 = intransigent</t>
+  </si>
+  <si>
+    <t>altruism</t>
+  </si>
+  <si>
+    <t>n.利他主义</t>
+  </si>
+  <si>
+    <t>altru = alter = 他人</t>
+  </si>
+  <si>
+    <t>altruistic</t>
+  </si>
+  <si>
+    <t>egotism n.利己主义
+autism a.自我中心主义</t>
+  </si>
+  <si>
+    <t>ameliorate</t>
+  </si>
+  <si>
+    <t>vt.改善</t>
+  </si>
+  <si>
+    <t>ameliorate a situation</t>
+  </si>
+  <si>
+    <t>mel = multi</t>
+  </si>
+  <si>
+    <t>improve
+enhance</t>
+  </si>
+  <si>
+    <t>augment</t>
+  </si>
+  <si>
+    <t>v.增强，增大</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>argument</t>
+  </si>
+  <si>
+    <t>beneficence</t>
+  </si>
+  <si>
+    <t>n.善行</t>
+  </si>
+  <si>
+    <t>benefit beneficial
+benevolent</t>
+  </si>
+  <si>
+    <t>brook</t>
+  </si>
+  <si>
+    <t>n.小溪
+vt.容许，允许</t>
+  </si>
+  <si>
+    <t>brook no opposition</t>
+  </si>
+  <si>
+    <t>tolerate
+accept</t>
+  </si>
+  <si>
+    <t>compromise</t>
+  </si>
+  <si>
+    <t>v.妥协，损害
+n.妥协</t>
+  </si>
+  <si>
+    <t>comprise the immune system</t>
+  </si>
+  <si>
+    <t>compromising = unyielding</t>
+  </si>
+  <si>
+    <t>comprise 组成，构成</t>
+  </si>
+  <si>
+    <t>considerable</t>
+  </si>
+  <si>
+    <t>a.大量的，可观的</t>
+  </si>
+  <si>
+    <t>consider
+considered a.深思熟虑的
+considerate a.体谅他人的</t>
+  </si>
+  <si>
+    <t>convivial</t>
+  </si>
+  <si>
+    <t>a.欢乐的，友好的</t>
+  </si>
+  <si>
+    <t>convivial atmosphere</t>
+  </si>
+  <si>
+    <t>conviviality</t>
+  </si>
+  <si>
+    <t>cordial</t>
+  </si>
+  <si>
+    <t>a.热情的，友好的</t>
+  </si>
+  <si>
+    <t>cordial atmosphere</t>
+  </si>
+  <si>
+    <t>cord = 心</t>
+  </si>
+  <si>
+    <t>cordiality</t>
+  </si>
+  <si>
+    <t>didactic</t>
+  </si>
+  <si>
+    <t>a.好说教的</t>
+  </si>
+  <si>
+    <t>diffident</t>
+  </si>
+  <si>
+    <t>a.羞怯的</t>
+  </si>
+  <si>
+    <t>diffidence</t>
+  </si>
+  <si>
+    <t>confident</t>
+  </si>
+  <si>
+    <t>indifferent 冷漠的</t>
+  </si>
+  <si>
+    <t>disclose</t>
+  </si>
+  <si>
+    <t>vt.透露</t>
+  </si>
+  <si>
+    <t>disclose details of</t>
+  </si>
+  <si>
+    <t>uncover
+reveal</t>
+  </si>
+  <si>
+    <t>dispute</t>
+  </si>
+  <si>
+    <t>vt.反驳
+n.争论</t>
+  </si>
+  <si>
+    <t>be in dispute</t>
+  </si>
+  <si>
+    <t>disputable a.可争论的
+disputative a.好争论的</t>
+  </si>
+  <si>
+    <t>exasperate</t>
+  </si>
+  <si>
+    <t>vt.恶化，触怒</t>
+  </si>
+  <si>
+    <t>exasperation</t>
+  </si>
+  <si>
+    <t>fecund</t>
+  </si>
+  <si>
+    <t>a.肥沃的，多产的</t>
+  </si>
+  <si>
+    <t>fecund land</t>
+  </si>
+  <si>
+    <t>fecundity</t>
+  </si>
+  <si>
+    <t>feeble</t>
+  </si>
+  <si>
+    <t>a.虚弱的，不可信的</t>
+  </si>
+  <si>
+    <t>feeble man/argument</t>
+  </si>
+  <si>
+    <t>fertile</t>
+  </si>
+  <si>
+    <t>a.肥沃的，能生育的</t>
+  </si>
+  <si>
+    <t>fertility</t>
+  </si>
+  <si>
+    <t>honorific</t>
+  </si>
+  <si>
+    <t>a.尊敬的
+n.尊称</t>
+  </si>
+  <si>
+    <t>the honorific title</t>
+  </si>
+  <si>
+    <t>honor</t>
+  </si>
+  <si>
+    <t>immutable</t>
+  </si>
+  <si>
+    <t>a.永恒的，不变的</t>
+  </si>
+  <si>
+    <t>mute</t>
+  </si>
+  <si>
+    <t>mutable</t>
+  </si>
+  <si>
+    <t>impede</t>
+  </si>
+  <si>
+    <t>vt.阻碍 ≠ prevent</t>
+  </si>
+  <si>
+    <t>impede growth/progress</t>
+  </si>
+  <si>
+    <t>impeded a.阻挠的
+impediment n.障碍物</t>
+  </si>
+  <si>
+    <t>impenetrable</t>
+  </si>
+  <si>
+    <t>a.难以穿越的，不能理解的</t>
+  </si>
+  <si>
+    <t>penetrate
+penetrable</t>
+  </si>
+  <si>
+    <t>inaccessible</t>
+  </si>
+  <si>
+    <t>instrumental</t>
+  </si>
+  <si>
+    <t>a.有用的</t>
+  </si>
+  <si>
+    <t>be instrumental in sth</t>
+  </si>
+  <si>
+    <t>instrument n.器具</t>
+  </si>
+  <si>
+    <t>irascible</t>
+  </si>
+  <si>
+    <t>a.易怒的</t>
+  </si>
+  <si>
+    <t>ira = ire = 愤怒</t>
+  </si>
+  <si>
+    <t>irascibility</t>
+  </si>
+  <si>
+    <t>lavish</t>
+  </si>
+  <si>
+    <t>a.浪费的，慷慨的
+vt.为...花很多钱/大加赞赏</t>
+  </si>
+  <si>
+    <t>lavish praise on one's work</t>
+  </si>
+  <si>
+    <t>lav = lava = 岩浆</t>
+  </si>
+  <si>
+    <t>wasteful</t>
+  </si>
+  <si>
+    <t>lopsided</t>
+  </si>
+  <si>
+    <t>a.不平衡的</t>
+  </si>
+  <si>
+    <t>imbalanced</t>
+  </si>
+  <si>
+    <t>malign</t>
+  </si>
+  <si>
+    <t>a.有害的
+vt.重伤</t>
+  </si>
+  <si>
+    <t>malign opponents</t>
+  </si>
+  <si>
+    <t>mal = 不好</t>
+  </si>
+  <si>
+    <t>malignant a.恶性的</t>
+  </si>
+  <si>
+    <t>malnutrition</t>
+  </si>
+  <si>
+    <t>overlook</t>
+  </si>
+  <si>
+    <t>vt.忽视
+n.忽视</t>
+  </si>
+  <si>
+    <t>oversight 疏忽，照管
+overview 概述
+outlook 观点</t>
+  </si>
+  <si>
+    <t>plastic</t>
+  </si>
+  <si>
+    <t>n.塑料
+a.可塑的，不自然的</t>
+  </si>
+  <si>
+    <t>plasticity n.可塑性</t>
+  </si>
+  <si>
+    <t>mannered a.不自然的</t>
+  </si>
+  <si>
+    <t>proprietary</t>
+  </si>
+  <si>
+    <t>a.专营的，专有的</t>
+  </si>
+  <si>
+    <t>proprietary brand</t>
+  </si>
+  <si>
+    <t>property</t>
+  </si>
+  <si>
+    <t>repertoire</t>
+  </si>
+  <si>
+    <t>n.指令系统，全部曲目</t>
+  </si>
+  <si>
+    <t>repudiate</t>
+  </si>
+  <si>
+    <t>vt.拒绝，否认</t>
+  </si>
+  <si>
+    <t>robust</t>
+  </si>
+  <si>
+    <t>a.强有力的，健壮的</t>
+  </si>
+  <si>
+    <t>robust recovery/defence</t>
+  </si>
+  <si>
+    <t>routine</t>
+  </si>
+  <si>
+    <t>n.惯例
+a.惯例的，平淡乏味的</t>
+  </si>
+  <si>
+    <t>sanguine</t>
+  </si>
+  <si>
+    <t>a.乐观的，自信的</t>
+  </si>
+  <si>
+    <t>be sanguine about</t>
+  </si>
+  <si>
+    <t>san = 血</t>
+  </si>
+  <si>
+    <t>optimistic</t>
+  </si>
+  <si>
+    <t>self-perpetuating</t>
+  </si>
+  <si>
+    <t>a.自存自续的（贬义）</t>
+  </si>
+  <si>
+    <t>perpetuate v.使持久化
+perpetual a.</t>
+  </si>
+  <si>
+    <t>straightforward</t>
+  </si>
+  <si>
+    <t>a.坦率的，易懂的</t>
+  </si>
+  <si>
+    <t>transparent
+forthright</t>
+  </si>
+  <si>
+    <t>turbulent</t>
+  </si>
+  <si>
+    <t>a.动荡的，湍急的</t>
+  </si>
+  <si>
+    <t>disturb</t>
+  </si>
+  <si>
+    <t>turbulence</t>
+  </si>
+  <si>
+    <t>verisimilitude</t>
+  </si>
+  <si>
+    <t>n.逼真</t>
+  </si>
+  <si>
+    <t>veri= very</t>
+  </si>
+  <si>
+    <t>ambivalent</t>
+  </si>
+  <si>
+    <t>a. 矛盾的，暧昧的</t>
+  </si>
+  <si>
+    <t>be ambivalent about sth</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>ambiguous a.模糊的</t>
+  </si>
+  <si>
+    <t>boast</t>
+  </si>
+  <si>
+    <t>v. 吹嘘
+n.吹嘘</t>
+  </si>
+  <si>
+    <t>boast about</t>
+  </si>
+  <si>
+    <t>censure</t>
+  </si>
+  <si>
+    <t>v.谴责
+n.谴责</t>
+  </si>
+  <si>
+    <t>attract international censure</t>
+  </si>
+  <si>
+    <t>censor n.审查员</t>
+  </si>
+  <si>
+    <t>compliment</t>
+  </si>
+  <si>
+    <t>vt.恭维
+n.恭维</t>
+  </si>
+  <si>
+    <t>complimentary a.赠送的</t>
+  </si>
+  <si>
+    <t>complement n.补足</t>
+  </si>
+  <si>
+    <t>condone</t>
+  </si>
+  <si>
+    <t>vt.纵容，宽恕</t>
+  </si>
+  <si>
+    <t>don = donate</t>
+  </si>
+  <si>
+    <t>condole</t>
+  </si>
+  <si>
+    <t>vi.慰问，吊唁</t>
+  </si>
+  <si>
+    <t>condole with sb</t>
+  </si>
+  <si>
+    <t>dole = 失业金</t>
   </si>
 </sst>
 </file>
@@ -351,10 +1343,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -380,10 +1372,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,7 +1427,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -411,7 +1481,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -426,91 +1503,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -531,31 +1523,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,13 +1565,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -591,7 +1685,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,115 +1703,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,11 +1717,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,8 +1735,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -758,26 +1765,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -793,17 +1780,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,142 +1819,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -972,11 +1964,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -984,6 +1982,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1307,384 +2314,1606 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.275" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.9666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6416666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.0916666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="31.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.4916666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.9833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.6916666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.9666666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="31.4083333333333" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="31.5" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="31.5" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="31.5" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="31.5" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" ht="47.25" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" ht="31.5" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" ht="31.5" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" ht="31.5" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" ht="31.5" spans="1:6">
+      <c r="A23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" ht="47.25" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" ht="31.5" spans="1:6">
+      <c r="A28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" ht="31.5" spans="1:7">
+      <c r="A29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" ht="31.5" spans="1:6">
+      <c r="A32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" ht="31.5" spans="1:5">
+      <c r="A34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" ht="31.5" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" ht="31.5" spans="1:5">
+      <c r="A37" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" ht="31.5" spans="1:6">
+      <c r="A38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" ht="31.5" spans="1:6">
+      <c r="A39" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" ht="31.5" spans="1:7">
+      <c r="A40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" ht="63" spans="1:6">
+      <c r="A41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" ht="31.5" spans="1:6">
+      <c r="A43" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" ht="31.5" spans="1:5">
+      <c r="A44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" ht="31.5" spans="1:6">
+      <c r="A45" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" ht="31.5" spans="1:6">
+      <c r="A47" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" ht="31.5" spans="1:8">
+      <c r="A50" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" ht="47.25" spans="1:6">
+      <c r="A51" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" ht="31.5" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56" ht="31.5" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" ht="31.5" spans="1:7">
+      <c r="A57" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" ht="31.5" spans="1:6">
+      <c r="A58" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="3" max="3" width="24.7833333333333" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
+    <col min="7" max="7" width="21.3" customWidth="1"/>
+    <col min="8" max="8" width="18.1416666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:7">
+      <c r="A2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:5">
+      <c r="A5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:6">
+      <c r="A6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:8">
+      <c r="A7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" ht="45" spans="1:5">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E12" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" t="s">
+        <v>293</v>
+      </c>
+      <c r="H12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:6">
+      <c r="A13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:5">
+      <c r="A14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" t="s">
+        <v>314</v>
+      </c>
+      <c r="E18" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:4">
+      <c r="A19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" t="s">
+        <v>321</v>
+      </c>
+      <c r="E20" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:6">
+      <c r="A22" t="s">
+        <v>328</v>
+      </c>
+      <c r="B22" t="s">
+        <v>329</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B23" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" t="s">
+        <v>334</v>
+      </c>
+      <c r="E23" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B24" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" t="s">
+        <v>339</v>
+      </c>
+      <c r="F24" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" ht="30" spans="1:6">
+      <c r="A25" t="s">
+        <v>340</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" t="s">
+        <v>343</v>
+      </c>
+      <c r="F25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B26" t="s">
+        <v>346</v>
+      </c>
+      <c r="F26" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:8">
+      <c r="A27" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C27" t="s">
+        <v>350</v>
+      </c>
+      <c r="D27" t="s">
+        <v>351</v>
+      </c>
+      <c r="E27" t="s">
+        <v>352</v>
+      </c>
+      <c r="H27" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" ht="45" spans="1:8">
+      <c r="A28" t="s">
+        <v>354</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:6">
+      <c r="A29" t="s">
+        <v>357</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E29" t="s">
+        <v>359</v>
+      </c>
+      <c r="F29" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C30" t="s">
+        <v>363</v>
+      </c>
+      <c r="E30" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>365</v>
+      </c>
+      <c r="B31" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B32" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>369</v>
+      </c>
+      <c r="B33" t="s">
+        <v>370</v>
+      </c>
+      <c r="C33" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:2">
+      <c r="A34" t="s">
+        <v>372</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B35" t="s">
+        <v>375</v>
+      </c>
+      <c r="C35" t="s">
+        <v>376</v>
+      </c>
+      <c r="D35" t="s">
+        <v>377</v>
+      </c>
+      <c r="F35" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36" ht="30" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" t="s">
+        <v>380</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:6">
+      <c r="A37" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" t="s">
+        <v>383</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>385</v>
+      </c>
+      <c r="B38" t="s">
+        <v>386</v>
+      </c>
+      <c r="D38" t="s">
+        <v>387</v>
+      </c>
+      <c r="E38" t="s">
+        <v>388</v>
+      </c>
+      <c r="F38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>389</v>
+      </c>
+      <c r="B39" t="s">
+        <v>390</v>
+      </c>
+      <c r="D39" t="s">
+        <v>391</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="6" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.9166666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.475" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.35" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.8416666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>394</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>397</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" spans="1:8">
+      <c r="A4" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>404</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>408</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>409</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="31.5" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="31.5" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" ht="30" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" ht="31.5" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="31.5" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" ht="31.5" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" ht="31.5" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" ht="31.5" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>413</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18165" windowHeight="12390" activeTab="2"/>
+    <workbookView windowWidth="27870" windowHeight="12570" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Section01" sheetId="1" r:id="rId1"/>
     <sheet name="Section02" sheetId="2" r:id="rId2"/>
     <sheet name="Section03" sheetId="3" r:id="rId3"/>
+    <sheet name="Section04" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="639">
   <si>
     <t>单词/词组</t>
   </si>
@@ -1301,6 +1302,9 @@
     <t>attract international censure</t>
   </si>
   <si>
+    <t>censurable</t>
+  </si>
+  <si>
     <t>censor n.审查员</t>
   </si>
   <si>
@@ -1311,7 +1315,7 @@
 n.恭维</t>
   </si>
   <si>
-    <t>complimentary a.赠送的</t>
+    <t>complimentary a.赠送的，赞美的</t>
   </si>
   <si>
     <t>complement n.补足</t>
@@ -1332,10 +1336,709 @@
     <t>vi.慰问，吊唁</t>
   </si>
   <si>
-    <t>condole with sb</t>
+    <t>condole with sb on sth</t>
   </si>
   <si>
     <t>dole = 失业金</t>
+  </si>
+  <si>
+    <t>condolent a.哀悼的</t>
+  </si>
+  <si>
+    <t>contemptuous</t>
+  </si>
+  <si>
+    <t>a.轻蔑的</t>
+  </si>
+  <si>
+    <t>contempt n.蔑视</t>
+  </si>
+  <si>
+    <t>convoluted</t>
+  </si>
+  <si>
+    <t>a.复杂的，难懂的</t>
+  </si>
+  <si>
+    <t>vol = involve = 缠绕</t>
+  </si>
+  <si>
+    <t>convolution</t>
+  </si>
+  <si>
+    <t>complicated</t>
+  </si>
+  <si>
+    <t>culinary</t>
+  </si>
+  <si>
+    <t>a.烹饪的</t>
+  </si>
+  <si>
+    <t>culinary culture/skill</t>
+  </si>
+  <si>
+    <t>decry</t>
+  </si>
+  <si>
+    <t>vt.谴责</t>
+  </si>
+  <si>
+    <t>cry = 呼喊</t>
+  </si>
+  <si>
+    <t>discredit</t>
+  </si>
+  <si>
+    <t>vt.使...丧失名誉</t>
+  </si>
+  <si>
+    <t>discredited a.名誉扫地的</t>
+  </si>
+  <si>
+    <t>disgrace</t>
+  </si>
+  <si>
+    <t>disposal</t>
+  </si>
+  <si>
+    <t>n.处理，清除</t>
+  </si>
+  <si>
+    <t>at your disposal 任你处理</t>
+  </si>
+  <si>
+    <t>dispose vt.安置
+disposition n.性情</t>
+  </si>
+  <si>
+    <t>downplay</t>
+  </si>
+  <si>
+    <t>vt.轻描淡写</t>
+  </si>
+  <si>
+    <t>downplay significance</t>
+  </si>
+  <si>
+    <t>overplay</t>
+  </si>
+  <si>
+    <t>understate/overstate</t>
+  </si>
+  <si>
+    <t>elicit</t>
+  </si>
+  <si>
+    <t>vt.引起，引发</t>
+  </si>
+  <si>
+    <t>elicit a positive response</t>
+  </si>
+  <si>
+    <t>lic = delicious = 诱惑</t>
+  </si>
+  <si>
+    <t>evoke
+provoke</t>
+  </si>
+  <si>
+    <t>emulate</t>
+  </si>
+  <si>
+    <t>a.模仿，效仿</t>
+  </si>
+  <si>
+    <t>emulation</t>
+  </si>
+  <si>
+    <t>imitate</t>
+  </si>
+  <si>
+    <t>enumerate 列举</t>
+  </si>
+  <si>
+    <t>explicate</t>
+  </si>
+  <si>
+    <t>vt.解释，说明</t>
+  </si>
+  <si>
+    <t>explicit n.清楚明白的
+explicable
+inexplicable</t>
+  </si>
+  <si>
+    <t>extensive</t>
+  </si>
+  <si>
+    <t>a.广泛的，巨大的</t>
+  </si>
+  <si>
+    <t>wide-ranging</t>
+  </si>
+  <si>
+    <t>narrow</t>
+  </si>
+  <si>
+    <t>groundless</t>
+  </si>
+  <si>
+    <t>a.没有根据的</t>
+  </si>
+  <si>
+    <t>groundless argument</t>
+  </si>
+  <si>
+    <t>baseless</t>
+  </si>
+  <si>
+    <t>inconsequential</t>
+  </si>
+  <si>
+    <t>a.不重要的</t>
+  </si>
+  <si>
+    <t>consequence</t>
+  </si>
+  <si>
+    <t>unimportant
+negligible</t>
+  </si>
+  <si>
+    <t>intricate</t>
+  </si>
+  <si>
+    <t>a.复杂的，精细的</t>
+  </si>
+  <si>
+    <t>extricate v.拜托
+convoluted</t>
+  </si>
+  <si>
+    <t>labyrinth</t>
+  </si>
+  <si>
+    <t>n.迷宫，错综复杂的事情</t>
+  </si>
+  <si>
+    <t>laybrinthine a.迷宫的</t>
+  </si>
+  <si>
+    <t>maze</t>
+  </si>
+  <si>
+    <t>loathe</t>
+  </si>
+  <si>
+    <t>vt.厌恶</t>
+  </si>
+  <si>
+    <t>loath a.不情愿的 = reluctant</t>
+  </si>
+  <si>
+    <t>muddle</t>
+  </si>
+  <si>
+    <t>v.混淆
+n.混乱</t>
+  </si>
+  <si>
+    <t>be in a muddle
+muddle (up) two things</t>
+  </si>
+  <si>
+    <t>mud = 泥巴</t>
+  </si>
+  <si>
+    <t>confuse
+perplex</t>
+  </si>
+  <si>
+    <t>neophyte</t>
+  </si>
+  <si>
+    <t>n.新手</t>
+  </si>
+  <si>
+    <t>neo = new phyte = plant</t>
+  </si>
+  <si>
+    <t>rookie</t>
+  </si>
+  <si>
+    <t>veteran 老兵</t>
+  </si>
+  <si>
+    <t>objective</t>
+  </si>
+  <si>
+    <t>a.客观的</t>
+  </si>
+  <si>
+    <t>object n.对象，目的 v.反对
+objectionable</t>
+  </si>
+  <si>
+    <t>unbiased
+fair</t>
+  </si>
+  <si>
+    <t>subjective</t>
+  </si>
+  <si>
+    <t>obligate</t>
+  </si>
+  <si>
+    <t>vt.迫使</t>
+  </si>
+  <si>
+    <t>obligate sb to do sth</t>
+  </si>
+  <si>
+    <t>oblige vt.迫使 be obliged to do
+obligation
+obligatory a.规定性的</t>
+  </si>
+  <si>
+    <t>overshadow</t>
+  </si>
+  <si>
+    <t>vt.给...蒙上阴影</t>
+  </si>
+  <si>
+    <t>A overshadow B</t>
+  </si>
+  <si>
+    <t>patron</t>
+  </si>
+  <si>
+    <t>n.资助人，顾客</t>
+  </si>
+  <si>
+    <t>patronize vt.赞助，屈尊对待
+patronizing a.摆架子的</t>
+  </si>
+  <si>
+    <t>pragmatic</t>
+  </si>
+  <si>
+    <t>a.务实的</t>
+  </si>
+  <si>
+    <t>prevail</t>
+  </si>
+  <si>
+    <t>vi.盛行，流行，获胜</t>
+  </si>
+  <si>
+    <t>prevail over</t>
+  </si>
+  <si>
+    <t>vail = value</t>
+  </si>
+  <si>
+    <t>prevailing a.流行的</t>
+  </si>
+  <si>
+    <t>prevalent</t>
+  </si>
+  <si>
+    <t>a.流行的</t>
+  </si>
+  <si>
+    <t>prevalence</t>
+  </si>
+  <si>
+    <t>prevailing</t>
+  </si>
+  <si>
+    <t>provoke</t>
+  </si>
+  <si>
+    <t>vt.引起，挑衅</t>
+  </si>
+  <si>
+    <t>vok = voice</t>
+  </si>
+  <si>
+    <t>provocative a.挑衅的
+provocation n.刺激的东西</t>
+  </si>
+  <si>
+    <t>evoke v.引起，唤起</t>
+  </si>
+  <si>
+    <t>remedy</t>
+  </si>
+  <si>
+    <t>vt.改善，纠正</t>
+  </si>
+  <si>
+    <t>remedy the situation</t>
+  </si>
+  <si>
+    <t>med = medicine</t>
+  </si>
+  <si>
+    <t>remedial a.纠正的</t>
+  </si>
+  <si>
+    <t>stunning</t>
+  </si>
+  <si>
+    <t>a.令人震惊的</t>
+  </si>
+  <si>
+    <t>stun vt.使人震惊
+stunned</t>
+  </si>
+  <si>
+    <t>startle</t>
+  </si>
+  <si>
+    <t>supplant</t>
+  </si>
+  <si>
+    <t>vt.代替</t>
+  </si>
+  <si>
+    <t>B is supplanted by A</t>
+  </si>
+  <si>
+    <t>sup = 下</t>
+  </si>
+  <si>
+    <t>replace
+substitute</t>
+  </si>
+  <si>
+    <t>unprecedented</t>
+  </si>
+  <si>
+    <t>a.前所未有的</t>
+  </si>
+  <si>
+    <t>precedent n.先例</t>
+  </si>
+  <si>
+    <t>unexampled</t>
+  </si>
+  <si>
+    <t>unwarranted</t>
+  </si>
+  <si>
+    <t>warrant n.执行令，授权令</t>
+  </si>
+  <si>
+    <t>groundless
+baseless</t>
+  </si>
+  <si>
+    <t>warranted</t>
+  </si>
+  <si>
+    <t>vice</t>
+  </si>
+  <si>
+    <t>n.罪行，恶行</t>
+  </si>
+  <si>
+    <t>vice versa</t>
+  </si>
+  <si>
+    <t>vicious a.狂暴的，残酷的 = brutal</t>
+  </si>
+  <si>
+    <t>virtue n.美德</t>
+  </si>
+  <si>
+    <t>zealot</t>
+  </si>
+  <si>
+    <t>n.狂热者</t>
+  </si>
+  <si>
+    <t>zeal n.热情
+zealous a.热情的</t>
+  </si>
+  <si>
+    <t>extremist n.极端分子</t>
+  </si>
+  <si>
+    <t>affable</t>
+  </si>
+  <si>
+    <t>a.和蔼的</t>
+  </si>
+  <si>
+    <t>an affable man</t>
+  </si>
+  <si>
+    <t>affability</t>
+  </si>
+  <si>
+    <t>amenable a.顺从的；顺服的</t>
+  </si>
+  <si>
+    <t>amicable</t>
+  </si>
+  <si>
+    <t>a.友好的</t>
+  </si>
+  <si>
+    <t>an amicable relationship</t>
+  </si>
+  <si>
+    <t>ami = 爱</t>
+  </si>
+  <si>
+    <t>allure</t>
+  </si>
+  <si>
+    <t>n.魅力，诱惑力</t>
+  </si>
+  <si>
+    <t>lure v.诱惑 n.诱惑
+alluring a.诱人的</t>
+  </si>
+  <si>
+    <t>anomalous</t>
+  </si>
+  <si>
+    <t>a.异常的</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>anomaly n.异常反常现象</t>
+  </si>
+  <si>
+    <t>abnormal
+atypical
+exceptional</t>
+  </si>
+  <si>
+    <t>asset</t>
+  </si>
+  <si>
+    <t>n.资产，优点</t>
+  </si>
+  <si>
+    <t>debt 债务</t>
+  </si>
+  <si>
+    <t>blemish</t>
+  </si>
+  <si>
+    <t>vt.损害
+n.瑕疵</t>
+  </si>
+  <si>
+    <t>blemish balm BB霜</t>
+  </si>
+  <si>
+    <t>blemished a.有瑕疵的
+unblemished</t>
+  </si>
+  <si>
+    <t>compassionate</t>
+  </si>
+  <si>
+    <t>a.同情的</t>
+  </si>
+  <si>
+    <t>com = 共同</t>
+  </si>
+  <si>
+    <t>compassion</t>
+  </si>
+  <si>
+    <t>sympathetic</t>
+  </si>
+  <si>
+    <t>apathetic a.冷漠的</t>
+  </si>
+  <si>
+    <t>passionate</t>
+  </si>
+  <si>
+    <t>consistent</t>
+  </si>
+  <si>
+    <t>a.一致的，始终的</t>
+  </si>
+  <si>
+    <t>A is consistent with B</t>
+  </si>
+  <si>
+    <t>inconsistent
+consistency</t>
+  </si>
+  <si>
+    <t>contagious</t>
+  </si>
+  <si>
+    <t>a.传染的，有感染力的</t>
+  </si>
+  <si>
+    <t>contagion n.传染</t>
+  </si>
+  <si>
+    <t>infectious
+communicative
+transmissible</t>
+  </si>
+  <si>
+    <t>decisive</t>
+  </si>
+  <si>
+    <t>a.果敢的，决定性的</t>
+  </si>
+  <si>
+    <t>decided a.明确的</t>
+  </si>
+  <si>
+    <t>deciding</t>
+  </si>
+  <si>
+    <t>discursive</t>
+  </si>
+  <si>
+    <t>a.散漫的，分析的</t>
+  </si>
+  <si>
+    <t>dis = 分开</t>
+  </si>
+  <si>
+    <t>discursion</t>
+  </si>
+  <si>
+    <t>digression
+analytical</t>
+  </si>
+  <si>
+    <t>disparate</t>
+  </si>
+  <si>
+    <t>a.不同的，多元的</t>
+  </si>
+  <si>
+    <t>disparity</t>
+  </si>
+  <si>
+    <t>desperate a.绝望的，不顾一切的</t>
+  </si>
+  <si>
+    <t>engaging</t>
+  </si>
+  <si>
+    <t>a.迷人的</t>
+  </si>
+  <si>
+    <t>engage in sth</t>
+  </si>
+  <si>
+    <t>engage v.从事，订婚</t>
+  </si>
+  <si>
+    <t>inviting</t>
+  </si>
+  <si>
+    <t>erode</t>
+  </si>
+  <si>
+    <t>vt.侵蚀，削弱</t>
+  </si>
+  <si>
+    <t>erosive a.侵蚀性的</t>
+  </si>
+  <si>
+    <t>exigency</t>
+  </si>
+  <si>
+    <t>n.危急关头</t>
+  </si>
+  <si>
+    <t>exact</t>
+  </si>
+  <si>
+    <t>exigent a.迫切的</t>
+  </si>
+  <si>
+    <t>emergency
+breaking point</t>
+  </si>
+  <si>
+    <t>flippant</t>
+  </si>
+  <si>
+    <t>a.轻率的</t>
+  </si>
+  <si>
+    <t>flip</t>
+  </si>
+  <si>
+    <t>flippancy</t>
+  </si>
+  <si>
+    <t>facetious</t>
+  </si>
+  <si>
+    <t>a.爱开玩笑的</t>
+  </si>
+  <si>
+    <t>face</t>
+  </si>
+  <si>
+    <t>fractious</t>
+  </si>
+  <si>
+    <t>be in a fractious mood</t>
+  </si>
+  <si>
+    <t>fraction</t>
+  </si>
+  <si>
+    <t>futile</t>
+  </si>
+  <si>
+    <t>a.无用的，徒劳的</t>
+  </si>
+  <si>
+    <t>a futile attempt</t>
+  </si>
+  <si>
+    <t>futility n.无用</t>
+  </si>
+  <si>
+    <t>fruitless
+vain</t>
+  </si>
+  <si>
+    <t>grandstanding</t>
+  </si>
+  <si>
+    <t>n.哗众取宠</t>
+  </si>
+  <si>
+    <t>grandstand vi.炫耀</t>
+  </si>
+  <si>
+    <t>show off</t>
+  </si>
+  <si>
+    <t>haphazard</t>
+  </si>
+  <si>
+    <t>a.偶然的，无计划的</t>
+  </si>
+  <si>
+    <t>hap = happen</t>
+  </si>
+  <si>
+    <t>hazardous a.危险的</t>
   </si>
 </sst>
 </file>
@@ -1344,9 +2047,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1373,18 +2076,32 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1397,47 +2114,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1450,7 +2129,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1472,9 +2151,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1487,6 +2165,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
@@ -1494,15 +2203,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1523,19 +2226,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1553,36 +2250,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1595,7 +2262,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,7 +2334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1619,19 +2352,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1649,13 +2382,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1667,43 +2400,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1714,30 +2417,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1761,6 +2440,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1794,23 +2497,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1819,142 +2522,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1983,16 +2686,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2317,901 +3020,901 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.0916666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="31.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.4916666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.9833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.6916666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.9666666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="31.4083333333333" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="16.0916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.4916666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.9833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6916666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.9666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.4083333333333" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" ht="31.5" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" ht="31.5" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" ht="31.5" spans="1:6">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:6">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" ht="31.5" spans="1:7">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="31.5" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" ht="47.25" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" ht="31.5" spans="1:6">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" ht="31.5" spans="1:6">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="6" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:7">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="34" ht="31.5" spans="1:5">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="37" ht="31.5" spans="1:5">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:7">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="41" ht="63" spans="1:6">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="44" ht="31.5" spans="1:5">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="6" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="47" ht="31.5" spans="1:6">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="6" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="6" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="54" ht="31.5" spans="1:8">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="1" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="56" ht="31.5" spans="1:8">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="1" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="58" ht="31.5" spans="1:6">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3238,33 +3941,33 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>250</v>
       </c>
       <c r="B2" t="s">
@@ -3276,12 +3979,12 @@
       <c r="E2" t="s">
         <v>253</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>255</v>
       </c>
       <c r="B3" t="s">
@@ -3293,7 +3996,7 @@
       <c r="D3" t="s">
         <v>258</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>259</v>
       </c>
     </row>
@@ -3321,7 +4024,7 @@
       <c r="B5" t="s">
         <v>265</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>266</v>
       </c>
     </row>
@@ -3329,13 +4032,13 @@
       <c r="A6" t="s">
         <v>267</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C6" t="s">
         <v>269</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>270</v>
       </c>
     </row>
@@ -3343,7 +4046,7 @@
       <c r="A7" t="s">
         <v>271</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>272</v>
       </c>
       <c r="C7" t="s">
@@ -3363,12 +4066,12 @@
       <c r="B8" t="s">
         <v>277</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>279</v>
       </c>
       <c r="B9" t="s">
@@ -3385,7 +4088,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>283</v>
       </c>
       <c r="B10" t="s">
@@ -3405,7 +4108,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>288</v>
       </c>
       <c r="B11" t="s">
@@ -3413,7 +4116,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>290</v>
       </c>
       <c r="B12" t="s">
@@ -3439,7 +4142,7 @@
       <c r="C13" t="s">
         <v>297</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3447,18 +4150,18 @@
       <c r="A14" t="s">
         <v>299</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="9" t="s">
         <v>300</v>
       </c>
       <c r="C14" t="s">
         <v>301</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>303</v>
       </c>
       <c r="B15" t="s">
@@ -3469,7 +4172,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="8" t="s">
         <v>306</v>
       </c>
       <c r="B16" t="s">
@@ -3511,7 +4214,7 @@
       <c r="A19" t="s">
         <v>316</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="9" t="s">
         <v>317</v>
       </c>
       <c r="C19" t="s">
@@ -3536,7 +4239,7 @@
       </c>
     </row>
     <row r="21" ht="30" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>324</v>
       </c>
       <c r="B21" t="s">
@@ -3545,7 +4248,7 @@
       <c r="C21" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3556,7 +4259,7 @@
       <c r="B22" t="s">
         <v>329</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>330</v>
       </c>
       <c r="F22" t="s">
@@ -3578,7 +4281,7 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="8" t="s">
         <v>336</v>
       </c>
       <c r="B24" t="s">
@@ -3598,7 +4301,7 @@
       <c r="A25" t="s">
         <v>340</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="9" t="s">
         <v>341</v>
       </c>
       <c r="C25" t="s">
@@ -3612,7 +4315,7 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>345</v>
       </c>
       <c r="B26" t="s">
@@ -3623,10 +4326,10 @@
       </c>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="9" t="s">
         <v>349</v>
       </c>
       <c r="C27" t="s">
@@ -3646,10 +4349,10 @@
       <c r="A28" t="s">
         <v>354</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="9" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3657,7 +4360,7 @@
       <c r="A29" t="s">
         <v>357</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="9" t="s">
         <v>358</v>
       </c>
       <c r="E29" t="s">
@@ -3668,7 +4371,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="8" t="s">
         <v>361</v>
       </c>
       <c r="B30" t="s">
@@ -3690,7 +4393,7 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="8" t="s">
         <v>367</v>
       </c>
       <c r="B32" t="s">
@@ -3715,12 +4418,12 @@
       <c r="A34" t="s">
         <v>372</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="9" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="8" t="s">
         <v>374</v>
       </c>
       <c r="B35" t="s">
@@ -3737,13 +4440,13 @@
       </c>
     </row>
     <row r="36" ht="30" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="8" t="s">
         <v>379</v>
       </c>
       <c r="B36" t="s">
         <v>380</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="9" t="s">
         <v>381</v>
       </c>
     </row>
@@ -3754,7 +4457,7 @@
       <c r="B37" t="s">
         <v>383</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="9" t="s">
         <v>384</v>
       </c>
     </row>
@@ -3795,51 +4498,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.9166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.475" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.8416666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.4333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.475" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>393</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3856,7 +4559,7 @@
       <c r="A3" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3867,53 +4570,910 @@
       <c r="A4" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>401</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" ht="31.5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B5" s="4" t="s">
         <v>405</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>406</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="13" ht="31.5" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="15" ht="31.5" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="17" ht="47.25" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" ht="31.5" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" ht="31.5" spans="1:7">
+      <c r="A21" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="24" ht="31.5" spans="1:6">
+      <c r="A24" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" ht="31.5" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="26" ht="31.5" spans="1:7">
+      <c r="A26" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" ht="47.25" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" ht="31.5" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="33" ht="31.5" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="35" ht="31.5" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="36" ht="31.5" spans="1:6">
+      <c r="A36" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="38" ht="31.5" spans="1:7">
+      <c r="A38" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="40" ht="31.5" spans="1:6">
+      <c r="A40" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="14.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.7666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.325" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.9416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.3583333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.225" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="5" ht="47.25" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="9" ht="31.5" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" ht="47.25" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="12" ht="31.5" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="16" ht="31.5" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" ht="31.5" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,20 +4,328 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="3"/>
+    <workbookView windowWidth="27870" windowHeight="12570" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Section01" sheetId="1" r:id="rId1"/>
-    <sheet name="Section02" sheetId="2" r:id="rId2"/>
-    <sheet name="Section03" sheetId="3" r:id="rId3"/>
-    <sheet name="Section04" sheetId="4" r:id="rId4"/>
+    <sheet name="Links" sheetId="5" r:id="rId1"/>
+    <sheet name="Section01" sheetId="1" r:id="rId2"/>
+    <sheet name="Section02" sheetId="2" r:id="rId3"/>
+    <sheet name="Section03" sheetId="3" r:id="rId4"/>
+    <sheet name="Section04" sheetId="4" r:id="rId5"/>
+    <sheet name="Section05" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="912">
+  <si>
+    <t>GRE单词地基词全集精讲</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY/</t>
+  </si>
+  <si>
+    <t>Section01</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=1</t>
+  </si>
+  <si>
+    <t>Section02</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=3</t>
+  </si>
+  <si>
+    <t>Section03</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=4</t>
+  </si>
+  <si>
+    <t>Section04</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=5</t>
+  </si>
+  <si>
+    <t>Section05</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=6</t>
+  </si>
+  <si>
+    <t>Section06</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=7</t>
+  </si>
+  <si>
+    <t>Section07</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=8</t>
+  </si>
+  <si>
+    <t>Section08</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=9</t>
+  </si>
+  <si>
+    <t>Section09</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=10</t>
+  </si>
+  <si>
+    <t>Section10</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=11</t>
+  </si>
+  <si>
+    <t>Section11</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=12</t>
+  </si>
+  <si>
+    <t>Section12</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=13</t>
+  </si>
+  <si>
+    <t>Section13</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=14</t>
+  </si>
+  <si>
+    <t>Section14</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=15</t>
+  </si>
+  <si>
+    <t>Section15</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=16</t>
+  </si>
+  <si>
+    <t>Section16</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=17</t>
+  </si>
+  <si>
+    <t>Section17</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=18</t>
+  </si>
+  <si>
+    <t>Section18</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=19</t>
+  </si>
+  <si>
+    <t>Section19</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=20</t>
+  </si>
+  <si>
+    <t>Section20</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=21</t>
+  </si>
+  <si>
+    <t>Section21</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=22</t>
+  </si>
+  <si>
+    <t>Section22</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=23</t>
+  </si>
+  <si>
+    <t>Section23</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=24</t>
+  </si>
+  <si>
+    <t>Section24</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=25</t>
+  </si>
+  <si>
+    <t>Section25</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=26</t>
+  </si>
+  <si>
+    <t>Section26</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=27</t>
+  </si>
+  <si>
+    <t>Section27</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=28</t>
+  </si>
+  <si>
+    <t>Section28</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=29</t>
+  </si>
+  <si>
+    <t>Section29</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=30</t>
+  </si>
+  <si>
+    <t>Section30</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=31</t>
+  </si>
+  <si>
+    <t>Section31</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=32</t>
+  </si>
+  <si>
+    <t>Section32</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=33</t>
+  </si>
+  <si>
+    <t>Section33</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=34</t>
+  </si>
+  <si>
+    <t>Section34</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=35</t>
+  </si>
+  <si>
+    <t>Section35</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=36</t>
+  </si>
+  <si>
+    <t>Section36</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=37</t>
+  </si>
+  <si>
+    <t>Section37</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=38</t>
+  </si>
+  <si>
+    <t>Section38</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=39</t>
+  </si>
+  <si>
+    <t>Section39</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=40</t>
+  </si>
+  <si>
+    <t>Section40</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=41</t>
+  </si>
+  <si>
+    <t>Section41</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=42</t>
+  </si>
+  <si>
+    <t>Section42</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=43</t>
+  </si>
+  <si>
+    <t>Section43</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=44</t>
+  </si>
+  <si>
+    <t>Section44</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=45</t>
+  </si>
+  <si>
+    <t>Section45</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=46</t>
+  </si>
+  <si>
+    <t>Section46</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=47</t>
+  </si>
+  <si>
+    <t>Section47</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=48</t>
+  </si>
+  <si>
+    <t>Section48</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=49</t>
+  </si>
+  <si>
+    <t>Section49</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=50</t>
+  </si>
+  <si>
+    <t>Section50</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1Zt4y1G7AY?p=51</t>
+  </si>
   <si>
     <t>单词/词组</t>
   </si>
@@ -1925,7 +2233,7 @@
     <t>a.不同的，多元的</t>
   </si>
   <si>
-    <t>disparity</t>
+    <t>disparity 不同，不等</t>
   </si>
   <si>
     <t>desperate a.绝望的，不顾一切的</t>
@@ -2039,6 +2347,554 @@
   </si>
   <si>
     <t>hazardous a.危险的</t>
+  </si>
+  <si>
+    <t>heterogeneous</t>
+  </si>
+  <si>
+    <t>a.异质的</t>
+  </si>
+  <si>
+    <t>hetero异 &lt;opp&gt; homo同
+homosexual
+heterosexual</t>
+  </si>
+  <si>
+    <t>heterogeneity n.异质性</t>
+  </si>
+  <si>
+    <t>homogeneous</t>
+  </si>
+  <si>
+    <t>hodgepodge</t>
+  </si>
+  <si>
+    <t>n.大杂烩</t>
+  </si>
+  <si>
+    <t>独特的构词</t>
+  </si>
+  <si>
+    <t>hotchpotch
+mishmash
+omnium-gatherum</t>
+  </si>
+  <si>
+    <t>inattentive</t>
+  </si>
+  <si>
+    <t>a.疏忽的</t>
+  </si>
+  <si>
+    <t>attentive a.关注的</t>
+  </si>
+  <si>
+    <t>intriguing</t>
+  </si>
+  <si>
+    <t>a.吸引人的</t>
+  </si>
+  <si>
+    <t>intrigue vt.吸引 n.阴谋</t>
+  </si>
+  <si>
+    <t>inveterate</t>
+  </si>
+  <si>
+    <t>a.根深蒂固的</t>
+  </si>
+  <si>
+    <t>an inveterate gambler</t>
+  </si>
+  <si>
+    <t>veteran n.老兵
+in 表强调</t>
+  </si>
+  <si>
+    <t>deep-rooted</t>
+  </si>
+  <si>
+    <t>venerate 尊敬</t>
+  </si>
+  <si>
+    <t>ingrained</t>
+  </si>
+  <si>
+    <t>ingrained prejudice</t>
+  </si>
+  <si>
+    <t>in 表强调</t>
+  </si>
+  <si>
+    <t>engrained 通假字</t>
+  </si>
+  <si>
+    <t>irk</t>
+  </si>
+  <si>
+    <t>vt.使某人烦恼</t>
+  </si>
+  <si>
+    <t>it irks me</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>irksome a.令人厌烦的
+handsome</t>
+  </si>
+  <si>
+    <t>vex = irk
+vexing = irksome</t>
+  </si>
+  <si>
+    <t>mar</t>
+  </si>
+  <si>
+    <t>vt.破坏
+n.污点</t>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <t>mediocre</t>
+  </si>
+  <si>
+    <t>a.平庸的</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>common
+ordinary</t>
+  </si>
+  <si>
+    <t>monolithic</t>
+  </si>
+  <si>
+    <t>a.大一统的，巨大而平庸</t>
+  </si>
+  <si>
+    <t>monolithic processor
+单片处理机</t>
+  </si>
+  <si>
+    <t>mono = 单 (monopoly)
+lithic = 石头 = paleolithic</t>
+  </si>
+  <si>
+    <t>motley</t>
+  </si>
+  <si>
+    <t>a.杂色的
+n.混杂物</t>
+  </si>
+  <si>
+    <t>mote 尘埃</t>
+  </si>
+  <si>
+    <t>nepotism</t>
+  </si>
+  <si>
+    <t>n.裙带关系</t>
+  </si>
+  <si>
+    <t>nep = nephew/niece</t>
+  </si>
+  <si>
+    <t>nepotistic a.搞裙带关系的</t>
+  </si>
+  <si>
+    <t>opportunistic</t>
+  </si>
+  <si>
+    <t>a.机会主义的，投机取巧的</t>
+  </si>
+  <si>
+    <t>opportunity</t>
+  </si>
+  <si>
+    <t>opportune</t>
+  </si>
+  <si>
+    <t>a.时机恰当的，时机正好的</t>
+  </si>
+  <si>
+    <t>overarching</t>
+  </si>
+  <si>
+    <t>a.包含一切的，首要的</t>
+  </si>
+  <si>
+    <t>overarching problem 母题</t>
+  </si>
+  <si>
+    <t>arch = 拱形</t>
+  </si>
+  <si>
+    <t>partisanship</t>
+  </si>
+  <si>
+    <t>n.对党派的盲目支持</t>
+  </si>
+  <si>
+    <t>party = 党</t>
+  </si>
+  <si>
+    <t>patchwork</t>
+  </si>
+  <si>
+    <t>a.拼凑的
+n.拼凑</t>
+  </si>
+  <si>
+    <t>patch = 补丁，碎片</t>
+  </si>
+  <si>
+    <t>prose</t>
+  </si>
+  <si>
+    <t>n.无韵文，散文</t>
+  </si>
+  <si>
+    <t>sagacious</t>
+  </si>
+  <si>
+    <t>a.睿智的</t>
+  </si>
+  <si>
+    <t>sage = 圣人</t>
+  </si>
+  <si>
+    <t>sagacity</t>
+  </si>
+  <si>
+    <t>wise</t>
+  </si>
+  <si>
+    <t>stigma</t>
+  </si>
+  <si>
+    <t>n.耻辱，污点</t>
+  </si>
+  <si>
+    <t>a stigma is attached to</t>
+  </si>
+  <si>
+    <t>stick</t>
+  </si>
+  <si>
+    <t>stigmatic a.有污点的
+stigmatize vt.污名化</t>
+  </si>
+  <si>
+    <t>tendentious</t>
+  </si>
+  <si>
+    <t>a.有倾向性的，偏心的</t>
+  </si>
+  <si>
+    <t>tend = 倾向</t>
+  </si>
+  <si>
+    <t>biased
+partial</t>
+  </si>
+  <si>
+    <t>uneven</t>
+  </si>
+  <si>
+    <t>a.不规则的，不均衡的</t>
+  </si>
+  <si>
+    <t>uneven distribution</t>
+  </si>
+  <si>
+    <t>evenhanded a.公平的</t>
+  </si>
+  <si>
+    <t>even</t>
+  </si>
+  <si>
+    <t>oscillate</t>
+  </si>
+  <si>
+    <t>vi.摇摆，波动</t>
+  </si>
+  <si>
+    <t>oscillate between A and B</t>
+  </si>
+  <si>
+    <t>decisive a.果敢</t>
+  </si>
+  <si>
+    <t>vacillate</t>
+  </si>
+  <si>
+    <t>vi.犹豫不决</t>
+  </si>
+  <si>
+    <t>vacillate between A and B</t>
+  </si>
+  <si>
+    <t>vacillation n.
+vacillating = vacillant a.</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>n.变量
+a.可变的</t>
+  </si>
+  <si>
+    <t>vary
+variance 方差</t>
+  </si>
+  <si>
+    <t>changeable
+mutable</t>
+  </si>
+  <si>
+    <t>adversarial</t>
+  </si>
+  <si>
+    <t>a.对抗的</t>
+  </si>
+  <si>
+    <t>an adversarial ralationship</t>
+  </si>
+  <si>
+    <t>verse = 转</t>
+  </si>
+  <si>
+    <t>adverse
+adversary n.对手，敌手</t>
+  </si>
+  <si>
+    <t>antagonistic</t>
+  </si>
+  <si>
+    <t>a.敌对的，不相容的</t>
+  </si>
+  <si>
+    <t>be antagonistic to sb</t>
+  </si>
+  <si>
+    <t>antagonist n.敌手，反派
+protagonist n.主人公，拥护者</t>
+  </si>
+  <si>
+    <t>benign</t>
+  </si>
+  <si>
+    <t>a.良性的，和善的</t>
+  </si>
+  <si>
+    <t>a benign tumor 良性肿瘤</t>
+  </si>
+  <si>
+    <t>benignant a.仁慈的 benevolent benefit</t>
+  </si>
+  <si>
+    <t>malign a.恶性的</t>
+  </si>
+  <si>
+    <t>boorish</t>
+  </si>
+  <si>
+    <t>a.粗鲁的</t>
+  </si>
+  <si>
+    <t>a boorish rejection</t>
+  </si>
+  <si>
+    <t>boor = 粗人</t>
+  </si>
+  <si>
+    <t>urbane a.儒雅的</t>
+  </si>
+  <si>
+    <t>calamitous</t>
+  </si>
+  <si>
+    <t>a.灾难的</t>
+  </si>
+  <si>
+    <t>cala = 擦啦</t>
+  </si>
+  <si>
+    <t>calamity n.灾难</t>
+  </si>
+  <si>
+    <t>catastrophic
+disaster = disastrous</t>
+  </si>
+  <si>
+    <t>catastrophic</t>
+  </si>
+  <si>
+    <t>strophe = storm</t>
+  </si>
+  <si>
+    <t>chivalrous</t>
+  </si>
+  <si>
+    <t>a.骑士的，彬彬有礼的</t>
+  </si>
+  <si>
+    <t>valor = 英勇</t>
+  </si>
+  <si>
+    <t>cavalier a.无忧无虑的</t>
+  </si>
+  <si>
+    <t>circumspect</t>
+  </si>
+  <si>
+    <t>a.谨慎的</t>
+  </si>
+  <si>
+    <t>circum = circle</t>
+  </si>
+  <si>
+    <t>careful
+guarded
+wary</t>
+  </si>
+  <si>
+    <t>circumscribe 限制
+circumvent 回避</t>
+  </si>
+  <si>
+    <t>compound</t>
+  </si>
+  <si>
+    <t>n.化合物
+a.合成的
+vt.加剧</t>
+  </si>
+  <si>
+    <t>the problem is compounded by</t>
+  </si>
+  <si>
+    <t>confound vt.混淆</t>
+  </si>
+  <si>
+    <t>conspicuous</t>
+  </si>
+  <si>
+    <t>a.显眼的，扎眼的</t>
+  </si>
+  <si>
+    <t>spic = spectator = 看</t>
+  </si>
+  <si>
+    <t>obvious
+remarkable
+noticeable</t>
+  </si>
+  <si>
+    <t>contradictory</t>
+  </si>
+  <si>
+    <t>a.互相矛盾的</t>
+  </si>
+  <si>
+    <t>contra = contrast</t>
+  </si>
+  <si>
+    <t>contradiction
+contradict</t>
+  </si>
+  <si>
+    <t>conflicting</t>
+  </si>
+  <si>
+    <t>contrive</t>
+  </si>
+  <si>
+    <t>v.策划(贬义)</t>
+  </si>
+  <si>
+    <t>con = 强调
+triv = trick</t>
+  </si>
+  <si>
+    <t>contrived a.人为的
+contrivance n.诡计</t>
+  </si>
+  <si>
+    <t>deleterious</t>
+  </si>
+  <si>
+    <t>a.有害的</t>
+  </si>
+  <si>
+    <t>have a deleterious effect on</t>
+  </si>
+  <si>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>toxic
+poisonous</t>
+  </si>
+  <si>
+    <t>dichotomous</t>
+  </si>
+  <si>
+    <t>a.对立的</t>
+  </si>
+  <si>
+    <t>di = diverge
+tomy = atom</t>
+  </si>
+  <si>
+    <t>dichotomy</t>
+  </si>
+  <si>
+    <t>discern</t>
+  </si>
+  <si>
+    <t>vt.觉察到</t>
+  </si>
+  <si>
+    <t>cern = concern = 分开</t>
+  </si>
+  <si>
+    <t>discernable = discernible
+discernment n.洞察力</t>
+  </si>
+  <si>
+    <t>discretion</t>
+  </si>
+  <si>
+    <t>n.审慎，酌情决定权</t>
+  </si>
+  <si>
+    <t>at the discretion of 任你处置</t>
+  </si>
+  <si>
+    <t>discretionary a.酌情决定的</t>
+  </si>
+  <si>
+    <t>disingenuous</t>
+  </si>
+  <si>
+    <t>a.虚伪的，不诚实的</t>
+  </si>
+  <si>
+    <t>gen = generate</t>
+  </si>
+  <si>
+    <t>ingenuous a.老实的</t>
+  </si>
+  <si>
+    <t>ingenious a.灵巧的</t>
   </si>
 </sst>
 </file>
@@ -2046,10 +2902,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2076,10 +2932,62 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2092,29 +3000,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2128,18 +3014,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2158,15 +3037,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -2174,17 +3046,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2197,15 +3061,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2226,7 +3082,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2238,7 +3094,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2250,7 +3130,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2262,13 +3148,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2280,7 +3190,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2292,25 +3244,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2322,91 +3256,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2424,22 +3280,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2459,11 +3300,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2498,7 +3345,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2522,142 +3378,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2674,13 +3530,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2692,11 +3545,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="48">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3017,6 +3873,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="42.125" customWidth="1"/>
+    <col min="2" max="6" width="47.125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Zt4y1G7AY?p=1"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1Zt4y1G7AY?p=3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
@@ -3033,889 +4317,889 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
+      <c r="A2" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:5">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>12</v>
+      <c r="A3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="5" t="s">
-        <v>15</v>
+      <c r="A4" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>17</v>
+        <v>118</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
+      <c r="A5" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" ht="31.5" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>125</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
+      <c r="A7" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
+        <v>132</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="5" t="s">
-        <v>32</v>
+      <c r="A8" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" ht="31.5" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>39</v>
+        <v>140</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" ht="31.5" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
+        <v>144</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>148</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>49</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" ht="31.5" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>56</v>
+        <v>157</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" ht="31.5" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>61</v>
+        <v>162</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>62</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" ht="47.25" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>64</v>
+      <c r="A15" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>66</v>
+        <v>167</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>68</v>
+      <c r="A16" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>77</v>
+      <c r="A18" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>180</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>181</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="5" t="s">
-        <v>81</v>
+      <c r="A19" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>83</v>
+        <v>184</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" ht="31.5" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>91</v>
+        <v>191</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" ht="31.5" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>100</v>
+        <v>200</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>101</v>
+      <c r="A24" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="5" t="s">
-        <v>109</v>
+      <c r="A26" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>112</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
-      <c r="A27" s="5" t="s">
-        <v>113</v>
+      <c r="A27" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>117</v>
+        <v>217</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
-      <c r="A28" s="5" t="s">
-        <v>118</v>
+      <c r="A28" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>121</v>
+        <v>222</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>124</v>
+        <v>225</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>125</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="5" t="s">
-        <v>126</v>
+      <c r="A30" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>130</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>132</v>
+        <v>234</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
-      <c r="A32" s="5" t="s">
-        <v>134</v>
+      <c r="A32" s="4" t="s">
+        <v>236</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>136</v>
+        <v>237</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>137</v>
+        <v>239</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>140</v>
+        <v>242</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" ht="31.5" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>146</v>
+        <v>247</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
-      <c r="A35" s="5" t="s">
-        <v>147</v>
+      <c r="A35" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>150</v>
+        <v>251</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="5" t="s">
-        <v>151</v>
+      <c r="A36" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>153</v>
+        <v>255</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>155</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" ht="31.5" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>156</v>
+        <v>258</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>157</v>
+        <v>259</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>160</v>
+        <v>261</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>162</v>
+      <c r="A38" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>165</v>
+      <c r="A39" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>169</v>
+        <v>270</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>171</v>
+        <v>273</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>174</v>
+        <v>274</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="41" ht="63" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>175</v>
+        <v>277</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>176</v>
+        <v>278</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>178</v>
+        <v>279</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>179</v>
+        <v>281</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>180</v>
+        <v>282</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>181</v>
+        <v>283</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>182</v>
+        <v>284</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>183</v>
+        <v>285</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>184</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
-      <c r="A43" s="5" t="s">
-        <v>185</v>
+      <c r="A43" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>187</v>
+        <v>288</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>188</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" ht="31.5" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>189</v>
+        <v>291</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>192</v>
+        <v>292</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
-      <c r="A45" s="5" t="s">
-        <v>193</v>
+      <c r="A45" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>195</v>
+        <v>296</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>185</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="5" t="s">
-        <v>197</v>
+      <c r="A46" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>198</v>
+        <v>300</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>199</v>
+        <v>301</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>201</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47" ht="31.5" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>204</v>
+        <v>305</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>197</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="5" t="s">
-        <v>205</v>
+      <c r="A48" s="4" t="s">
+        <v>307</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="5" t="s">
-        <v>208</v>
+      <c r="A49" s="4" t="s">
+        <v>310</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>210</v>
+        <v>312</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>211</v>
+        <v>313</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>212</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
-      <c r="A50" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>214</v>
+      <c r="A50" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>316</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>215</v>
+        <v>317</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>216</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
-      <c r="A51" s="5" t="s">
-        <v>217</v>
+      <c r="A51" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>220</v>
+        <v>321</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="5" t="s">
-        <v>221</v>
+      <c r="A52" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>222</v>
+        <v>324</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>224</v>
+        <v>325</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>225</v>
+        <v>327</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>226</v>
+        <v>328</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>227</v>
+        <v>329</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>228</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" ht="31.5" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>229</v>
+        <v>331</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>231</v>
+        <v>332</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>333</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>232</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>233</v>
+        <v>335</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>234</v>
+        <v>336</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>235</v>
+        <v>337</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>236</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" ht="31.5" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>238</v>
+        <v>340</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>240</v>
+        <v>341</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>241</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
-      <c r="A57" s="5" t="s">
-        <v>242</v>
+      <c r="A57" s="4" t="s">
+        <v>344</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>244</v>
+        <v>345</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>245</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" ht="31.5" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>249</v>
+        <v>348</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>351</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>221</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3924,7 +5208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H39"/>
@@ -3942,551 +5226,551 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:7">
-      <c r="A2" s="8" t="s">
-        <v>250</v>
+      <c r="A2" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>252</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>254</v>
+        <v>355</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="8" t="s">
-        <v>255</v>
+      <c r="A3" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>259</v>
+        <v>360</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>362</v>
       </c>
       <c r="B4" t="s">
-        <v>261</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>364</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="H4" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:5">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>366</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>266</v>
+        <v>367</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:6">
       <c r="A6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>268</v>
+        <v>369</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>270</v>
+        <v>371</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="30" spans="1:8">
       <c r="A7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>272</v>
+        <v>373</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>374</v>
       </c>
       <c r="C7" t="s">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>376</v>
       </c>
       <c r="H7" t="s">
-        <v>275</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:5">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>278</v>
+        <v>379</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="8" t="s">
-        <v>279</v>
+      <c r="A9" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="B9" t="s">
-        <v>280</v>
+        <v>382</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="E9" t="s">
-        <v>282</v>
+        <v>384</v>
       </c>
       <c r="F9" t="s">
-        <v>283</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="8" t="s">
-        <v>283</v>
+      <c r="A10" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="B10" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
       <c r="C10" t="s">
-        <v>285</v>
+        <v>387</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="E10" t="s">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="F10" t="s">
-        <v>279</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="8" t="s">
-        <v>288</v>
+      <c r="A11" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8" t="s">
-        <v>290</v>
+      <c r="A12" s="2" t="s">
+        <v>392</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>394</v>
       </c>
       <c r="G12" t="s">
-        <v>293</v>
+        <v>395</v>
       </c>
       <c r="H12" t="s">
-        <v>294</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:6">
       <c r="A13" t="s">
-        <v>295</v>
+        <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
-        <v>297</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>298</v>
+        <v>399</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:5">
       <c r="A14" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>300</v>
+        <v>401</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>402</v>
       </c>
       <c r="C14" t="s">
-        <v>301</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>302</v>
+        <v>403</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="8" t="s">
-        <v>303</v>
+      <c r="A15" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>406</v>
       </c>
       <c r="E15" t="s">
-        <v>305</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="8" t="s">
-        <v>306</v>
+      <c r="A16" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="B16" t="s">
-        <v>307</v>
+        <v>409</v>
       </c>
       <c r="C16" t="s">
-        <v>308</v>
+        <v>410</v>
       </c>
       <c r="E16" t="s">
-        <v>309</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>412</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
-        <v>312</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>313</v>
+        <v>415</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>416</v>
       </c>
       <c r="E18" t="s">
-        <v>315</v>
+        <v>417</v>
       </c>
       <c r="F18" t="s">
-        <v>306</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:4">
       <c r="A19" t="s">
-        <v>316</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>317</v>
+        <v>418</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="C19" t="s">
-        <v>318</v>
+        <v>420</v>
       </c>
       <c r="D19" t="s">
-        <v>319</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>422</v>
       </c>
       <c r="B20" t="s">
-        <v>321</v>
+        <v>423</v>
       </c>
       <c r="E20" t="s">
-        <v>322</v>
+        <v>424</v>
       </c>
       <c r="G20" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:5">
-      <c r="A21" s="8" t="s">
-        <v>324</v>
+      <c r="A21" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="B21" t="s">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="C21" t="s">
-        <v>326</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>327</v>
+        <v>428</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:6">
       <c r="A22" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="B22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>330</v>
+        <v>431</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>432</v>
       </c>
       <c r="F22" t="s">
-        <v>331</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>332</v>
+        <v>434</v>
       </c>
       <c r="B23" t="s">
-        <v>333</v>
+        <v>435</v>
       </c>
       <c r="C23" t="s">
-        <v>334</v>
+        <v>436</v>
       </c>
       <c r="E23" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="8" t="s">
-        <v>336</v>
+      <c r="A24" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="B24" t="s">
-        <v>337</v>
+        <v>439</v>
       </c>
       <c r="D24" t="s">
-        <v>338</v>
+        <v>440</v>
       </c>
       <c r="E24" t="s">
-        <v>339</v>
+        <v>441</v>
       </c>
       <c r="F24" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:6">
       <c r="A25" t="s">
-        <v>340</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>341</v>
+        <v>442</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>443</v>
       </c>
       <c r="C25" t="s">
-        <v>342</v>
+        <v>444</v>
       </c>
       <c r="D25" t="s">
-        <v>343</v>
+        <v>445</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="8" t="s">
-        <v>345</v>
+      <c r="A26" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="B26" t="s">
-        <v>346</v>
+        <v>448</v>
       </c>
       <c r="F26" t="s">
-        <v>347</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>349</v>
+      <c r="A27" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>451</v>
       </c>
       <c r="C27" t="s">
-        <v>350</v>
+        <v>452</v>
       </c>
       <c r="D27" t="s">
-        <v>351</v>
+        <v>453</v>
       </c>
       <c r="E27" t="s">
-        <v>352</v>
+        <v>454</v>
       </c>
       <c r="H27" t="s">
-        <v>353</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" ht="45" spans="1:8">
       <c r="A28" t="s">
-        <v>354</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>356</v>
+        <v>456</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:6">
       <c r="A29" t="s">
-        <v>357</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>358</v>
+        <v>459</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>460</v>
       </c>
       <c r="E29" t="s">
-        <v>359</v>
+        <v>461</v>
       </c>
       <c r="F29" t="s">
-        <v>360</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="8" t="s">
-        <v>361</v>
+      <c r="A30" s="2" t="s">
+        <v>463</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>464</v>
       </c>
       <c r="C30" t="s">
-        <v>363</v>
+        <v>465</v>
       </c>
       <c r="E30" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>365</v>
+        <v>467</v>
       </c>
       <c r="B31" t="s">
-        <v>366</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="8" t="s">
-        <v>367</v>
+      <c r="A32" s="2" t="s">
+        <v>469</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="F32" t="s">
-        <v>299</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>369</v>
+        <v>471</v>
       </c>
       <c r="B33" t="s">
-        <v>370</v>
+        <v>472</v>
       </c>
       <c r="C33" t="s">
-        <v>371</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:2">
       <c r="A34" t="s">
-        <v>372</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>373</v>
+        <v>474</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="8" t="s">
-        <v>374</v>
+      <c r="A35" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="B35" t="s">
-        <v>375</v>
+        <v>477</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>478</v>
       </c>
       <c r="D35" t="s">
-        <v>377</v>
+        <v>479</v>
       </c>
       <c r="F35" t="s">
-        <v>378</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:5">
-      <c r="A36" s="8" t="s">
-        <v>379</v>
+      <c r="A36" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="B36" t="s">
-        <v>380</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>381</v>
+        <v>482</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:6">
       <c r="A37" t="s">
-        <v>382</v>
+        <v>484</v>
       </c>
       <c r="B37" t="s">
-        <v>383</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>384</v>
+        <v>485</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>385</v>
+        <v>487</v>
       </c>
       <c r="B38" t="s">
-        <v>386</v>
+        <v>488</v>
       </c>
       <c r="D38" t="s">
-        <v>387</v>
+        <v>489</v>
       </c>
       <c r="E38" t="s">
-        <v>388</v>
+        <v>490</v>
       </c>
       <c r="F38" t="s">
-        <v>233</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>389</v>
+        <v>491</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>492</v>
       </c>
       <c r="D39" t="s">
-        <v>391</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4495,7 +5779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H40"/>
@@ -4514,598 +5798,598 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
-        <v>392</v>
+      <c r="A2" s="4" t="s">
+        <v>494</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>393</v>
+        <v>495</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>395</v>
+        <v>497</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>396</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>398</v>
+        <v>499</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>500</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>399</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:8">
-      <c r="A4" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>401</v>
+      <c r="A4" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>402</v>
+        <v>504</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>403</v>
+        <v>505</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>404</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" ht="31.5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>406</v>
+        <v>507</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>508</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>407</v>
+        <v>509</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>408</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>409</v>
+      <c r="A6" s="4" t="s">
+        <v>511</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>512</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>411</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
-        <v>412</v>
+      <c r="A7" s="4" t="s">
+        <v>514</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>413</v>
+        <v>515</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>414</v>
+        <v>516</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>415</v>
+        <v>517</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>416</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="5" t="s">
-        <v>417</v>
+      <c r="A8" s="4" t="s">
+        <v>519</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>418</v>
+        <v>520</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>419</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>420</v>
+        <v>522</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>421</v>
+        <v>523</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>422</v>
+        <v>524</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>423</v>
+        <v>525</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>424</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>425</v>
+      <c r="A10" s="4" t="s">
+        <v>527</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>426</v>
+        <v>528</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>427</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>428</v>
+        <v>530</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>429</v>
+        <v>531</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>430</v>
+        <v>532</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>400</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>431</v>
+        <v>533</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>432</v>
+        <v>534</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>434</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" ht="31.5" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>435</v>
+        <v>537</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>436</v>
+        <v>538</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>438</v>
+        <v>539</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5" t="s">
-        <v>439</v>
+      <c r="A14" s="4" t="s">
+        <v>541</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>440</v>
+        <v>542</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>441</v>
+        <v>543</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>443</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" ht="31.5" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>444</v>
+        <v>546</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>445</v>
+        <v>547</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>446</v>
+        <v>548</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>448</v>
+        <v>549</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5" t="s">
-        <v>449</v>
+      <c r="A16" s="4" t="s">
+        <v>551</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>450</v>
+        <v>552</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>451</v>
+        <v>553</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>452</v>
+        <v>554</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>453</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" ht="47.25" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>454</v>
+      <c r="A17" s="4" t="s">
+        <v>556</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>456</v>
+        <v>557</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>457</v>
+        <v>559</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>459</v>
+        <v>561</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>460</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>461</v>
+        <v>563</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>462</v>
+        <v>564</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>463</v>
+        <v>565</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>464</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>465</v>
+      <c r="A20" s="4" t="s">
+        <v>567</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>466</v>
+        <v>568</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>468</v>
+        <v>569</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="21" ht="31.5" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>469</v>
+        <v>571</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>471</v>
+        <v>572</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
-        <v>472</v>
+      <c r="A22" s="4" t="s">
+        <v>574</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>474</v>
+        <v>576</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>475</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>476</v>
+      <c r="A23" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>477</v>
+        <v>579</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>478</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" ht="31.5" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>481</v>
+      <c r="A24" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>583</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="25" ht="31.5" spans="1:7">
-      <c r="A25" s="5" t="s">
-        <v>484</v>
+        <v>584</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>586</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>486</v>
+        <v>587</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>487</v>
+        <v>589</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>488</v>
+        <v>590</v>
       </c>
     </row>
     <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>489</v>
+        <v>591</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>492</v>
+        <v>592</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>594</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>493</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>494</v>
+        <v>596</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>495</v>
+        <v>597</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>497</v>
+        <v>598</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>498</v>
+        <v>600</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>499</v>
+        <v>601</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>500</v>
+        <v>602</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>501</v>
+      <c r="A29" s="4" t="s">
+        <v>603</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>503</v>
+        <v>604</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="5" t="s">
-        <v>504</v>
+      <c r="A30" s="4" t="s">
+        <v>606</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>505</v>
+        <v>607</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>506</v>
+        <v>608</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>507</v>
+        <v>609</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>508</v>
+        <v>610</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>509</v>
+        <v>611</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>510</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>511</v>
+        <v>613</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>512</v>
+        <v>614</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>513</v>
+        <v>615</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>514</v>
+        <v>616</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>515</v>
+        <v>617</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>516</v>
+        <v>618</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>518</v>
+        <v>619</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>620</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>444</v>
+        <v>546</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>519</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>520</v>
+        <v>622</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>521</v>
+        <v>623</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>522</v>
+        <v>624</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>523</v>
+        <v>625</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>524</v>
+        <v>626</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>525</v>
+      <c r="A35" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>527</v>
+        <v>628</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>629</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>528</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" ht="31.5" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>529</v>
+      <c r="A36" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>530</v>
+        <v>632</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>531</v>
+        <v>633</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>533</v>
+        <v>634</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>534</v>
+        <v>636</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>535</v>
+        <v>637</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>536</v>
+        <v>638</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>537</v>
+        <v>639</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:7">
-      <c r="A38" s="5" t="s">
-        <v>538</v>
+      <c r="A38" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>462</v>
+        <v>564</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>540</v>
+        <v>641</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>642</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>541</v>
+        <v>643</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>542</v>
+        <v>644</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>543</v>
+        <v>645</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>544</v>
+        <v>646</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>545</v>
+        <v>647</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>546</v>
+        <v>648</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:6">
-      <c r="A40" s="5" t="s">
-        <v>547</v>
+      <c r="A40" s="4" t="s">
+        <v>649</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>549</v>
+        <v>650</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>651</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>550</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -5114,366 +6398,1058 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.7666666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.325" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.9416666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.3583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="29.225" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="14.225" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.325" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.4" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.9416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.3583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.225" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>555</v>
+      <c r="A2" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>551</v>
+      <c r="A3" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>562</v>
+      <c r="A4" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="5" ht="47.25" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>567</v>
+      <c r="A5" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="9" ht="31.5" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="10" ht="47.25" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="12" ht="31.5" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="16" ht="31.5" spans="1:6">
+      <c r="A16" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" ht="31.5" spans="1:6">
+      <c r="A20" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" ht="47.25" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="24" ht="47.25" spans="1:6">
+      <c r="A24" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="27" ht="31.5" spans="1:8">
+      <c r="A27" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="29" ht="31.5" spans="1:6">
+      <c r="A29" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="30" ht="31.5" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="31" ht="31.5" spans="1:6">
+      <c r="A31" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="32" ht="31.5" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="33" ht="31.5" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="39" ht="31.5" spans="1:6">
+      <c r="A39" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1" spans="1:6">
+      <c r="A42" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="43" ht="31.5" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="46" ht="31.5" spans="1:6">
+      <c r="A46" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="47" ht="31.5" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>837</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="12.425" customWidth="1"/>
+    <col min="2" max="2" width="18.7" customWidth="1"/>
+    <col min="3" max="3" width="25.425" customWidth="1"/>
+    <col min="4" max="4" width="16.55" customWidth="1"/>
+    <col min="5" max="5" width="29.7333333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.9" customWidth="1"/>
+    <col min="7" max="7" width="16.95" customWidth="1"/>
+    <col min="8" max="8" width="14.8416666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C3" t="s">
+        <v>845</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="F3" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>847</v>
+      </c>
+      <c r="B4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C4" t="s">
+        <v>849</v>
+      </c>
+      <c r="E4" t="s">
+        <v>850</v>
+      </c>
+      <c r="G4" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C5" t="s">
+        <v>854</v>
+      </c>
+      <c r="E5" t="s">
+        <v>855</v>
+      </c>
+      <c r="G5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="7" ht="31.5" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="9" ht="31.5" spans="1:5">
+        <v>857</v>
+      </c>
+      <c r="B6" t="s">
+        <v>858</v>
+      </c>
+      <c r="D6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E6" t="s">
+        <v>860</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B7" t="s">
+        <v>858</v>
+      </c>
+      <c r="D7" t="s">
+        <v>863</v>
+      </c>
+      <c r="F7" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B8" t="s">
+        <v>865</v>
+      </c>
+      <c r="D8" t="s">
+        <v>866</v>
+      </c>
+      <c r="E8" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="9" ht="45" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="10" ht="47.25" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="12" ht="31.5" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="16" ht="31.5" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>615</v>
+        <v>868</v>
+      </c>
+      <c r="B9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D9" t="s">
+        <v>870</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="10" ht="45" spans="1:8">
+      <c r="A10" t="s">
+        <v>873</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="C10" t="s">
+        <v>875</v>
+      </c>
+      <c r="H10" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="11" ht="45" spans="1:6">
+      <c r="A11" t="s">
+        <v>877</v>
+      </c>
+      <c r="B11" t="s">
+        <v>878</v>
+      </c>
+      <c r="D11" t="s">
+        <v>879</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="1:6">
+      <c r="A12" t="s">
+        <v>881</v>
+      </c>
+      <c r="B12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D12" t="s">
+        <v>883</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="F12" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:5">
+      <c r="A13" t="s">
+        <v>886</v>
+      </c>
+      <c r="B13" t="s">
+        <v>887</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:6">
+      <c r="A14" t="s">
+        <v>890</v>
+      </c>
+      <c r="B14" t="s">
+        <v>891</v>
+      </c>
+      <c r="C14" t="s">
+        <v>892</v>
+      </c>
+      <c r="D14" t="s">
+        <v>893</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:6">
+      <c r="A15" t="s">
+        <v>895</v>
+      </c>
+      <c r="B15" t="s">
+        <v>896</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="E15" t="s">
+        <v>898</v>
+      </c>
+      <c r="F15" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="16" ht="30" spans="1:5">
+      <c r="A16" t="s">
+        <v>899</v>
+      </c>
+      <c r="B16" t="s">
+        <v>900</v>
+      </c>
+      <c r="D16" t="s">
+        <v>901</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>638</v>
+      <c r="A17" t="s">
+        <v>903</v>
+      </c>
+      <c r="B17" t="s">
+        <v>904</v>
+      </c>
+      <c r="C17" t="s">
+        <v>905</v>
+      </c>
+      <c r="D17" t="s">
+        <v>899</v>
+      </c>
+      <c r="E17" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>907</v>
+      </c>
+      <c r="B18" t="s">
+        <v>908</v>
+      </c>
+      <c r="D18" t="s">
+        <v>909</v>
+      </c>
+      <c r="E18" t="s">
+        <v>910</v>
+      </c>
+      <c r="H18" t="s">
+        <v>911</v>
       </c>
     </row>
   </sheetData>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="5"/>
+    <workbookView windowWidth="27870" windowHeight="12570" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="5" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="Section03" sheetId="3" r:id="rId4"/>
     <sheet name="Section04" sheetId="4" r:id="rId5"/>
     <sheet name="Section05" sheetId="6" r:id="rId6"/>
+    <sheet name="Section06" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="998">
   <si>
     <t>GRE单词地基词全集精讲</t>
   </si>
@@ -2895,6 +2896,276 @@
   </si>
   <si>
     <t>ingenious a.灵巧的</t>
+  </si>
+  <si>
+    <t>disregard</t>
+  </si>
+  <si>
+    <t>vt.忽视，置之不理</t>
+  </si>
+  <si>
+    <t>dismiss 忽视</t>
+  </si>
+  <si>
+    <t>efficacious</t>
+  </si>
+  <si>
+    <t>a.有效的</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>efficacy n.功效</t>
+  </si>
+  <si>
+    <t>enigmatic</t>
+  </si>
+  <si>
+    <t>a.迷一样的</t>
+  </si>
+  <si>
+    <t>enigma n.谜题</t>
+  </si>
+  <si>
+    <t>mysterious mystery</t>
+  </si>
+  <si>
+    <t>exotic</t>
+  </si>
+  <si>
+    <t>a.外国的，奇异的</t>
+  </si>
+  <si>
+    <t>exotic flowers</t>
+  </si>
+  <si>
+    <t>ex = 外</t>
+  </si>
+  <si>
+    <t>forbear</t>
+  </si>
+  <si>
+    <t>v.忍住不做</t>
+  </si>
+  <si>
+    <t>forbear to do / from doing</t>
+  </si>
+  <si>
+    <t>forbearance n.宽容</t>
+  </si>
+  <si>
+    <t>foresee</t>
+  </si>
+  <si>
+    <t>vt.预知</t>
+  </si>
+  <si>
+    <t>foreseeable</t>
+  </si>
+  <si>
+    <t>prescient a.
+prophetic a.</t>
+  </si>
+  <si>
+    <t>hazardous</t>
+  </si>
+  <si>
+    <t>a.危险的</t>
+  </si>
+  <si>
+    <t>haphazard a.偶然的</t>
+  </si>
+  <si>
+    <t>impetuous</t>
+  </si>
+  <si>
+    <t>a.冲动的</t>
+  </si>
+  <si>
+    <t>pet = compete</t>
+  </si>
+  <si>
+    <t>impetus n.</t>
+  </si>
+  <si>
+    <t>indigenous</t>
+  </si>
+  <si>
+    <t>a.本土的</t>
+  </si>
+  <si>
+    <t>indigenous population</t>
+  </si>
+  <si>
+    <t>nonindigenous</t>
+  </si>
+  <si>
+    <t>native</t>
+  </si>
+  <si>
+    <t>disingenuous a.不老实的</t>
+  </si>
+  <si>
+    <t>inherent</t>
+  </si>
+  <si>
+    <t>a.内在的，固有的</t>
+  </si>
+  <si>
+    <t>her = adhere</t>
+  </si>
+  <si>
+    <t>inverse</t>
+  </si>
+  <si>
+    <t>a.相反的
+n.倒置</t>
+  </si>
+  <si>
+    <t>the inverse of the logic</t>
+  </si>
+  <si>
+    <t>invert v.颠倒
+inversion</t>
+  </si>
+  <si>
+    <t>jettison</t>
+  </si>
+  <si>
+    <t>vt.丢弃，拒绝接受</t>
+  </si>
+  <si>
+    <t>jettison the plan</t>
+  </si>
+  <si>
+    <t>jet = 扔</t>
+  </si>
+  <si>
+    <t>momentous</t>
+  </si>
+  <si>
+    <t>a.重大的</t>
+  </si>
+  <si>
+    <t>the momentous decision</t>
+  </si>
+  <si>
+    <t>moment</t>
+  </si>
+  <si>
+    <t>momentary a.短暂的</t>
+  </si>
+  <si>
+    <t>consequential
+significant
+eventful</t>
+  </si>
+  <si>
+    <t>myrid</t>
+  </si>
+  <si>
+    <t>a.无数的</t>
+  </si>
+  <si>
+    <t>a myrid of problem</t>
+  </si>
+  <si>
+    <t>orthodoxy</t>
+  </si>
+  <si>
+    <t>n.正统</t>
+  </si>
+  <si>
+    <t>the new orthodoxy in field</t>
+  </si>
+  <si>
+    <t>orthodox a.正统的
+unorthodox</t>
+  </si>
+  <si>
+    <t>precarious</t>
+  </si>
+  <si>
+    <t>pre = pray</t>
+  </si>
+  <si>
+    <t>reactionary</t>
+  </si>
+  <si>
+    <t>a.保守的，反动的</t>
+  </si>
+  <si>
+    <t>reaction</t>
+  </si>
+  <si>
+    <t>subversive</t>
+  </si>
+  <si>
+    <t>a.颠覆性的
+n.颠覆分子</t>
+  </si>
+  <si>
+    <t>sub = 下
+vert = 转</t>
+  </si>
+  <si>
+    <t>subvert vt.颠覆</t>
+  </si>
+  <si>
+    <t>surrender</t>
+  </si>
+  <si>
+    <t>v.投向，放弃，交出
+n.投向，放弃，交出</t>
+  </si>
+  <si>
+    <t>surrender all rights to my property
+放弃所有财产的权利</t>
+  </si>
+  <si>
+    <t>trifling</t>
+  </si>
+  <si>
+    <t>a.微不足道的</t>
+  </si>
+  <si>
+    <t>trifle n.琐事</t>
+  </si>
+  <si>
+    <t>trivial</t>
+  </si>
+  <si>
+    <t>a.琐碎的</t>
+  </si>
+  <si>
+    <t>trifle</t>
+  </si>
+  <si>
+    <t>untenable</t>
+  </si>
+  <si>
+    <t>a.站不住脚的</t>
+  </si>
+  <si>
+    <t>an untenable argument</t>
+  </si>
+  <si>
+    <t>tenable a.站得住脚的</t>
+  </si>
+  <si>
+    <t>unwarranted
+groundless
+baseless</t>
+  </si>
+  <si>
+    <t>vulnerable</t>
+  </si>
+  <si>
+    <t>a.易受影响的，脆弱的</t>
+  </si>
+  <si>
+    <t>be vulnerable to covid</t>
   </si>
 </sst>
 </file>
@@ -2903,9 +3174,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2931,6 +3202,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -2947,70 +3240,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3031,7 +3265,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3046,7 +3302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3054,7 +3310,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3082,79 +3353,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3172,13 +3407,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3196,55 +3509,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3256,13 +3527,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3273,6 +3544,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3296,6 +3582,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3332,44 +3638,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3378,118 +3649,118 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3498,22 +3769,22 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3523,7 +3794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3541,15 +3812,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="48">
       <alignment vertical="center"/>
@@ -3877,14 +4139,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="42.125" customWidth="1"/>
-    <col min="2" max="6" width="47.125" style="8" customWidth="1"/>
+    <col min="2" max="6" width="47.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3892,15 +4154,15 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" ht="15" spans="1:2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3908,7 +4170,7 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3916,7 +4178,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3924,7 +4186,7 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3932,7 +4194,7 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3940,7 +4202,7 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3948,7 +4210,7 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3956,7 +4218,7 @@
       <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3964,7 +4226,7 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3972,7 +4234,7 @@
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3980,7 +4242,7 @@
       <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3988,7 +4250,7 @@
       <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3996,7 +4258,7 @@
       <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4004,7 +4266,7 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4012,7 +4274,7 @@
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4020,7 +4282,7 @@
       <c r="A18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4028,7 +4290,7 @@
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4036,7 +4298,7 @@
       <c r="A20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4044,7 +4306,7 @@
       <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4052,7 +4314,7 @@
       <c r="A22" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4060,7 +4322,7 @@
       <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4068,7 +4330,7 @@
       <c r="A24" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4076,7 +4338,7 @@
       <c r="A25" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4084,7 +4346,7 @@
       <c r="A26" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4092,7 +4354,7 @@
       <c r="A27" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4100,7 +4362,7 @@
       <c r="A28" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4108,7 +4370,7 @@
       <c r="A29" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4116,7 +4378,7 @@
       <c r="A30" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4124,7 +4386,7 @@
       <c r="A31" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4132,7 +4394,7 @@
       <c r="A32" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4140,7 +4402,7 @@
       <c r="A33" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4148,7 +4410,7 @@
       <c r="A34" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4156,7 +4418,7 @@
       <c r="A35" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4164,7 +4426,7 @@
       <c r="A36" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4172,7 +4434,7 @@
       <c r="A37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4180,7 +4442,7 @@
       <c r="A38" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4188,7 +4450,7 @@
       <c r="A39" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4196,7 +4458,7 @@
       <c r="A40" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4204,7 +4466,7 @@
       <c r="A41" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4212,7 +4474,7 @@
       <c r="A42" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4220,7 +4482,7 @@
       <c r="A43" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4228,7 +4490,7 @@
       <c r="A44" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="1" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4236,7 +4498,7 @@
       <c r="A45" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4244,7 +4506,7 @@
       <c r="A46" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4252,7 +4514,7 @@
       <c r="A47" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="1" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4260,7 +4522,7 @@
       <c r="A48" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4268,7 +4530,7 @@
       <c r="A49" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="1" t="s">
         <v>97</v>
       </c>
     </row>
@@ -4276,7 +4538,7 @@
       <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4284,7 +4546,7 @@
       <c r="A51" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5263,7 +5525,7 @@
       <c r="E2" t="s">
         <v>355</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5280,7 +5542,7 @@
       <c r="D3" t="s">
         <v>360</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="3" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5308,7 +5570,7 @@
       <c r="B5" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5316,13 +5578,13 @@
       <c r="A6" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C6" t="s">
         <v>371</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>372</v>
       </c>
     </row>
@@ -5330,7 +5592,7 @@
       <c r="A7" t="s">
         <v>373</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C7" t="s">
@@ -5350,7 +5612,7 @@
       <c r="B8" t="s">
         <v>379</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>380</v>
       </c>
     </row>
@@ -5426,7 +5688,7 @@
       <c r="C13" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="3" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5434,13 +5696,13 @@
       <c r="A14" t="s">
         <v>401</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>402</v>
       </c>
       <c r="C14" t="s">
         <v>403</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="3" t="s">
         <v>404</v>
       </c>
     </row>
@@ -5498,7 +5760,7 @@
       <c r="A19" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="3" t="s">
         <v>419</v>
       </c>
       <c r="C19" t="s">
@@ -5532,7 +5794,7 @@
       <c r="C21" t="s">
         <v>428</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="3" t="s">
         <v>429</v>
       </c>
     </row>
@@ -5543,7 +5805,7 @@
       <c r="B22" t="s">
         <v>431</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="3" t="s">
         <v>432</v>
       </c>
       <c r="F22" t="s">
@@ -5585,7 +5847,7 @@
       <c r="A25" t="s">
         <v>442</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>443</v>
       </c>
       <c r="C25" t="s">
@@ -5613,7 +5875,7 @@
       <c r="A27" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="3" t="s">
         <v>451</v>
       </c>
       <c r="C27" t="s">
@@ -5633,10 +5895,10 @@
       <c r="A28" t="s">
         <v>456</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="3" t="s">
         <v>458</v>
       </c>
     </row>
@@ -5644,7 +5906,7 @@
       <c r="A29" t="s">
         <v>459</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="3" t="s">
         <v>460</v>
       </c>
       <c r="E29" t="s">
@@ -5702,7 +5964,7 @@
       <c r="A34" t="s">
         <v>474</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="3" t="s">
         <v>475</v>
       </c>
     </row>
@@ -5730,7 +5992,7 @@
       <c r="B36" t="s">
         <v>482</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="3" t="s">
         <v>483</v>
       </c>
     </row>
@@ -5741,7 +6003,7 @@
       <c r="B37" t="s">
         <v>485</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="3" t="s">
         <v>486</v>
       </c>
     </row>
@@ -6766,7 +7028,7 @@
       <c r="B23" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>743</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -6786,7 +7048,7 @@
       <c r="D24" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>749</v>
       </c>
     </row>
@@ -6825,7 +7087,7 @@
       <c r="C27" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>759</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -6868,10 +7130,10 @@
       <c r="D29" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>771</v>
       </c>
     </row>
@@ -6879,7 +7141,7 @@
       <c r="A30" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>773</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -6896,7 +7158,7 @@
       <c r="D31" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>778</v>
       </c>
     </row>
@@ -6907,10 +7169,10 @@
       <c r="B32" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>782</v>
       </c>
     </row>
@@ -6918,7 +7180,7 @@
       <c r="A33" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>784</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -6996,7 +7258,7 @@
       <c r="A39" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>803</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -7047,7 +7309,7 @@
       <c r="D42" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>816</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -7064,7 +7326,7 @@
       <c r="D43" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>820</v>
       </c>
     </row>
@@ -7112,7 +7374,7 @@
       <c r="C46" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>833</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -7123,13 +7385,13 @@
       <c r="A47" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>837</v>
       </c>
     </row>
@@ -7142,17 +7404,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.425" customWidth="1"/>
     <col min="2" max="2" width="18.7" customWidth="1"/>
-    <col min="3" max="3" width="25.425" customWidth="1"/>
+    <col min="3" max="3" width="27.4" customWidth="1"/>
     <col min="4" max="4" width="16.55" customWidth="1"/>
     <col min="5" max="5" width="29.7333333333333" customWidth="1"/>
     <col min="6" max="6" width="18.9" customWidth="1"/>
     <col min="7" max="7" width="16.95" customWidth="1"/>
-    <col min="8" max="8" width="14.8416666666667" customWidth="1"/>
+    <col min="8" max="8" width="20.075" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
@@ -7452,6 +7714,385 @@
         <v>911</v>
       </c>
     </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>912</v>
+      </c>
+      <c r="B19" t="s">
+        <v>913</v>
+      </c>
+      <c r="F19" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>915</v>
+      </c>
+      <c r="B20" t="s">
+        <v>916</v>
+      </c>
+      <c r="D20" t="s">
+        <v>917</v>
+      </c>
+      <c r="E20" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>919</v>
+      </c>
+      <c r="B21" t="s">
+        <v>920</v>
+      </c>
+      <c r="E21" t="s">
+        <v>921</v>
+      </c>
+      <c r="F21" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>923</v>
+      </c>
+      <c r="B22" t="s">
+        <v>924</v>
+      </c>
+      <c r="C22" t="s">
+        <v>925</v>
+      </c>
+      <c r="D22" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>927</v>
+      </c>
+      <c r="B23" t="s">
+        <v>928</v>
+      </c>
+      <c r="C23" t="s">
+        <v>929</v>
+      </c>
+      <c r="E23" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:6">
+      <c r="A24" t="s">
+        <v>931</v>
+      </c>
+      <c r="B24" t="s">
+        <v>932</v>
+      </c>
+      <c r="E24" t="s">
+        <v>933</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>935</v>
+      </c>
+      <c r="B25" t="s">
+        <v>936</v>
+      </c>
+      <c r="H25" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>938</v>
+      </c>
+      <c r="B26" t="s">
+        <v>939</v>
+      </c>
+      <c r="D26" t="s">
+        <v>940</v>
+      </c>
+      <c r="E26" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>942</v>
+      </c>
+      <c r="B27" t="s">
+        <v>943</v>
+      </c>
+      <c r="C27" t="s">
+        <v>944</v>
+      </c>
+      <c r="D27" t="s">
+        <v>909</v>
+      </c>
+      <c r="E27" t="s">
+        <v>945</v>
+      </c>
+      <c r="F27" t="s">
+        <v>946</v>
+      </c>
+      <c r="G27" t="s">
+        <v>923</v>
+      </c>
+      <c r="H27" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>948</v>
+      </c>
+      <c r="B28" t="s">
+        <v>949</v>
+      </c>
+      <c r="D28" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:5">
+      <c r="A29" t="s">
+        <v>951</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="C29" t="s">
+        <v>953</v>
+      </c>
+      <c r="D29" t="s">
+        <v>841</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>955</v>
+      </c>
+      <c r="B30" t="s">
+        <v>956</v>
+      </c>
+      <c r="C30" t="s">
+        <v>957</v>
+      </c>
+      <c r="D30" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="31" ht="45" spans="1:6">
+      <c r="A31" t="s">
+        <v>959</v>
+      </c>
+      <c r="B31" t="s">
+        <v>960</v>
+      </c>
+      <c r="C31" t="s">
+        <v>961</v>
+      </c>
+      <c r="D31" t="s">
+        <v>962</v>
+      </c>
+      <c r="E31" t="s">
+        <v>963</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>965</v>
+      </c>
+      <c r="B32" t="s">
+        <v>966</v>
+      </c>
+      <c r="C32" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:5">
+      <c r="A33" t="s">
+        <v>968</v>
+      </c>
+      <c r="B33" t="s">
+        <v>969</v>
+      </c>
+      <c r="C33" t="s">
+        <v>970</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>972</v>
+      </c>
+      <c r="B34" t="s">
+        <v>936</v>
+      </c>
+      <c r="D34" t="s">
+        <v>973</v>
+      </c>
+      <c r="F34" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>974</v>
+      </c>
+      <c r="B35" t="s">
+        <v>975</v>
+      </c>
+      <c r="D35" t="s">
+        <v>976</v>
+      </c>
+      <c r="F35" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" ht="30" spans="1:6">
+      <c r="A36" t="s">
+        <v>977</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="E36" t="s">
+        <v>980</v>
+      </c>
+      <c r="F36" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:6">
+      <c r="A37" t="s">
+        <v>981</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="F37" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>984</v>
+      </c>
+      <c r="B38" t="s">
+        <v>985</v>
+      </c>
+      <c r="E38" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>987</v>
+      </c>
+      <c r="B39" t="s">
+        <v>988</v>
+      </c>
+      <c r="D39" t="s">
+        <v>989</v>
+      </c>
+      <c r="F39" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="40" ht="45" spans="1:6">
+      <c r="A40" t="s">
+        <v>990</v>
+      </c>
+      <c r="B40" t="s">
+        <v>991</v>
+      </c>
+      <c r="C40" t="s">
+        <v>992</v>
+      </c>
+      <c r="E40" t="s">
+        <v>993</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>995</v>
+      </c>
+      <c r="B41" t="s">
+        <v>996</v>
+      </c>
+      <c r="C41" t="s">
+        <v>997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="22.875" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="31.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="22.75" customWidth="1"/>
+    <col min="7" max="7" width="29.5" customWidth="1"/>
+    <col min="8" max="8" width="23.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,23 +4,24 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="6"/>
+    <workbookView windowWidth="27870" windowHeight="12570" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="5" r:id="rId1"/>
-    <sheet name="Section01" sheetId="1" r:id="rId2"/>
-    <sheet name="Section02" sheetId="2" r:id="rId3"/>
-    <sheet name="Section03" sheetId="3" r:id="rId4"/>
-    <sheet name="Section04" sheetId="4" r:id="rId5"/>
-    <sheet name="Section05" sheetId="6" r:id="rId6"/>
-    <sheet name="Section06" sheetId="7" r:id="rId7"/>
+    <sheet name="S01" sheetId="1" r:id="rId2"/>
+    <sheet name="S02" sheetId="2" r:id="rId3"/>
+    <sheet name="S03" sheetId="3" r:id="rId4"/>
+    <sheet name="S04" sheetId="4" r:id="rId5"/>
+    <sheet name="S05" sheetId="6" r:id="rId6"/>
+    <sheet name="S06" sheetId="7" r:id="rId7"/>
+    <sheet name="S07" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="1246">
   <si>
     <t>GRE单词地基词全集精讲</t>
   </si>
@@ -1611,7 +1612,7 @@
     <t>attract international censure</t>
   </si>
   <si>
-    <t>censurable</t>
+    <t>censurable a.该责备的</t>
   </si>
   <si>
     <t>censor n.审查员</t>
@@ -1761,10 +1762,11 @@
     <t>emulation</t>
   </si>
   <si>
-    <t>imitate</t>
-  </si>
-  <si>
-    <t>enumerate 列举</t>
+    <t>imitate v.模仿；仿效</t>
+  </si>
+  <si>
+    <t>enumerate 列举
+intimate a.亲密的</t>
   </si>
   <si>
     <t>explicate</t>
@@ -1821,8 +1823,13 @@
     <t>a.复杂的，精细的</t>
   </si>
   <si>
-    <t>extricate v.拜托
+    <t>sophisticated
+delicate
 convoluted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extricate v.摆脱
+</t>
   </si>
   <si>
     <t>labyrinth</t>
@@ -2676,6 +2683,9 @@
 adversary n.对手，敌手</t>
   </si>
   <si>
+    <t>hostile</t>
+  </si>
+  <si>
     <t>antagonistic</t>
   </si>
   <si>
@@ -2739,6 +2749,9 @@
   </si>
   <si>
     <t>strophe = storm</t>
+  </si>
+  <si>
+    <t>catastrophy n.</t>
   </si>
   <si>
     <t>chivalrous</t>
@@ -2842,6 +2855,7 @@
   </si>
   <si>
     <t>toxic
+malignant
 poisonous</t>
   </si>
   <si>
@@ -2871,13 +2885,17 @@
 discernment n.洞察力</t>
   </si>
   <si>
+    <t>concern vt.影响；涉及</t>
+  </si>
+  <si>
     <t>discretion</t>
   </si>
   <si>
     <t>n.审慎，酌情决定权</t>
   </si>
   <si>
-    <t>at the discretion of 任你处置</t>
+    <t>at the discretion of 任你处置
+at your disposal</t>
   </si>
   <si>
     <t>discretionary a.酌情决定的</t>
@@ -2986,7 +3004,7 @@
     <t>pet = compete</t>
   </si>
   <si>
-    <t>impetus n.</t>
+    <t>impetus n.动力</t>
   </si>
   <si>
     <t>indigenous</t>
@@ -3040,6 +3058,9 @@
   </si>
   <si>
     <t>jet = 扔</t>
+  </si>
+  <si>
+    <t>jet 喷气飞机</t>
   </si>
   <si>
     <t>momentous</t>
@@ -3062,13 +3083,18 @@
 eventful</t>
   </si>
   <si>
-    <t>myrid</t>
+    <t>memorial n.纪念碑 a.纪念的
+memorandam = memo = 备忘录
+momentum n.动力</t>
+  </si>
+  <si>
+    <t>myriad</t>
   </si>
   <si>
     <t>a.无数的</t>
   </si>
   <si>
-    <t>a myrid of problem</t>
+    <t>a myriad of problem</t>
   </si>
   <si>
     <t>orthodoxy</t>
@@ -3156,7 +3182,8 @@
   <si>
     <t>unwarranted
 groundless
-baseless</t>
+baseless
+feeble</t>
   </si>
   <si>
     <t>vulnerable</t>
@@ -3165,7 +3192,810 @@
     <t>a.易受影响的，脆弱的</t>
   </si>
   <si>
-    <t>be vulnerable to covid</t>
+    <t>be vulnerable to covid-19</t>
+  </si>
+  <si>
+    <t>accentuate</t>
+  </si>
+  <si>
+    <t>vt. 强调</t>
+  </si>
+  <si>
+    <t>accent</t>
+  </si>
+  <si>
+    <t>emphasize
+highlight
+underscore</t>
+  </si>
+  <si>
+    <t>acrimony</t>
+  </si>
+  <si>
+    <t>n.辛辣，尖刻</t>
+  </si>
+  <si>
+    <t>acri = acid</t>
+  </si>
+  <si>
+    <t>acrimonious</t>
+  </si>
+  <si>
+    <t>bitterness</t>
+  </si>
+  <si>
+    <t>adversity</t>
+  </si>
+  <si>
+    <t>n.逆境，困境</t>
+  </si>
+  <si>
+    <t>adverse</t>
+  </si>
+  <si>
+    <t>misfortune</t>
+  </si>
+  <si>
+    <t>anachronistic</t>
+  </si>
+  <si>
+    <t>a.过时的，时代错误的</t>
+  </si>
+  <si>
+    <t>ana = 否定
+chrono = 时间</t>
+  </si>
+  <si>
+    <t>atypical</t>
+  </si>
+  <si>
+    <t>a.非典型的</t>
+  </si>
+  <si>
+    <t>a + typical</t>
+  </si>
+  <si>
+    <t>archetypical a.典型的</t>
+  </si>
+  <si>
+    <t>belie</t>
+  </si>
+  <si>
+    <t>vt.掩饰，证明...是假的</t>
+  </si>
+  <si>
+    <t>lie</t>
+  </si>
+  <si>
+    <t>betray</t>
+  </si>
+  <si>
+    <t>vt.背叛，流露出</t>
+  </si>
+  <si>
+    <t>his face betrayed nothing</t>
+  </si>
+  <si>
+    <t>coagulate</t>
+  </si>
+  <si>
+    <t>vi.凝固(血液)</t>
+  </si>
+  <si>
+    <t>coagulation n.凝血</t>
+  </si>
+  <si>
+    <t>commensurate</t>
+  </si>
+  <si>
+    <t>a.相称的，相当的</t>
+  </si>
+  <si>
+    <t>A is commensurate with B</t>
+  </si>
+  <si>
+    <t>mens = measure</t>
+  </si>
+  <si>
+    <t>incommensurate a.不相称的
+commensurable a.可比较的</t>
+  </si>
+  <si>
+    <t>comity</t>
+  </si>
+  <si>
+    <t>n.礼仪，礼让</t>
+  </si>
+  <si>
+    <t>courtesy
+civility</t>
+  </si>
+  <si>
+    <t>condemn</t>
+  </si>
+  <si>
+    <t>be condemned to life imprisonment</t>
+  </si>
+  <si>
+    <t>condemnation</t>
+  </si>
+  <si>
+    <t>censure
+decry</t>
+  </si>
+  <si>
+    <t>conformity</t>
+  </si>
+  <si>
+    <t>n.遵守，随大流</t>
+  </si>
+  <si>
+    <t>in conformity with 依照</t>
+  </si>
+  <si>
+    <t>conform+to vi
+nonconformist n.离经叛道者</t>
+  </si>
+  <si>
+    <t>comity n.礼仪</t>
+  </si>
+  <si>
+    <t>consummate</t>
+  </si>
+  <si>
+    <t>a.完美的，技艺高超的
+vt.性交，使圆满</t>
+  </si>
+  <si>
+    <t>consummate skill/performer</t>
+  </si>
+  <si>
+    <t>sum = 总和，圆满</t>
+  </si>
+  <si>
+    <t>devolve</t>
+  </si>
+  <si>
+    <t>v.权利下放，演变(退化)</t>
+  </si>
+  <si>
+    <t>devolve power to regional government</t>
+  </si>
+  <si>
+    <t>de = 下</t>
+  </si>
+  <si>
+    <t>evolve</t>
+  </si>
+  <si>
+    <t>discriminate</t>
+  </si>
+  <si>
+    <t>vt.区别对待，歧视</t>
+  </si>
+  <si>
+    <t>discriminate in favor of/against</t>
+  </si>
+  <si>
+    <t>discrimination
+discriminatory
+indiscriminate a.随意的</t>
+  </si>
+  <si>
+    <t>dissent</t>
+  </si>
+  <si>
+    <t>vi&amp;n.异议</t>
+  </si>
+  <si>
+    <t>10 member dissented</t>
+  </si>
+  <si>
+    <t>dissenter</t>
+  </si>
+  <si>
+    <t>drawback</t>
+  </si>
+  <si>
+    <t>n.缺点，障碍</t>
+  </si>
+  <si>
+    <t>draw = 拉</t>
+  </si>
+  <si>
+    <t>flaw
+defect
+deficiency
+disadvantage
+shortcoming</t>
+  </si>
+  <si>
+    <t>dwindle</t>
+  </si>
+  <si>
+    <t>vi.缩小，减少</t>
+  </si>
+  <si>
+    <t>dwindle from ... to ...</t>
+  </si>
+  <si>
+    <t>dwindling a.减少的</t>
+  </si>
+  <si>
+    <t>decrease</t>
+  </si>
+  <si>
+    <t>endorse</t>
+  </si>
+  <si>
+    <t>vt.背书，公开支持</t>
+  </si>
+  <si>
+    <t>endorsement n.代言，赞同</t>
+  </si>
+  <si>
+    <t>evade</t>
+  </si>
+  <si>
+    <t>vt.逃避</t>
+  </si>
+  <si>
+    <t>evade a topic</t>
+  </si>
+  <si>
+    <t>evasive a.回避提问的，推诿的</t>
+  </si>
+  <si>
+    <t>invade
+erode</t>
+  </si>
+  <si>
+    <t>excessive</t>
+  </si>
+  <si>
+    <t>a.过多的</t>
+  </si>
+  <si>
+    <t>excess adj&amp;n.过量</t>
+  </si>
+  <si>
+    <t>expel</t>
+  </si>
+  <si>
+    <t>vt.驱逐，开除</t>
+  </si>
+  <si>
+    <t>extrapolate</t>
+  </si>
+  <si>
+    <t>vt.推断</t>
+  </si>
+  <si>
+    <t>extrapolate from known facts</t>
+  </si>
+  <si>
+    <t>extrapolation n.</t>
+  </si>
+  <si>
+    <t>flamboyant</t>
+  </si>
+  <si>
+    <t>a.耀眼的，派头十足的</t>
+  </si>
+  <si>
+    <t>flam = flame</t>
+  </si>
+  <si>
+    <t>flamboyance</t>
+  </si>
+  <si>
+    <t>improvise</t>
+  </si>
+  <si>
+    <t>v.即兴创作</t>
+  </si>
+  <si>
+    <t>im = 否定
+provise = provide</t>
+  </si>
+  <si>
+    <t>innocuous</t>
+  </si>
+  <si>
+    <t>a.无害的</t>
+  </si>
+  <si>
+    <t>nocuous a.有害的</t>
+  </si>
+  <si>
+    <t>noxious
+deleterious</t>
+  </si>
+  <si>
+    <t>intrinsic</t>
+  </si>
+  <si>
+    <t>the intrinsic value of education</t>
+  </si>
+  <si>
+    <t>instinct 直觉</t>
+  </si>
+  <si>
+    <t>insurmountable</t>
+  </si>
+  <si>
+    <t>a.不能克服的</t>
+  </si>
+  <si>
+    <t>surmount 克服</t>
+  </si>
+  <si>
+    <t>unconquerable
+unbeatable</t>
+  </si>
+  <si>
+    <t>lucrative</t>
+  </si>
+  <si>
+    <t>a.活力丰厚的</t>
+  </si>
+  <si>
+    <t>lucra = lucre</t>
+  </si>
+  <si>
+    <t>profitable</t>
+  </si>
+  <si>
+    <t>mask</t>
+  </si>
+  <si>
+    <t>n.面具
+vt.掩饰，遮掩</t>
+  </si>
+  <si>
+    <t>mitigate</t>
+  </si>
+  <si>
+    <t>vt.缓解</t>
+  </si>
+  <si>
+    <t>miti = mild = 缓和</t>
+  </si>
+  <si>
+    <t>mitigation n.</t>
+  </si>
+  <si>
+    <t>mediate vt.调节 med = middle
+meditate vt.冥想</t>
+  </si>
+  <si>
+    <t>mordant</t>
+  </si>
+  <si>
+    <t>a.尖酸的，刻薄的</t>
+  </si>
+  <si>
+    <t>mordancy n.尖酸</t>
+  </si>
+  <si>
+    <t>nullify</t>
+  </si>
+  <si>
+    <t>vt.使...无效</t>
+  </si>
+  <si>
+    <r>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF010102"/>
+        <rFont val="oalecd9"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF010102"/>
+        <rFont val="oalecd9"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>void</t>
+    </r>
+  </si>
+  <si>
+    <t>null a.零值的；等于零的</t>
+  </si>
+  <si>
+    <t>invalidate
+negate</t>
+  </si>
+  <si>
+    <t>obviate</t>
+  </si>
+  <si>
+    <t>vt.消除，使...不必要</t>
+  </si>
+  <si>
+    <t>oust</t>
+  </si>
+  <si>
+    <t>vt.驱逐</t>
+  </si>
+  <si>
+    <t>out</t>
+  </si>
+  <si>
+    <t>persistent</t>
+  </si>
+  <si>
+    <t>a.持续存在的，执着的</t>
+  </si>
+  <si>
+    <t>persist</t>
+  </si>
+  <si>
+    <t>insistent
+preserving</t>
+  </si>
+  <si>
+    <t>quirky</t>
+  </si>
+  <si>
+    <t>a.古怪的</t>
+  </si>
+  <si>
+    <t>quirk n.怪癖</t>
+  </si>
+  <si>
+    <t>bizarre
+weird</t>
+  </si>
+  <si>
+    <t>resemble</t>
+  </si>
+  <si>
+    <t>vt.类似</t>
+  </si>
+  <si>
+    <t>resemblance n</t>
+  </si>
+  <si>
+    <t>assemble vt.集合
+dissemble vt.掩饰</t>
+  </si>
+  <si>
+    <t>sanction</t>
+  </si>
+  <si>
+    <t>vt.批准，认可
+n.制裁</t>
+  </si>
+  <si>
+    <t>impose sanctions against</t>
+  </si>
+  <si>
+    <t>warrant</t>
+  </si>
+  <si>
+    <t>scant</t>
+  </si>
+  <si>
+    <t>a.少量的，不足的</t>
+  </si>
+  <si>
+    <t>pay scant attention to</t>
+  </si>
+  <si>
+    <t>scanty</t>
+  </si>
+  <si>
+    <t>steadfast</t>
+  </si>
+  <si>
+    <t>a.坚定的</t>
+  </si>
+  <si>
+    <t>steady</t>
+  </si>
+  <si>
+    <t>undue</t>
+  </si>
+  <si>
+    <t>a.过分的，未到期的</t>
+  </si>
+  <si>
+    <t>due a.到期的，恰当的</t>
+  </si>
+  <si>
+    <t>abbreviate</t>
+  </si>
+  <si>
+    <t>vt.缩写</t>
+  </si>
+  <si>
+    <t>abbreviate ... to ...</t>
+  </si>
+  <si>
+    <t>brev = brief</t>
+  </si>
+  <si>
+    <t>abbreviated a.简短的
+abbreviation n.缩写词</t>
+  </si>
+  <si>
+    <t>amplify</t>
+  </si>
+  <si>
+    <t>vt.扩大，增强</t>
+  </si>
+  <si>
+    <t>amplify a sound</t>
+  </si>
+  <si>
+    <t>ample a.丰富的</t>
+  </si>
+  <si>
+    <t>intensify
+augment</t>
+  </si>
+  <si>
+    <t>bolster</t>
+  </si>
+  <si>
+    <t>n.长枕头
+vt.增强，巩固</t>
+  </si>
+  <si>
+    <t>bolster economy/confidence</t>
+  </si>
+  <si>
+    <t>chiche</t>
+  </si>
+  <si>
+    <t>n.陈词滥调</t>
+  </si>
+  <si>
+    <t>condescending</t>
+  </si>
+  <si>
+    <t>a.屈尊的，居高临下的</t>
+  </si>
+  <si>
+    <t>con = 强调 descend = 下降</t>
+  </si>
+  <si>
+    <t>condescend to do /to sb 摆架子</t>
+  </si>
+  <si>
+    <t>patronizing</t>
+  </si>
+  <si>
+    <t>conjecture</t>
+  </si>
+  <si>
+    <t>vi&amp;vt&amp;n.推测</t>
+  </si>
+  <si>
+    <t>con = 强调 ject = jettison = 扔</t>
+  </si>
+  <si>
+    <t>empirical/empiricism</t>
+  </si>
+  <si>
+    <t>connoisseur</t>
+  </si>
+  <si>
+    <t>n.鉴赏家，行家</t>
+  </si>
+  <si>
+    <t>noiss = know</t>
+  </si>
+  <si>
+    <t>Renaissance 文艺复兴</t>
+  </si>
+  <si>
+    <t>conventional</t>
+  </si>
+  <si>
+    <t>a.传统的</t>
+  </si>
+  <si>
+    <t>convention n.管理，大会，集会</t>
+  </si>
+  <si>
+    <t>orthodox</t>
+  </si>
+  <si>
+    <t>corroborate</t>
+  </si>
+  <si>
+    <t>vt.证实</t>
+  </si>
+  <si>
+    <t>corroborate the story</t>
+  </si>
+  <si>
+    <t>rob = robust</t>
+  </si>
+  <si>
+    <t>corroboration</t>
+  </si>
+  <si>
+    <t>establish</t>
+  </si>
+  <si>
+    <t>collaborate</t>
+  </si>
+  <si>
+    <t>dampen</t>
+  </si>
+  <si>
+    <t>vt.抑制，减少</t>
+  </si>
+  <si>
+    <t>dampen enthusiasm 泼冷水</t>
+  </si>
+  <si>
+    <t>damp 潮湿的</t>
+  </si>
+  <si>
+    <t>restrain</t>
+  </si>
+  <si>
+    <t>discreet</t>
+  </si>
+  <si>
+    <t>a.小心的，谨慎的</t>
+  </si>
+  <si>
+    <t>be discreet about sth</t>
+  </si>
+  <si>
+    <t>discreetly</t>
+  </si>
+  <si>
+    <t>eclipse</t>
+  </si>
+  <si>
+    <t>n.日食月食
+vt.使黯然失色</t>
+  </si>
+  <si>
+    <t>ec = ex = 外
+lipse = leave</t>
+  </si>
+  <si>
+    <t>ellipse 椭圆</t>
+  </si>
+  <si>
+    <t>edify</t>
+  </si>
+  <si>
+    <t>vt.启发</t>
+  </si>
+  <si>
+    <t>edifying</t>
+  </si>
+  <si>
+    <t>illuminate
+enlighten</t>
+  </si>
+  <si>
+    <t>erudite</t>
+  </si>
+  <si>
+    <t>a.博学的</t>
+  </si>
+  <si>
+    <t>erudition</t>
+  </si>
+  <si>
+    <t>learned</t>
+  </si>
+  <si>
+    <t>exacting</t>
+  </si>
+  <si>
+    <t>a.费劲的，严格的</t>
+  </si>
+  <si>
+    <t>an exacting task</t>
+  </si>
+  <si>
+    <t>laborious a.费劲的
+demanding</t>
+  </si>
+  <si>
+    <t>felicitous</t>
+  </si>
+  <si>
+    <t>a.幸福的，恰如其分的</t>
+  </si>
+  <si>
+    <t>a felicitous remark</t>
+  </si>
+  <si>
+    <t>felicity
+infelicitous</t>
+  </si>
+  <si>
+    <t>fungible</t>
+  </si>
+  <si>
+    <t>a.可替换的</t>
+  </si>
+  <si>
+    <t>non-fungible token</t>
+  </si>
+  <si>
+    <t>fungi = function</t>
+  </si>
+  <si>
+    <t>exchangeable
+interchangeable
+substitutable</t>
+  </si>
+  <si>
+    <t>fungus 真菌</t>
+  </si>
+  <si>
+    <t>judicious</t>
+  </si>
+  <si>
+    <t>a.明智的，判断正确的</t>
+  </si>
+  <si>
+    <t>judicious decision</t>
+  </si>
+  <si>
+    <t>judge</t>
+  </si>
+  <si>
+    <t>discreet
+intelligent</t>
+  </si>
+  <si>
+    <t>marvel</t>
+  </si>
+  <si>
+    <t>n.奇迹
+vi.大为赞叹</t>
+  </si>
+  <si>
+    <t>marvel at sth</t>
+  </si>
+  <si>
+    <t>marvelous</t>
+  </si>
+  <si>
+    <t>meticulous</t>
+  </si>
+  <si>
+    <t>a.一丝不苟的，关注细节的</t>
   </si>
 </sst>
 </file>
@@ -3173,12 +4003,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3202,23 +4032,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3232,9 +4055,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3248,11 +4101,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3265,29 +4147,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3302,40 +4162,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF010102"/>
+      <name val="oalecd9"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -3353,7 +4189,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3365,43 +4261,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3419,121 +4363,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3572,41 +4408,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -3639,8 +4440,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3649,142 +4485,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3794,14 +4630,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4162,7 +5004,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4604,7 +5446,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -4615,10 +5457,10 @@
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -4629,13 +5471,13 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -4643,7 +5485,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -4660,7 +5502,7 @@
       <c r="A6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -4671,7 +5513,7 @@
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4683,12 +5525,12 @@
       <c r="E7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4711,7 +5553,7 @@
       <c r="C9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4725,10 +5567,10 @@
       <c r="C10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4739,7 +5581,7 @@
       <c r="B11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -4770,7 +5612,7 @@
       <c r="C13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>158</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -4787,7 +5629,7 @@
       <c r="C14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -4795,16 +5637,16 @@
       </c>
     </row>
     <row r="15" ht="47.25" spans="1:6">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>168</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -4812,7 +5654,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>170</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -4843,13 +5685,13 @@
       </c>
     </row>
     <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="6" t="s">
         <v>179</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>181</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -4857,13 +5699,13 @@
       </c>
     </row>
     <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>185</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -4888,10 +5730,10 @@
       <c r="C21" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>193</v>
       </c>
     </row>
@@ -4919,15 +5761,15 @@
       <c r="B23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>203</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -4958,7 +5800,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -4972,7 +5814,7 @@
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>215</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -4981,15 +5823,15 @@
       <c r="C27" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="7" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -4998,7 +5840,7 @@
       <c r="D28" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="7" t="s">
         <v>223</v>
       </c>
     </row>
@@ -5009,7 +5851,7 @@
       <c r="B29" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>226</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -5017,7 +5859,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>228</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -5048,13 +5890,13 @@
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>236</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>238</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -5094,12 +5936,12 @@
       <c r="B34" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>249</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -5108,12 +5950,12 @@
       <c r="C35" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>253</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -5142,15 +5984,15 @@
       <c r="D37" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="7" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>264</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -5161,7 +6003,7 @@
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>267</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -5173,7 +6015,7 @@
       <c r="D39" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="7" t="s">
         <v>271</v>
       </c>
     </row>
@@ -5187,10 +6029,10 @@
       <c r="E40" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="7" t="s">
         <v>276</v>
       </c>
     </row>
@@ -5204,7 +6046,7 @@
       <c r="E41" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="7" t="s">
         <v>280</v>
       </c>
     </row>
@@ -5229,13 +6071,13 @@
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>287</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="7" t="s">
         <v>289</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -5249,21 +6091,21 @@
       <c r="B44" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="7" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="6" t="s">
         <v>295</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="7" t="s">
         <v>297</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -5274,7 +6116,7 @@
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="6" t="s">
         <v>299</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -5297,7 +6139,7 @@
       <c r="B47" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="7" t="s">
         <v>306</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -5305,7 +6147,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="6" t="s">
         <v>307</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -5316,7 +6158,7 @@
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="6" t="s">
         <v>310</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -5333,10 +6175,10 @@
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="7" t="s">
         <v>316</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -5347,7 +6189,7 @@
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
         <v>319</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -5356,12 +6198,12 @@
       <c r="C51" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="7" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="6" t="s">
         <v>323</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -5370,7 +6212,7 @@
       <c r="C52" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="7" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5395,7 +6237,7 @@
       <c r="B54" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="7" t="s">
         <v>333</v>
       </c>
       <c r="H54" s="1" t="s">
@@ -5426,7 +6268,7 @@
       <c r="E56" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="7" t="s">
         <v>342</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -5434,13 +6276,13 @@
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="6" t="s">
         <v>344</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="7" t="s">
         <v>346</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -5451,13 +6293,13 @@
       <c r="A58" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="7" t="s">
         <v>351</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -5513,7 +6355,7 @@
       </c>
     </row>
     <row r="2" ht="30" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B2" t="s">
@@ -5525,12 +6367,12 @@
       <c r="E2" t="s">
         <v>355</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>357</v>
       </c>
       <c r="B3" t="s">
@@ -5542,7 +6384,7 @@
       <c r="D3" t="s">
         <v>360</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5570,7 +6412,7 @@
       <c r="B5" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5578,13 +6420,13 @@
       <c r="A6" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>370</v>
       </c>
       <c r="C6" t="s">
         <v>371</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>372</v>
       </c>
     </row>
@@ -5592,7 +6434,7 @@
       <c r="A7" t="s">
         <v>373</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>374</v>
       </c>
       <c r="C7" t="s">
@@ -5612,12 +6454,12 @@
       <c r="B8" t="s">
         <v>379</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>381</v>
       </c>
       <c r="B9" t="s">
@@ -5634,7 +6476,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>385</v>
       </c>
       <c r="B10" t="s">
@@ -5654,7 +6496,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>390</v>
       </c>
       <c r="B11" t="s">
@@ -5662,7 +6504,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>392</v>
       </c>
       <c r="B12" t="s">
@@ -5688,7 +6530,7 @@
       <c r="C13" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5696,18 +6538,18 @@
       <c r="A14" t="s">
         <v>401</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>402</v>
       </c>
       <c r="C14" t="s">
         <v>403</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>405</v>
       </c>
       <c r="B15" t="s">
@@ -5718,7 +6560,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>408</v>
       </c>
       <c r="B16" t="s">
@@ -5760,7 +6602,7 @@
       <c r="A19" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C19" t="s">
@@ -5785,7 +6627,7 @@
       </c>
     </row>
     <row r="21" ht="30" spans="1:5">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B21" t="s">
@@ -5794,7 +6636,7 @@
       <c r="C21" t="s">
         <v>428</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>429</v>
       </c>
     </row>
@@ -5805,7 +6647,7 @@
       <c r="B22" t="s">
         <v>431</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="5" t="s">
         <v>432</v>
       </c>
       <c r="F22" t="s">
@@ -5827,7 +6669,7 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>438</v>
       </c>
       <c r="B24" t="s">
@@ -5847,7 +6689,7 @@
       <c r="A25" t="s">
         <v>442</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>443</v>
       </c>
       <c r="C25" t="s">
@@ -5861,7 +6703,7 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>447</v>
       </c>
       <c r="B26" t="s">
@@ -5872,10 +6714,10 @@
       </c>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>451</v>
       </c>
       <c r="C27" t="s">
@@ -5895,10 +6737,10 @@
       <c r="A28" t="s">
         <v>456</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="5" t="s">
         <v>458</v>
       </c>
     </row>
@@ -5906,7 +6748,7 @@
       <c r="A29" t="s">
         <v>459</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>460</v>
       </c>
       <c r="E29" t="s">
@@ -5917,7 +6759,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>463</v>
       </c>
       <c r="B30" t="s">
@@ -5939,7 +6781,7 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>469</v>
       </c>
       <c r="B32" t="s">
@@ -5964,12 +6806,12 @@
       <c r="A34" t="s">
         <v>474</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>476</v>
       </c>
       <c r="B35" t="s">
@@ -5986,13 +6828,13 @@
       </c>
     </row>
     <row r="36" ht="30" spans="1:5">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>481</v>
       </c>
       <c r="B36" t="s">
         <v>482</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>483</v>
       </c>
     </row>
@@ -6003,7 +6845,7 @@
       <c r="B37" t="s">
         <v>485</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="5" t="s">
         <v>486</v>
       </c>
     </row>
@@ -6085,7 +6927,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>494</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -6105,7 +6947,7 @@
       <c r="A3" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>500</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6113,10 +6955,10 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:8">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -6133,7 +6975,7 @@
       <c r="A5" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>508</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -6144,7 +6986,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>511</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -6155,7 +6997,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>514</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -6172,7 +7014,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>519</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -6200,7 +7042,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>527</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -6248,12 +7090,12 @@
       <c r="C13" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>541</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -6282,12 +7124,12 @@
       <c r="D15" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="31.5" spans="1:8">
+      <c r="A16" s="6" t="s">
         <v>551</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -6299,18 +7141,18 @@
       <c r="F16" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="7" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="17" ht="47.25" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="6" t="s">
         <v>556</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>558</v>
       </c>
     </row>
@@ -6343,7 +7185,7 @@
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>567</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -6352,139 +7194,142 @@
       <c r="D20" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="21" ht="31.5" spans="1:7">
+    <row r="21" ht="47.25" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>571</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>573</v>
       </c>
+      <c r="G21" s="7" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="4" t="s">
-        <v>574</v>
+      <c r="A22" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
-        <v>578</v>
+      <c r="A23" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="24" ht="31.5" spans="1:6">
-      <c r="A24" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>583</v>
       </c>
+      <c r="C24" s="7" t="s">
+        <v>584</v>
+      </c>
       <c r="D24" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="F24" s="5" t="s">
         <v>585</v>
       </c>
+      <c r="F24" s="7" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
-        <v>586</v>
+      <c r="A25" s="6" t="s">
+        <v>587</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="D25" s="5" t="s">
         <v>588</v>
       </c>
+      <c r="D25" s="7" t="s">
+        <v>589</v>
+      </c>
       <c r="F25" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="E26" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>594</v>
       </c>
+      <c r="F26" s="7" t="s">
+        <v>595</v>
+      </c>
       <c r="G26" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E27" s="5" t="s">
         <v>599</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>603</v>
+      <c r="A29" s="6" t="s">
+        <v>604</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="E29" s="5" t="s">
         <v>605</v>
       </c>
+      <c r="E29" s="7" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="4" t="s">
-        <v>606</v>
+      <c r="A30" s="6" t="s">
+        <v>607</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>227</v>
@@ -6495,163 +7340,163 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="E33" s="5" t="s">
         <v>620</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>621</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>546</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>627</v>
+      <c r="A35" s="6" t="s">
+        <v>628</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E35" s="5" t="s">
         <v>629</v>
       </c>
+      <c r="E35" s="7" t="s">
+        <v>630</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="36" ht="31.5" spans="1:6">
-      <c r="A36" s="4" t="s">
-        <v>631</v>
+      <c r="A36" s="6" t="s">
+        <v>632</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="F36" s="5" t="s">
         <v>635</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:7">
-      <c r="A38" s="4" t="s">
-        <v>640</v>
+      <c r="A38" s="6" t="s">
+        <v>641</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>564</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="F38" s="5" t="s">
         <v>642</v>
       </c>
+      <c r="F38" s="7" t="s">
+        <v>643</v>
+      </c>
       <c r="G38" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:6">
-      <c r="A40" s="4" t="s">
-        <v>649</v>
+      <c r="A40" s="6" t="s">
+        <v>650</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="E40" s="5" t="s">
         <v>651</v>
       </c>
+      <c r="E40" s="7" t="s">
+        <v>652</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -6704,695 +7549,695 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>653</v>
+      <c r="A2" s="6" t="s">
+        <v>654</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>664</v>
       </c>
+      <c r="E4" s="7" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="5" ht="47.25" spans="1:7">
-      <c r="A5" s="4" t="s">
-        <v>665</v>
+      <c r="A5" s="6" t="s">
+        <v>666</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="D5" s="5" t="s">
         <v>667</v>
       </c>
+      <c r="D5" s="7" t="s">
+        <v>668</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="G5" s="5" t="s">
         <v>669</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:5">
-      <c r="A7" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>674</v>
       </c>
+      <c r="B7" s="7" t="s">
+        <v>675</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E7" s="5" t="s">
         <v>676</v>
       </c>
+      <c r="E7" s="7" t="s">
+        <v>677</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="4" t="s">
-        <v>677</v>
+      <c r="A8" s="6" t="s">
+        <v>678</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="9" ht="31.5" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E9" s="5" t="s">
         <v>687</v>
       </c>
+      <c r="E9" s="7" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="10" ht="47.25" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>688</v>
+      <c r="A10" s="6" t="s">
+        <v>689</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F10" s="5" t="s">
         <v>691</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12" ht="31.5" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>696</v>
+      <c r="A12" s="6" t="s">
+        <v>697</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="F12" s="5" t="s">
         <v>700</v>
       </c>
+      <c r="F12" s="7" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="4" t="s">
-        <v>701</v>
+      <c r="A13" s="6" t="s">
+        <v>702</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>713</v>
+      <c r="A16" s="6" t="s">
+        <v>714</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="F16" s="5" t="s">
         <v>717</v>
       </c>
+      <c r="F16" s="7" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
-        <v>718</v>
+      <c r="A17" s="6" t="s">
+        <v>719</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>718</v>
-      </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>725</v>
+      <c r="A19" s="6" t="s">
+        <v>726</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>439</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="4" t="s">
-        <v>728</v>
+      <c r="A20" s="6" t="s">
+        <v>729</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="F20" s="5" t="s">
         <v>732</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="4" t="s">
-        <v>737</v>
+      <c r="A22" s="6" t="s">
+        <v>738</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="23" ht="47.25" spans="1:7">
-      <c r="A23" s="4" t="s">
-        <v>741</v>
+      <c r="A23" s="6" t="s">
+        <v>742</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="D23" s="5" t="s">
         <v>743</v>
       </c>
+      <c r="D23" s="7" t="s">
+        <v>744</v>
+      </c>
       <c r="E23" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" ht="47.25" spans="1:6">
-      <c r="A24" s="4" t="s">
-        <v>746</v>
+      <c r="A24" s="6" t="s">
+        <v>747</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="F24" s="5" t="s">
         <v>749</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="27" ht="31.5" spans="1:8">
-      <c r="A27" s="4" t="s">
-        <v>756</v>
+      <c r="A27" s="6" t="s">
+        <v>757</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>756</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:6">
-      <c r="A29" s="4" t="s">
-        <v>766</v>
+      <c r="A29" s="6" t="s">
+        <v>767</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="E29" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>771</v>
       </c>
+      <c r="F29" s="7" t="s">
+        <v>772</v>
+      </c>
     </row>
     <row r="30" ht="31.5" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>773</v>
       </c>
+      <c r="B30" s="7" t="s">
+        <v>774</v>
+      </c>
       <c r="D30" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" ht="31.5" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>775</v>
+      <c r="A31" s="6" t="s">
+        <v>776</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="F31" s="5" t="s">
         <v>778</v>
       </c>
+      <c r="F31" s="7" t="s">
+        <v>779</v>
+      </c>
     </row>
     <row r="32" ht="31.5" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>779</v>
+      <c r="A32" s="6" t="s">
+        <v>780</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="C32" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>782</v>
       </c>
+      <c r="D32" s="7" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="33" ht="31.5" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>784</v>
       </c>
+      <c r="B33" s="7" t="s">
+        <v>785</v>
+      </c>
       <c r="D33" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="4" t="s">
-        <v>786</v>
+      <c r="A34" s="6" t="s">
+        <v>787</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>792</v>
-      </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
-        <v>795</v>
+      <c r="A37" s="6" t="s">
+        <v>796</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="4" t="s">
-        <v>799</v>
+      <c r="A38" s="6" t="s">
+        <v>800</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="B39" s="5" t="s">
         <v>803</v>
       </c>
+      <c r="B39" s="7" t="s">
+        <v>804</v>
+      </c>
       <c r="D39" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="4" t="s">
-        <v>805</v>
+      <c r="A40" s="6" t="s">
+        <v>806</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="4" t="s">
-        <v>807</v>
+      <c r="A41" s="6" t="s">
+        <v>808</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:6">
-      <c r="A42" s="4" t="s">
-        <v>812</v>
+      <c r="A42" s="6" t="s">
+        <v>813</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="E42" s="5" t="s">
         <v>816</v>
       </c>
+      <c r="E42" s="7" t="s">
+        <v>817</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="F43" s="5" t="s">
         <v>820</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>821</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>447</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="46" ht="31.5" spans="1:6">
+      <c r="A46" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="46" ht="31.5" spans="1:6">
-      <c r="A46" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="47" ht="31.5" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="B47" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="B47" s="7" t="s">
         <v>836</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="E47" s="7" t="s">
         <v>837</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -7414,7 +8259,7 @@
     <col min="5" max="5" width="29.7333333333333" customWidth="1"/>
     <col min="6" max="6" width="18.9" customWidth="1"/>
     <col min="7" max="7" width="16.95" customWidth="1"/>
-    <col min="8" max="8" width="20.075" customWidth="1"/>
+    <col min="8" max="8" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
@@ -7443,536 +8288,551 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>838</v>
+    <row r="2" ht="30" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>839</v>
       </c>
       <c r="B2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2" t="s">
+        <v>841</v>
+      </c>
+      <c r="D2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="F2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B3" t="s">
+        <v>846</v>
+      </c>
+      <c r="C3" t="s">
+        <v>847</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="F3" t="s">
         <v>839</v>
-      </c>
-      <c r="C2" t="s">
-        <v>840</v>
-      </c>
-      <c r="D2" t="s">
-        <v>841</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B3" t="s">
-        <v>844</v>
-      </c>
-      <c r="C3" t="s">
-        <v>845</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="F3" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="G4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>852</v>
+      <c r="A5" s="3" t="s">
+        <v>854</v>
       </c>
       <c r="B5" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E5" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>857</v>
+      <c r="A6" s="3" t="s">
+        <v>859</v>
       </c>
       <c r="B6" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D6" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E6" t="s">
-        <v>860</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B7" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D7" t="s">
-        <v>863</v>
+        <v>865</v>
+      </c>
+      <c r="E7" t="s">
+        <v>866</v>
       </c>
       <c r="F7" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>864</v>
+      <c r="A8" s="3" t="s">
+        <v>867</v>
       </c>
       <c r="B8" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D8" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E8" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>868</v>
+      <c r="A9" s="3" t="s">
+        <v>871</v>
       </c>
       <c r="B9" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D9" t="s">
-        <v>870</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="10" ht="45" spans="1:8">
       <c r="A10" t="s">
-        <v>873</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>877</v>
       </c>
       <c r="C10" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="H10" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="11" ht="45" spans="1:6">
-      <c r="A11" t="s">
-        <v>877</v>
+      <c r="A11" s="3" t="s">
+        <v>880</v>
       </c>
       <c r="B11" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D11" t="s">
-        <v>879</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:6">
       <c r="A12" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B12" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D12" t="s">
-        <v>883</v>
-      </c>
-      <c r="E12" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F12" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="B13" t="s">
+        <v>890</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="14" ht="45" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B14" t="s">
+        <v>894</v>
+      </c>
+      <c r="C14" t="s">
+        <v>895</v>
+      </c>
+      <c r="D14" t="s">
+        <v>896</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="B15" t="s">
+        <v>899</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="E15" t="s">
+        <v>901</v>
+      </c>
+      <c r="F15" t="s">
         <v>884</v>
       </c>
-      <c r="F12" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="13" ht="30" spans="1:5">
-      <c r="A13" t="s">
-        <v>886</v>
-      </c>
-      <c r="B13" t="s">
-        <v>887</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:6">
-      <c r="A14" t="s">
-        <v>890</v>
-      </c>
-      <c r="B14" t="s">
-        <v>891</v>
-      </c>
-      <c r="C14" t="s">
-        <v>892</v>
-      </c>
-      <c r="D14" t="s">
-        <v>893</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:6">
-      <c r="A15" t="s">
-        <v>895</v>
-      </c>
-      <c r="B15" t="s">
-        <v>896</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="E15" t="s">
-        <v>898</v>
-      </c>
-      <c r="F15" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="16" ht="30" spans="1:5">
-      <c r="A16" t="s">
-        <v>899</v>
+    </row>
+    <row r="16" ht="30" spans="1:8">
+      <c r="A16" s="3" t="s">
+        <v>902</v>
       </c>
       <c r="B16" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D16" t="s">
-        <v>901</v>
-      </c>
-      <c r="E16" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="H16" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="B17" t="s">
+        <v>908</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D17" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>903</v>
-      </c>
-      <c r="B17" t="s">
-        <v>904</v>
-      </c>
-      <c r="C17" t="s">
-        <v>905</v>
-      </c>
-      <c r="D17" t="s">
-        <v>899</v>
-      </c>
       <c r="E17" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>907</v>
+      <c r="A18" s="3" t="s">
+        <v>911</v>
       </c>
       <c r="B18" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D18" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="E18" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="H18" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B19" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="F19" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>915</v>
+      <c r="A20" s="3" t="s">
+        <v>919</v>
       </c>
       <c r="B20" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D20" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="E20" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>919</v>
+      <c r="A21" s="3" t="s">
+        <v>923</v>
       </c>
       <c r="B21" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E21" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="F21" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B22" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C22" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D22" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>927</v>
+      <c r="A23" s="3" t="s">
+        <v>931</v>
       </c>
       <c r="B23" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C23" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="E23" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:6">
       <c r="A24" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B24" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E24" t="s">
-        <v>933</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B25" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="H25" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>938</v>
+      <c r="A26" s="3" t="s">
+        <v>942</v>
       </c>
       <c r="B26" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D26" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E26" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>942</v>
+      <c r="A27" s="3" t="s">
+        <v>946</v>
       </c>
       <c r="B27" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C27" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D27" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="E27" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="F27" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="G27" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="H27" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B28" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D28" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:5">
       <c r="A29" t="s">
-        <v>951</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>952</v>
+        <v>955</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>956</v>
       </c>
       <c r="C29" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D29" t="s">
-        <v>841</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>955</v>
+        <v>842</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>959</v>
       </c>
       <c r="B30" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C30" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D30" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="31" ht="45" spans="1:6">
-      <c r="A31" t="s">
-        <v>959</v>
+        <v>962</v>
+      </c>
+      <c r="E30" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="31" ht="45" spans="1:8">
+      <c r="A31" s="3" t="s">
+        <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="C31" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="D31" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="E31" t="s">
-        <v>963</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>964</v>
+        <v>968</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>965</v>
+      <c r="A32" s="3" t="s">
+        <v>971</v>
       </c>
       <c r="B32" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="C32" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:5">
       <c r="A33" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="B33" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C33" t="s">
-        <v>970</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>971</v>
+        <v>976</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>977</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>972</v>
+      <c r="A34" s="3" t="s">
+        <v>978</v>
       </c>
       <c r="B34" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D34" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="F34" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>974</v>
+      <c r="A35" s="3" t="s">
+        <v>980</v>
       </c>
       <c r="B35" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D35" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="F35" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:6">
-      <c r="A36" t="s">
-        <v>977</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>979</v>
+      <c r="A36" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>984</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>985</v>
       </c>
       <c r="E36" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="F36" t="s">
         <v>335</v>
@@ -7980,69 +8840,69 @@
     </row>
     <row r="37" ht="30" spans="1:6">
       <c r="A37" t="s">
-        <v>981</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>983</v>
+        <v>987</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>989</v>
       </c>
       <c r="F37" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>984</v>
+      <c r="A38" s="3" t="s">
+        <v>990</v>
       </c>
       <c r="B38" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="E38" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="B39" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D39" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="F39" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="40" ht="45" spans="1:6">
-      <c r="A40" t="s">
         <v>990</v>
       </c>
+    </row>
+    <row r="40" ht="60" spans="1:6">
+      <c r="A40" s="3" t="s">
+        <v>996</v>
+      </c>
       <c r="B40" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C40" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="E40" t="s">
-        <v>993</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>994</v>
+        <v>999</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="B41" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="C41" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -8054,17 +8914,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
+    <col min="1" max="1" width="16.3" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="31.875" customWidth="1"/>
-    <col min="4" max="4" width="25.875" customWidth="1"/>
-    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="30.425" customWidth="1"/>
+    <col min="4" max="4" width="16.9583333333333" customWidth="1"/>
+    <col min="5" max="5" width="25.325" customWidth="1"/>
     <col min="6" max="6" width="22.75" customWidth="1"/>
     <col min="7" max="7" width="29.5" customWidth="1"/>
-    <col min="8" max="8" width="23.625" customWidth="1"/>
+    <col min="8" max="8" width="25.975" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
@@ -8093,6 +8953,968 @@
         <v>109</v>
       </c>
     </row>
+    <row r="2" ht="45" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E4" t="s">
+        <v>839</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F6" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="1:8">
+      <c r="A12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B12" t="s">
+        <v>531</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H12" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:8">
+      <c r="A13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="16" ht="45" spans="1:5">
+      <c r="A16" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="18" ht="75" spans="1:6">
+      <c r="A18" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:8">
+      <c r="A21" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F21" t="s">
+        <v>304</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D23" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="1:4">
+      <c r="A26" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:6">
+      <c r="A27" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>953</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F28" t="s">
+        <v>952</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:6">
+      <c r="A29" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="31" ht="30" spans="1:6">
+      <c r="A31" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:8">
+      <c r="A32" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:6">
+      <c r="A34" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:6">
+      <c r="A37" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="38" ht="30" spans="1:6">
+      <c r="A38" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="39" ht="30" spans="1:8">
+      <c r="A39" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="40" ht="30" spans="1:6">
+      <c r="A40" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D40"/>
+      <c r="F40" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="22.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.7166666666667" customWidth="1"/>
+    <col min="4" max="4" width="23.475" customWidth="1"/>
+    <col min="5" max="5" width="26.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="33.375" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="8" max="8" width="21.1916666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:5">
+      <c r="A2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:3">
+      <c r="A4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D12" t="s">
+        <v>902</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F12" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:8">
+      <c r="A13" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F13" t="s">
+        <v>601</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:6">
+      <c r="A14" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="16" ht="30" spans="1:8">
+      <c r="A16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E16" t="s">
+        <v>716</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H16" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="1:5">
+      <c r="A17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="18" ht="45" spans="1:8">
+      <c r="A18" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:6">
+      <c r="A19" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="1:5">
+      <c r="A20" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="7"/>
+    <workbookView windowWidth="27870" windowHeight="12570" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="5" r:id="rId1"/>
@@ -15,13 +15,14 @@
     <sheet name="S05" sheetId="6" r:id="rId6"/>
     <sheet name="S06" sheetId="7" r:id="rId7"/>
     <sheet name="S07" sheetId="8" r:id="rId8"/>
+    <sheet name="S8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="1368">
   <si>
     <t>GRE单词地基词全集精讲</t>
   </si>
@@ -3996,6 +3997,396 @@
   </si>
   <si>
     <t>a.一丝不苟的，关注细节的</t>
+  </si>
+  <si>
+    <t>careful</t>
+  </si>
+  <si>
+    <t>misleading</t>
+  </si>
+  <si>
+    <t>a.误导人的</t>
+  </si>
+  <si>
+    <t>mis = mistake</t>
+  </si>
+  <si>
+    <t>misguided</t>
+  </si>
+  <si>
+    <t>obscure</t>
+  </si>
+  <si>
+    <t>a.模糊的，难懂的
+vt.遮掩</t>
+  </si>
+  <si>
+    <t>obscurity n.晦涩</t>
+  </si>
+  <si>
+    <t>ambiguous</t>
+  </si>
+  <si>
+    <t>onerous</t>
+  </si>
+  <si>
+    <t>a.费劲的</t>
+  </si>
+  <si>
+    <t>onus = 责任</t>
+  </si>
+  <si>
+    <t>exacting
+laborious</t>
+  </si>
+  <si>
+    <t>opaque</t>
+  </si>
+  <si>
+    <t>a.半透明的，难懂的</t>
+  </si>
+  <si>
+    <t>outstrip</t>
+  </si>
+  <si>
+    <t>vt.超过</t>
+  </si>
+  <si>
+    <t>demand outstrip supply</t>
+  </si>
+  <si>
+    <t>outperform
+outweigh</t>
+  </si>
+  <si>
+    <t>precipitate</t>
+  </si>
+  <si>
+    <t>vt.让...仓促发生
+a.仓促的</t>
+  </si>
+  <si>
+    <t>A precipitate B</t>
+  </si>
+  <si>
+    <t>precipitation n.降水(雨、雪)
+precipitous a.鲁莽的，险峻的</t>
+  </si>
+  <si>
+    <t>perpetuate vt.使持久化；使持续</t>
+  </si>
+  <si>
+    <t>prolific</t>
+  </si>
+  <si>
+    <t>a.多产的</t>
+  </si>
+  <si>
+    <t>fruitful
+fertile
+fecund</t>
+  </si>
+  <si>
+    <t>remarkable</t>
+  </si>
+  <si>
+    <t>a.卓越的</t>
+  </si>
+  <si>
+    <t>remark 评论，点评</t>
+  </si>
+  <si>
+    <t>scarce</t>
+  </si>
+  <si>
+    <t>a.短缺的，不足的</t>
+  </si>
+  <si>
+    <t>speculate</t>
+  </si>
+  <si>
+    <t>v.猜测，投机</t>
+  </si>
+  <si>
+    <t>speculative a.猜测性质的
+speculation n.</t>
+  </si>
+  <si>
+    <t>tactful</t>
+  </si>
+  <si>
+    <t>a.老练的，有分寸的</t>
+  </si>
+  <si>
+    <t>tact n.圆通，老练，圆滑</t>
+  </si>
+  <si>
+    <t>sophisticated
+diplomatic</t>
+  </si>
+  <si>
+    <t>tactless
+ingenuous 单纯的；天真的</t>
+  </si>
+  <si>
+    <t>thrive</t>
+  </si>
+  <si>
+    <t>vi.茁壮成长</t>
+  </si>
+  <si>
+    <t>thriving a.</t>
+  </si>
+  <si>
+    <t>unfounded</t>
+  </si>
+  <si>
+    <t>found = 建造</t>
+  </si>
+  <si>
+    <t>unwarranted
+untenable
+groundless
+baseless</t>
+  </si>
+  <si>
+    <t>adjunct</t>
+  </si>
+  <si>
+    <t>n.补充，附属物，副</t>
+  </si>
+  <si>
+    <t>A is an adjunct to B</t>
+  </si>
+  <si>
+    <t>junct = join = 连接</t>
+  </si>
+  <si>
+    <t>adjunctive
+adjunction n.添加</t>
+  </si>
+  <si>
+    <t>antediluvian</t>
+  </si>
+  <si>
+    <t>a.过时的，陈旧的</t>
+  </si>
+  <si>
+    <t>antediluvian attitude</t>
+  </si>
+  <si>
+    <t>ante = 前(anticipate)</t>
+  </si>
+  <si>
+    <t>anachronistic
+chiche</t>
+  </si>
+  <si>
+    <t>constitute</t>
+  </si>
+  <si>
+    <t>v.构成，组成</t>
+  </si>
+  <si>
+    <t>A constitute B</t>
+  </si>
+  <si>
+    <t>Constitution n.宪法
+constituent n.选民</t>
+  </si>
+  <si>
+    <t>chauvinistic</t>
+  </si>
+  <si>
+    <t>a.沙文主义的</t>
+  </si>
+  <si>
+    <t>chauvinist n.
+chauvinsim n.沙文主义</t>
+  </si>
+  <si>
+    <t>jingoism 谐音军国</t>
+  </si>
+  <si>
+    <t>disown</t>
+  </si>
+  <si>
+    <t>vt.否认，和...脱离关系</t>
+  </si>
+  <si>
+    <t>disown sb/sth</t>
+  </si>
+  <si>
+    <t>downright</t>
+  </si>
+  <si>
+    <t>a&amp;ad.彻头彻尾的</t>
+  </si>
+  <si>
+    <t>thorough</t>
+  </si>
+  <si>
+    <t>draconian</t>
+  </si>
+  <si>
+    <t>德拉科</t>
+  </si>
+  <si>
+    <t>severe
+rigorous</t>
+  </si>
+  <si>
+    <t>envisage</t>
+  </si>
+  <si>
+    <t>vt.摄像</t>
+  </si>
+  <si>
+    <t>envisage the consequence</t>
+  </si>
+  <si>
+    <t>vis = visible = 看见</t>
+  </si>
+  <si>
+    <t>fault</t>
+  </si>
+  <si>
+    <t>n.错误，断层
+vt.批评</t>
+  </si>
+  <si>
+    <t>find fault with 鸡蛋里挑骨头</t>
+  </si>
+  <si>
+    <t>flighty</t>
+  </si>
+  <si>
+    <t>a.轻浮的</t>
+  </si>
+  <si>
+    <t>flighty capital markets</t>
+  </si>
+  <si>
+    <t>flight</t>
+  </si>
+  <si>
+    <t>flippant
+facetious</t>
+  </si>
+  <si>
+    <t>interdependence</t>
+  </si>
+  <si>
+    <t>n.相互依赖</t>
+  </si>
+  <si>
+    <t>independence</t>
+  </si>
+  <si>
+    <t>magisterial</t>
+  </si>
+  <si>
+    <t>a.有权威的，专横的</t>
+  </si>
+  <si>
+    <t>mag = magnitude</t>
+  </si>
+  <si>
+    <t>authoritative</t>
+  </si>
+  <si>
+    <t>outlook</t>
+  </si>
+  <si>
+    <t>n.观点，前景</t>
+  </si>
+  <si>
+    <t>a positive outlook on life</t>
+  </si>
+  <si>
+    <t>perspective
+viewpoint</t>
+  </si>
+  <si>
+    <t>overlook 疏忽
+oversight 监督</t>
+  </si>
+  <si>
+    <t>predominant</t>
+  </si>
+  <si>
+    <t>a.主导型的</t>
+  </si>
+  <si>
+    <t>predominance</t>
+  </si>
+  <si>
+    <t>predominate
+prevailing</t>
+  </si>
+  <si>
+    <t>proclaim</t>
+  </si>
+  <si>
+    <t>vt.宣告，强调</t>
+  </si>
+  <si>
+    <t>proclaim independence</t>
+  </si>
+  <si>
+    <t>proclaimation</t>
+  </si>
+  <si>
+    <t>profess</t>
+  </si>
+  <si>
+    <t>vt.(口是心非的)声称</t>
+  </si>
+  <si>
+    <t>profess to do sth</t>
+  </si>
+  <si>
+    <t>profession 职业，声明</t>
+  </si>
+  <si>
+    <t>rapacious</t>
+  </si>
+  <si>
+    <t>a.贪婪的</t>
+  </si>
+  <si>
+    <t>rape</t>
+  </si>
+  <si>
+    <t>rapacity</t>
+  </si>
+  <si>
+    <t>self-serving</t>
+  </si>
+  <si>
+    <t>a.自私自利的</t>
+  </si>
+  <si>
+    <t>versatile</t>
+  </si>
+  <si>
+    <t>a.多才多艺的，用途广泛的</t>
+  </si>
+  <si>
+    <t>versatility</t>
+  </si>
+  <si>
+    <t>all-rounded</t>
+  </si>
+  <si>
+    <t>withstand</t>
+  </si>
+  <si>
+    <t>vt.抵御</t>
+  </si>
+  <si>
+    <t>withdraw 撤回，取款
+withhold 绝给，不给</t>
   </si>
 </sst>
 </file>
@@ -4630,7 +5021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4642,6 +5033,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -5004,7 +5398,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5446,7 +5840,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -5457,10 +5851,10 @@
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -5471,13 +5865,13 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -5485,7 +5879,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -5502,7 +5896,7 @@
       <c r="A6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -5513,7 +5907,7 @@
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -5525,12 +5919,12 @@
       <c r="E7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5553,7 +5947,7 @@
       <c r="C9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5567,10 +5961,10 @@
       <c r="C10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5581,7 +5975,7 @@
       <c r="B11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -5612,7 +6006,7 @@
       <c r="C13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>158</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -5629,7 +6023,7 @@
       <c r="C14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -5637,16 +6031,16 @@
       </c>
     </row>
     <row r="15" ht="47.25" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>166</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>168</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -5654,7 +6048,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>170</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5685,13 +6079,13 @@
       </c>
     </row>
     <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>179</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>181</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -5699,13 +6093,13 @@
       </c>
     </row>
     <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>185</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -5730,10 +6124,10 @@
       <c r="C21" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5761,15 +6155,15 @@
       <c r="B23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>203</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5800,7 +6194,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>211</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5814,7 +6208,7 @@
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>215</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -5823,15 +6217,15 @@
       <c r="C27" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -5840,7 +6234,7 @@
       <c r="D28" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>223</v>
       </c>
     </row>
@@ -5851,7 +6245,7 @@
       <c r="B29" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>226</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -5859,7 +6253,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>228</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -5890,13 +6284,13 @@
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>236</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>238</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -5936,12 +6330,12 @@
       <c r="B34" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="8" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>249</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -5950,12 +6344,12 @@
       <c r="C35" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>253</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -5984,15 +6378,15 @@
       <c r="D37" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>264</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -6003,7 +6397,7 @@
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>267</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6015,7 +6409,7 @@
       <c r="D39" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="8" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6029,10 +6423,10 @@
       <c r="E40" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="8" t="s">
         <v>276</v>
       </c>
     </row>
@@ -6046,7 +6440,7 @@
       <c r="E41" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="8" t="s">
         <v>280</v>
       </c>
     </row>
@@ -6071,13 +6465,13 @@
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>287</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="8" t="s">
         <v>289</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -6091,21 +6485,21 @@
       <c r="B44" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>295</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="8" t="s">
         <v>297</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -6116,7 +6510,7 @@
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>299</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -6139,7 +6533,7 @@
       <c r="B47" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="8" t="s">
         <v>306</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -6147,7 +6541,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>307</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -6158,7 +6552,7 @@
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="7" t="s">
         <v>310</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -6175,10 +6569,10 @@
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>316</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -6189,7 +6583,7 @@
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="7" t="s">
         <v>319</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -6198,12 +6592,12 @@
       <c r="C51" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="8" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>323</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -6212,7 +6606,7 @@
       <c r="C52" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="8" t="s">
         <v>326</v>
       </c>
     </row>
@@ -6237,7 +6631,7 @@
       <c r="B54" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="8" t="s">
         <v>333</v>
       </c>
       <c r="H54" s="1" t="s">
@@ -6268,7 +6662,7 @@
       <c r="E56" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="8" t="s">
         <v>342</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -6276,13 +6670,13 @@
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="7" t="s">
         <v>344</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="8" t="s">
         <v>346</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -6293,13 +6687,13 @@
       <c r="A58" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="8" t="s">
         <v>351</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -6367,7 +6761,7 @@
       <c r="E2" t="s">
         <v>355</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>356</v>
       </c>
     </row>
@@ -6384,7 +6778,7 @@
       <c r="D3" t="s">
         <v>360</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6412,7 +6806,7 @@
       <c r="B5" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>368</v>
       </c>
     </row>
@@ -6420,13 +6814,13 @@
       <c r="A6" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>370</v>
       </c>
       <c r="C6" t="s">
         <v>371</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>372</v>
       </c>
     </row>
@@ -6434,7 +6828,7 @@
       <c r="A7" t="s">
         <v>373</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>374</v>
       </c>
       <c r="C7" t="s">
@@ -6454,7 +6848,7 @@
       <c r="B8" t="s">
         <v>379</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>380</v>
       </c>
     </row>
@@ -6530,7 +6924,7 @@
       <c r="C13" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6538,13 +6932,13 @@
       <c r="A14" t="s">
         <v>401</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>402</v>
       </c>
       <c r="C14" t="s">
         <v>403</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>404</v>
       </c>
     </row>
@@ -6602,7 +6996,7 @@
       <c r="A19" t="s">
         <v>418</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>419</v>
       </c>
       <c r="C19" t="s">
@@ -6636,7 +7030,7 @@
       <c r="C21" t="s">
         <v>428</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>429</v>
       </c>
     </row>
@@ -6647,7 +7041,7 @@
       <c r="B22" t="s">
         <v>431</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>432</v>
       </c>
       <c r="F22" t="s">
@@ -6689,7 +7083,7 @@
       <c r="A25" t="s">
         <v>442</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>443</v>
       </c>
       <c r="C25" t="s">
@@ -6717,7 +7111,7 @@
       <c r="A27" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>451</v>
       </c>
       <c r="C27" t="s">
@@ -6737,10 +7131,10 @@
       <c r="A28" t="s">
         <v>456</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>458</v>
       </c>
     </row>
@@ -6748,7 +7142,7 @@
       <c r="A29" t="s">
         <v>459</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>460</v>
       </c>
       <c r="E29" t="s">
@@ -6806,7 +7200,7 @@
       <c r="A34" t="s">
         <v>474</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>475</v>
       </c>
     </row>
@@ -6834,7 +7228,7 @@
       <c r="B36" t="s">
         <v>482</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="6" t="s">
         <v>483</v>
       </c>
     </row>
@@ -6845,7 +7239,7 @@
       <c r="B37" t="s">
         <v>485</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>486</v>
       </c>
     </row>
@@ -6927,7 +7321,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>494</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -6947,7 +7341,7 @@
       <c r="A3" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>500</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6955,10 +7349,10 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -6975,7 +7369,7 @@
       <c r="A5" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>508</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -6986,7 +7380,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>511</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -6997,7 +7391,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>514</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -7014,7 +7408,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>519</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -7042,7 +7436,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>527</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -7090,12 +7484,12 @@
       <c r="C13" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>541</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -7124,12 +7518,12 @@
       <c r="D15" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:8">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>551</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -7141,18 +7535,18 @@
       <c r="F16" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="17" ht="47.25" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>556</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>558</v>
       </c>
     </row>
@@ -7185,7 +7579,7 @@
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>567</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -7194,7 +7588,7 @@
       <c r="D20" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>570</v>
       </c>
     </row>
@@ -7205,15 +7599,15 @@
       <c r="B21" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>575</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -7227,7 +7621,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>579</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -7238,30 +7632,30 @@
       </c>
     </row>
     <row r="24" ht="31.5" spans="1:6">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>584</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="8" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>587</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>589</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -7278,10 +7672,10 @@
       <c r="B26" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="8" t="s">
         <v>595</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -7298,7 +7692,7 @@
       <c r="C27" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>600</v>
       </c>
     </row>
@@ -7314,18 +7708,18 @@
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>604</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>607</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -7379,7 +7773,7 @@
       <c r="D33" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>621</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -7407,13 +7801,13 @@
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:6">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>628</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>630</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -7421,7 +7815,7 @@
       </c>
     </row>
     <row r="36" ht="31.5" spans="1:6">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>632</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -7433,7 +7827,7 @@
       <c r="D36" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>636</v>
       </c>
     </row>
@@ -7452,7 +7846,7 @@
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:7">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>641</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -7461,7 +7855,7 @@
       <c r="E38" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="8" t="s">
         <v>643</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -7486,13 +7880,13 @@
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:6">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>650</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>652</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -7549,7 +7943,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>654</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -7566,7 +7960,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>659</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7589,24 +7983,24 @@
       <c r="B4" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="5" ht="47.25" spans="1:7">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>666</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>668</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>670</v>
       </c>
     </row>
@@ -7622,21 +8016,21 @@
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:5">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>675</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>678</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -7668,12 +8062,12 @@
       <c r="C9" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="10" ht="47.25" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>689</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -7682,7 +8076,7 @@
       <c r="E10" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7701,7 +8095,7 @@
       </c>
     </row>
     <row r="12" ht="31.5" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>697</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -7713,12 +8107,12 @@
       <c r="E12" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>702</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -7760,7 +8154,7 @@
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>714</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -7772,12 +8166,12 @@
       <c r="E16" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>719</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -7791,7 +8185,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>723</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -7805,7 +8199,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>726</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -7822,7 +8216,7 @@
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>729</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -7834,7 +8228,7 @@
       <c r="E20" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>733</v>
       </c>
     </row>
@@ -7853,7 +8247,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>738</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -7867,13 +8261,13 @@
       </c>
     </row>
     <row r="23" ht="47.25" spans="1:7">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>742</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>744</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -7884,7 +8278,7 @@
       </c>
     </row>
     <row r="24" ht="47.25" spans="1:6">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>747</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -7893,7 +8287,7 @@
       <c r="D24" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="8" t="s">
         <v>750</v>
       </c>
     </row>
@@ -7923,7 +8317,7 @@
       </c>
     </row>
     <row r="27" ht="31.5" spans="1:8">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>757</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -7932,7 +8326,7 @@
       <c r="C27" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>760</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -7943,7 +8337,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>763</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -7963,7 +8357,7 @@
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:6">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>767</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -7975,18 +8369,18 @@
       <c r="D29" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="8" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="30" ht="31.5" spans="1:4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>774</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -7994,7 +8388,7 @@
       </c>
     </row>
     <row r="31" ht="31.5" spans="1:6">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>776</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -8003,29 +8397,29 @@
       <c r="D31" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="8" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:4">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>780</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="8" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:6">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>785</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -8036,7 +8430,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>787</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -8061,7 +8455,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>794</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -8072,7 +8466,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>796</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -8086,7 +8480,7 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>800</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -8103,7 +8497,7 @@
       <c r="A39" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>804</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -8114,7 +8508,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>806</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -8125,7 +8519,7 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="7" t="s">
         <v>808</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -8142,7 +8536,7 @@
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:6">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>813</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -8154,7 +8548,7 @@
       <c r="D42" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>817</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -8171,7 +8565,7 @@
       <c r="D43" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="8" t="s">
         <v>821</v>
       </c>
     </row>
@@ -8210,7 +8604,7 @@
       </c>
     </row>
     <row r="46" ht="31.5" spans="1:6">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>831</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -8219,7 +8613,7 @@
       <c r="C46" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="8" t="s">
         <v>834</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -8230,13 +8624,13 @@
       <c r="A47" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="8" t="s">
         <v>838</v>
       </c>
     </row>
@@ -8257,8 +8651,8 @@
     <col min="3" max="3" width="27.4" customWidth="1"/>
     <col min="4" max="4" width="16.55" customWidth="1"/>
     <col min="5" max="5" width="29.7333333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.9" customWidth="1"/>
-    <col min="7" max="7" width="16.95" customWidth="1"/>
+    <col min="6" max="6" width="16.4583333333333" customWidth="1"/>
+    <col min="7" max="7" width="14.2166666666667" customWidth="1"/>
     <col min="8" max="8" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8301,7 +8695,7 @@
       <c r="D2" t="s">
         <v>842</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>843</v>
       </c>
       <c r="F2" t="s">
@@ -8318,7 +8712,7 @@
       <c r="C3" t="s">
         <v>847</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>848</v>
       </c>
       <c r="F3" t="s">
@@ -8372,7 +8766,7 @@
       <c r="E6" t="s">
         <v>862</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>863</v>
       </c>
     </row>
@@ -8417,10 +8811,10 @@
       <c r="D9" t="s">
         <v>873</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>875</v>
       </c>
     </row>
@@ -8428,7 +8822,7 @@
       <c r="A10" t="s">
         <v>876</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>877</v>
       </c>
       <c r="C10" t="s">
@@ -8448,7 +8842,7 @@
       <c r="D11" t="s">
         <v>882</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>883</v>
       </c>
     </row>
@@ -8462,7 +8856,7 @@
       <c r="D12" t="s">
         <v>886</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>887</v>
       </c>
       <c r="F12" t="s">
@@ -8476,10 +8870,10 @@
       <c r="B13" t="s">
         <v>890</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>891</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>892</v>
       </c>
     </row>
@@ -8496,7 +8890,7 @@
       <c r="D14" t="s">
         <v>896</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>897</v>
       </c>
     </row>
@@ -8507,7 +8901,7 @@
       <c r="B15" t="s">
         <v>899</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>900</v>
       </c>
       <c r="E15" t="s">
@@ -8527,7 +8921,7 @@
       <c r="D16" t="s">
         <v>904</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>905</v>
       </c>
       <c r="H16" t="s">
@@ -8645,7 +9039,7 @@
       <c r="E24" t="s">
         <v>937</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>938</v>
       </c>
     </row>
@@ -8715,7 +9109,7 @@
       <c r="A29" t="s">
         <v>955</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>956</v>
       </c>
       <c r="C29" t="s">
@@ -8724,7 +9118,7 @@
       <c r="D29" t="s">
         <v>842</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>958</v>
       </c>
     </row>
@@ -8761,7 +9155,7 @@
       <c r="E31" t="s">
         <v>968</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>969</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -8789,7 +9183,7 @@
       <c r="C33" t="s">
         <v>976</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>977</v>
       </c>
     </row>
@@ -8825,10 +9219,10 @@
       <c r="A36" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="6" t="s">
         <v>985</v>
       </c>
       <c r="E36" t="s">
@@ -8842,10 +9236,10 @@
       <c r="A37" t="s">
         <v>987</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>989</v>
       </c>
       <c r="F37" t="s">
@@ -8890,7 +9284,7 @@
       <c r="E40" t="s">
         <v>999</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>1000</v>
       </c>
     </row>
@@ -8917,14 +9311,14 @@
   <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="16.3" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="30.425" customWidth="1"/>
+    <col min="1" max="1" width="14.0333333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="30.575" customWidth="1"/>
     <col min="4" max="4" width="16.9583333333333" customWidth="1"/>
     <col min="5" max="5" width="25.325" customWidth="1"/>
-    <col min="6" max="6" width="22.75" customWidth="1"/>
-    <col min="7" max="7" width="29.5" customWidth="1"/>
-    <col min="8" max="8" width="25.975" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" customWidth="1"/>
+    <col min="7" max="7" width="14.3166666666667" customWidth="1"/>
+    <col min="8" max="8" width="24.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
@@ -9420,7 +9814,7 @@
       <c r="B34" t="s">
         <v>1126</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>1127</v>
       </c>
       <c r="E34" t="s">
@@ -9563,7 +9957,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -9571,9 +9965,9 @@
     <col min="3" max="3" width="22.7166666666667" customWidth="1"/>
     <col min="4" max="4" width="23.475" customWidth="1"/>
     <col min="5" max="5" width="26.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="33.375" customWidth="1"/>
-    <col min="7" max="7" width="25.75" customWidth="1"/>
-    <col min="8" max="8" width="21.1916666666667" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="22.7166666666667" customWidth="1"/>
+    <col min="8" max="8" width="26.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
@@ -9823,7 +10217,7 @@
       </c>
     </row>
     <row r="16" ht="30" spans="1:8">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>1221</v>
       </c>
       <c r="B16" t="s">
@@ -9843,7 +10237,7 @@
       </c>
     </row>
     <row r="17" ht="30" spans="1:5">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>1225</v>
       </c>
       <c r="B17" t="s">
@@ -9857,7 +10251,7 @@
       </c>
     </row>
     <row r="18" ht="45" spans="1:8">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>1229</v>
       </c>
       <c r="B18" t="s">
@@ -9877,7 +10271,7 @@
       </c>
     </row>
     <row r="19" ht="30" spans="1:6">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>1235</v>
       </c>
       <c r="B19" t="s">
@@ -9907,12 +10301,524 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="B21" t="s">
         <v>1245</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="23" ht="30" spans="1:6">
+      <c r="A23" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="1:8">
+      <c r="A26" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="28" ht="45" spans="1:6">
+      <c r="A28" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F29" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="31" ht="30" spans="1:6">
+      <c r="A31" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:7">
+      <c r="A32" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="34" ht="60" spans="1:6">
+      <c r="A34" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B34" t="s">
+        <v>564</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="21.975" customWidth="1"/>
+    <col min="3" max="3" width="22.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="23.4416666666667" customWidth="1"/>
+    <col min="6" max="6" width="15.125" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="8" max="8" width="20.975" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:5">
+      <c r="A2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:6">
+      <c r="A4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="30" spans="1:6">
+      <c r="A5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="8" ht="30" spans="1:6">
+      <c r="A8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="1:3">
+      <c r="A10" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:6">
+      <c r="A11" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:8">
+      <c r="A14" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:6">
+      <c r="A15" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G19" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:8">
+      <c r="A21" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>1367</v>
       </c>
     </row>
   </sheetData>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="6"/>
+    <workbookView windowWidth="13875" windowHeight="12390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="5" r:id="rId1"/>
@@ -15,14 +15,15 @@
     <sheet name="S05" sheetId="6" r:id="rId6"/>
     <sheet name="S06" sheetId="7" r:id="rId7"/>
     <sheet name="S07" sheetId="8" r:id="rId8"/>
-    <sheet name="S8" sheetId="9" r:id="rId9"/>
+    <sheet name="S08" sheetId="9" r:id="rId9"/>
+    <sheet name="S09" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="1368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="1512">
   <si>
     <t>GRE单词地基词全集精讲</t>
   </si>
@@ -404,8 +405,20 @@
     <t>bias</t>
   </si>
   <si>
-    <t>n.偏见 
-vt.使某人产生偏见</t>
+    <r>
+      <t>n.偏见 
+vt.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使某人产生偏见</t>
+    </r>
   </si>
   <si>
     <t>bias in favor of / against sth</t>
@@ -458,7 +471,19 @@
     <t>competing</t>
   </si>
   <si>
-    <t>a.项目矛盾的</t>
+    <r>
+      <t>a.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>相互矛盾的</t>
+    </r>
   </si>
   <si>
     <t>the competing demands</t>
@@ -485,7 +510,8 @@
     <t>comprehend v.理解，包含</t>
   </si>
   <si>
-    <t>thorough a.详细的</t>
+    <t>thorough a.详细的
+exhaustive</t>
   </si>
   <si>
     <t>controversial</t>
@@ -565,7 +591,29 @@
     <t>v.偏离</t>
   </si>
   <si>
-    <t>deviate from original plan</t>
+    <r>
+      <t xml:space="preserve">deviate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>from</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> original plan</t>
+    </r>
   </si>
   <si>
     <t>deviation n.偏差</t>
@@ -603,7 +651,19 @@
     <t>established</t>
   </si>
   <si>
-    <t>a.被证实了的，著名的</t>
+    <r>
+      <t>a.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>被证实了的，著名的</t>
+    </r>
   </si>
   <si>
     <t>exaggeration</t>
@@ -662,6 +722,9 @@
   </si>
   <si>
     <t>fickleness</t>
+  </si>
+  <si>
+    <t>nickel 镍，五分硬币</t>
   </si>
   <si>
     <t>framework</t>
@@ -744,7 +807,7 @@
     <t>im = into</t>
   </si>
   <si>
-    <t>eminent a.杰出的，非凡的</t>
+    <t>eminent a.杰出的，非凡的 = prominent</t>
   </si>
   <si>
     <t>impending</t>
@@ -759,7 +822,39 @@
     <t>indifferent</t>
   </si>
   <si>
-    <t>a.冷漠的，平庸的</t>
+    <r>
+      <t>a.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冷漠的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平庸的</t>
+    </r>
   </si>
   <si>
     <t>be indifferent to sth
@@ -844,8 +939,20 @@
     <t>mercenary</t>
   </si>
   <si>
-    <t>n.雇佣兵 
-a.唯利是图的</t>
+    <r>
+      <t>n.雇佣兵 
+a.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>唯利是图的</t>
+    </r>
   </si>
   <si>
     <t>merchant</t>
@@ -868,6 +975,9 @@
   <si>
     <t>holy
 supernatural</t>
+  </si>
+  <si>
+    <t>unanimous a.一致的</t>
   </si>
   <si>
     <t>overstatement</t>
@@ -905,7 +1015,19 @@
     <t>partial</t>
   </si>
   <si>
-    <t>a.部分的，偏心的</t>
+    <r>
+      <t>a.部分的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>偏心的</t>
+    </r>
   </si>
   <si>
     <t>be parcial to sth/sb</t>
@@ -936,7 +1058,19 @@
     <t>presumption</t>
   </si>
   <si>
-    <t>n.假定，傲慢，自大</t>
+    <r>
+      <t>n.假定，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>傲慢，自大</t>
+    </r>
   </si>
   <si>
     <t>pre = 前
@@ -947,6 +1081,9 @@
 presumptuous a.擅自做主的</t>
   </si>
   <si>
+    <t>contempt n.蔑视；轻蔑；鄙视</t>
+  </si>
+  <si>
     <t>prophetic</t>
   </si>
   <si>
@@ -1012,8 +1149,33 @@
     <t>sterling</t>
   </si>
   <si>
-    <t>a.优秀的 
+    <r>
+      <t>a.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>优秀的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
 n.英镑</t>
+    </r>
+  </si>
+  <si>
+    <t>sterling quality 优秀品质</t>
   </si>
   <si>
     <t>star</t>
@@ -3240,7 +3402,26 @@
     <t>anachronistic</t>
   </si>
   <si>
-    <t>a.过时的，时代错误的</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a.过时的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时代错误的</t>
+    </r>
   </si>
   <si>
     <t>ana = 否定
@@ -3262,7 +3443,26 @@
     <t>belie</t>
   </si>
   <si>
-    <t>vt.掩饰，证明...是假的</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vt.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>掩饰，证明...是假的</t>
+    </r>
   </si>
   <si>
     <t>lie</t>
@@ -3271,7 +3471,26 @@
     <t>betray</t>
   </si>
   <si>
-    <t>vt.背叛，流露出</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vt.背叛，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流露出</t>
+    </r>
   </si>
   <si>
     <t>his face betrayed nothing</t>
@@ -3586,6 +3805,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>null</t>
     </r>
     <r>
@@ -4388,6 +4614,460 @@
     <t>withdraw 撤回，取款
 withhold 绝给，不给</t>
   </si>
+  <si>
+    <t>apropos</t>
+  </si>
+  <si>
+    <t>prep.关于，谈及</t>
+  </si>
+  <si>
+    <t>suggestion apropos the script
+所有有关该剧本的建议
+apropos of that 谈及此</t>
+  </si>
+  <si>
+    <t>pose 放置</t>
+  </si>
+  <si>
+    <t>arduous</t>
+  </si>
+  <si>
+    <t>a.费力的，艰难的</t>
+  </si>
+  <si>
+    <t>a long and arduous trip</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>strenuous
+stressful
+exacting
+onerous</t>
+  </si>
+  <si>
+    <t>avaricious</t>
+  </si>
+  <si>
+    <t>avid a.热切的</t>
+  </si>
+  <si>
+    <t>avarice n.贪婪，贪财</t>
+  </si>
+  <si>
+    <t>greedy
+mercenary 唯利是图的
+rapacious</t>
+  </si>
+  <si>
+    <t>bearing</t>
+  </si>
+  <si>
+    <t>n.举止，关系</t>
+  </si>
+  <si>
+    <t>A have a bearing on B</t>
+  </si>
+  <si>
+    <t>burlesque</t>
+  </si>
+  <si>
+    <t>n.滑稽剧</t>
+  </si>
+  <si>
+    <t>black comic burlesque</t>
+  </si>
+  <si>
+    <t>cagey</t>
+  </si>
+  <si>
+    <t>a.遮掩的，精明的</t>
+  </si>
+  <si>
+    <t>a cagey consumer
+be cagey about giving out details</t>
+  </si>
+  <si>
+    <t>tactful 老练的</t>
+  </si>
+  <si>
+    <t>chronicle</t>
+  </si>
+  <si>
+    <t>n.编年史
+vt.按时间顺序写</t>
+  </si>
+  <si>
+    <t>chron = 时间</t>
+  </si>
+  <si>
+    <t>chronic a.慢性的
+chronology n.年表</t>
+  </si>
+  <si>
+    <t>churlish</t>
+  </si>
+  <si>
+    <t>a.不礼貌的，粗野的</t>
+  </si>
+  <si>
+    <t>churl = 农民</t>
+  </si>
+  <si>
+    <t>clandestine</t>
+  </si>
+  <si>
+    <t>a.神秘的</t>
+  </si>
+  <si>
+    <t>clandestine meeting</t>
+  </si>
+  <si>
+    <t>cla = cellar</t>
+  </si>
+  <si>
+    <t>secretive
+underground</t>
+  </si>
+  <si>
+    <t>complacent</t>
+  </si>
+  <si>
+    <t>a.自满的</t>
+  </si>
+  <si>
+    <t>com = 强调 plac = pleasant</t>
+  </si>
+  <si>
+    <t>complacency n.</t>
+  </si>
+  <si>
+    <t>complaisant a.彬彬有礼的</t>
+  </si>
+  <si>
+    <t>covert</t>
+  </si>
+  <si>
+    <t>a.隐秘的</t>
+  </si>
+  <si>
+    <t>supply covert military aid</t>
+  </si>
+  <si>
+    <t>covet vt.垂涎欲滴</t>
+  </si>
+  <si>
+    <t>deliberate</t>
+  </si>
+  <si>
+    <t>a.故意的，深思熟虑的
+v.仔细考虑</t>
+  </si>
+  <si>
+    <t>considered
+designed
+intended</t>
+  </si>
+  <si>
+    <t>derivative</t>
+  </si>
+  <si>
+    <t>a.衍生的
+n.衍生物</t>
+  </si>
+  <si>
+    <t>derive</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>esoteric</t>
+  </si>
+  <si>
+    <t>a.限于小圈子的，难懂的</t>
+  </si>
+  <si>
+    <t>eso = in
+ter = internal</t>
+  </si>
+  <si>
+    <t>convoluted
+impenetrable
+ambiguous
+opaque
+obscure</t>
+  </si>
+  <si>
+    <t>evanescent</t>
+  </si>
+  <si>
+    <t>a.容易消散的，短暂的</t>
+  </si>
+  <si>
+    <t>capture the evanescent experience</t>
+  </si>
+  <si>
+    <t>van = vanish</t>
+  </si>
+  <si>
+    <t>evanescence n.</t>
+  </si>
+  <si>
+    <t>temporary</t>
+  </si>
+  <si>
+    <t>exhilarating</t>
+  </si>
+  <si>
+    <t>a.令人高兴的</t>
+  </si>
+  <si>
+    <t>hilarious a.滑稽的</t>
+  </si>
+  <si>
+    <t>exhilarate v.</t>
+  </si>
+  <si>
+    <t>rehabilitate 康复，恢复</t>
+  </si>
+  <si>
+    <t>forestall</t>
+  </si>
+  <si>
+    <t>vt.预先阻止</t>
+  </si>
+  <si>
+    <t>fore + stall熄火</t>
+  </si>
+  <si>
+    <t>prevent
+preclude</t>
+  </si>
+  <si>
+    <t>illusory</t>
+  </si>
+  <si>
+    <t>a.虚幻的</t>
+  </si>
+  <si>
+    <t>his freedom is illusory</t>
+  </si>
+  <si>
+    <t>illusion 幻觉
+illusionary a.错觉的</t>
+  </si>
+  <si>
+    <t>loquacious</t>
+  </si>
+  <si>
+    <t>a.多话的</t>
+  </si>
+  <si>
+    <t>chatty
+gabby</t>
+  </si>
+  <si>
+    <t>momentary</t>
+  </si>
+  <si>
+    <t>a.瞬间的，短暂的</t>
+  </si>
+  <si>
+    <t>momentous a.重大的</t>
+  </si>
+  <si>
+    <t>mundane</t>
+  </si>
+  <si>
+    <t>a.世俗的
+n.平凡的事务</t>
+  </si>
+  <si>
+    <t>do mundane tasks</t>
+  </si>
+  <si>
+    <t>secular a.世俗的</t>
+  </si>
+  <si>
+    <t>parody</t>
+  </si>
+  <si>
+    <t>vt&amp;n.戏仿</t>
+  </si>
+  <si>
+    <t>pastiche</t>
+  </si>
+  <si>
+    <t>n.模仿之作</t>
+  </si>
+  <si>
+    <t>a pastiche of ideas</t>
+  </si>
+  <si>
+    <t>hodgepodge
+motley</t>
+  </si>
+  <si>
+    <t>penetrating</t>
+  </si>
+  <si>
+    <t>a.刺耳的，有洞察力的</t>
+  </si>
+  <si>
+    <t>penetrate</t>
+  </si>
+  <si>
+    <t>piercing</t>
+  </si>
+  <si>
+    <t>perfidious</t>
+  </si>
+  <si>
+    <t>a.不忠诚的</t>
+  </si>
+  <si>
+    <t>per = 完全 fid = faith = 相信</t>
+  </si>
+  <si>
+    <t>perfidy n.</t>
+  </si>
+  <si>
+    <t>disloyal
+traitorous</t>
+  </si>
+  <si>
+    <t>perilous</t>
+  </si>
+  <si>
+    <t>a.危险的，险恶的</t>
+  </si>
+  <si>
+    <t>peril n.
+imperil vt.</t>
+  </si>
+  <si>
+    <t>precarious
+hazardous</t>
+  </si>
+  <si>
+    <t>permeate</t>
+  </si>
+  <si>
+    <t>vt.弥漫，全面影响</t>
+  </si>
+  <si>
+    <t>bias against women permeate every level</t>
+  </si>
+  <si>
+    <t>permeable a.</t>
+  </si>
+  <si>
+    <t>pioneering</t>
+  </si>
+  <si>
+    <t>a.先锋的，先驱的</t>
+  </si>
+  <si>
+    <t>pioneer n.</t>
+  </si>
+  <si>
+    <t>innovative</t>
+  </si>
+  <si>
+    <t>plagiarize</t>
+  </si>
+  <si>
+    <t>vt.剽窃</t>
+  </si>
+  <si>
+    <t>plagiarism n.剽窃
+plagiarist n.剽窃者</t>
+  </si>
+  <si>
+    <t>pretence</t>
+  </si>
+  <si>
+    <t>n.假装，伪装</t>
+  </si>
+  <si>
+    <t>make a pretence of reading</t>
+  </si>
+  <si>
+    <t>pretend</t>
+  </si>
+  <si>
+    <t>affect</t>
+  </si>
+  <si>
+    <t>prosaic</t>
+  </si>
+  <si>
+    <t>a.平凡的</t>
+  </si>
+  <si>
+    <t>pugnacious</t>
+  </si>
+  <si>
+    <t>a.好斗的</t>
+  </si>
+  <si>
+    <t>pugnacity n.</t>
+  </si>
+  <si>
+    <t>aggressive</t>
+  </si>
+  <si>
+    <t>punctilious</t>
+  </si>
+  <si>
+    <t>a.一丝不苟的；循规蹈矩的</t>
+  </si>
+  <si>
+    <t>punctual a.守时的</t>
+  </si>
+  <si>
+    <t>satire</t>
+  </si>
+  <si>
+    <t>n.讽刺，讽刺作品</t>
+  </si>
+  <si>
+    <t>satirize
+satirical</t>
+  </si>
+  <si>
+    <t>irony
+sarcasm</t>
+  </si>
+  <si>
+    <t>tabloid</t>
+  </si>
+  <si>
+    <t>n.通俗小报</t>
+  </si>
+  <si>
+    <t>tablet</t>
+  </si>
+  <si>
+    <t>truculent</t>
+  </si>
+  <si>
+    <t>truculence</t>
+  </si>
+  <si>
+    <t>voracious</t>
+  </si>
+  <si>
+    <t>vorac = devour</t>
+  </si>
+  <si>
+    <t>greedy
+mercenary 唯利是图的
+rapacious
+avaracious</t>
+  </si>
 </sst>
 </file>
 
@@ -4395,11 +5075,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4423,16 +5103,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4447,22 +5171,31 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4477,39 +5210,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4523,39 +5240,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4563,6 +5250,13 @@
       <color rgb="FF010102"/>
       <name val="oalecd9"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -4580,13 +5274,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4598,157 +5412,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4764,6 +5440,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -4774,26 +5468,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4809,30 +5488,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4855,8 +5510,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4871,147 +5526,186 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5021,12 +5715,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5040,11 +5737,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5398,7 +6095,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5791,6 +6488,603 @@
     <hyperlink ref="B2" r:id="rId1" display="https://www.bilibili.com/video/BV1Zt4y1G7AY?p=1"/>
     <hyperlink ref="B3" r:id="rId2" display="https://www.bilibili.com/video/BV1Zt4y1G7AY?p=3"/>
   </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="19.35" customWidth="1"/>
+    <col min="2" max="2" width="22.0166666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.0583333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.5333333333333" customWidth="1"/>
+    <col min="5" max="7" width="19.35" customWidth="1"/>
+    <col min="8" max="8" width="20.7666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="45" spans="1:4">
+      <c r="A2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="3" ht="60" spans="1:6">
+      <c r="A3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="4" ht="45" spans="1:6">
+      <c r="A4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H5" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:6">
+      <c r="A7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="8" ht="30" spans="1:8">
+      <c r="A8" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F9" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="1:6">
+      <c r="A10" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="13" ht="45" spans="1:6">
+      <c r="A13" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:7">
+      <c r="A14" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="15" ht="75" spans="1:6">
+      <c r="A15" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="18" ht="30" spans="1:6">
+      <c r="A18" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:6">
+      <c r="A19" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="1:6">
+      <c r="A20" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D21" t="s">
+        <v>971</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:6">
+      <c r="A22" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:6">
+      <c r="A24" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="1:6">
+      <c r="A26" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:6">
+      <c r="A27" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D32" t="s">
+        <v>810</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="35" ht="30" spans="1:6">
+      <c r="A35" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H37" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="38" ht="60" spans="1:6">
+      <c r="A38" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5809,7 +7103,7 @@
     <col min="5" max="5" width="30.9833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.6916666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.9666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.4083333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5968,7 +7262,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="1:6">
+    <row r="11" ht="31.5" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>147</v>
       </c>
@@ -5981,7 +7275,7 @@
       <c r="E11" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="9" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6162,7 +7456,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:8">
       <c r="A24" s="7" t="s">
         <v>203</v>
       </c>
@@ -6178,120 +7472,123 @@
       <c r="F24" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
       <c r="A27" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>117</v>
@@ -6299,405 +7596,414 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>160</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" ht="31.5" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
       <c r="A35" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" ht="31.5" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="39" ht="31.5" spans="1:6">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" ht="31.5" spans="1:8">
       <c r="A39" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" ht="63" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
       <c r="A43" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="44" ht="31.5" spans="1:5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="44" ht="31.5" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
       <c r="A45" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="47" ht="31.5" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
       <c r="A50" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>316</v>
+        <v>319</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
       <c r="A51" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" ht="31.5" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56" ht="31.5" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
       <c r="A57" s="7" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" ht="31.5" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -6749,526 +8055,526 @@
       </c>
     </row>
     <row r="2" ht="30" spans="1:7">
-      <c r="A2" s="3" t="s">
-        <v>352</v>
+      <c r="A2" s="4" t="s">
+        <v>356</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>357</v>
+      <c r="A3" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="B3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D3" t="s">
-        <v>360</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:5">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B5" t="s">
-        <v>367</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:6">
       <c r="A6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="7" ht="30" spans="1:8">
       <c r="A7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="C7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H7" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:5">
       <c r="A8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B8" t="s">
-        <v>379</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>381</v>
+      <c r="A9" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E9" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" t="s">
+        <v>391</v>
+      </c>
+      <c r="D10" t="s">
+        <v>392</v>
+      </c>
+      <c r="E10" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B10" t="s">
-        <v>386</v>
-      </c>
-      <c r="C10" t="s">
-        <v>387</v>
-      </c>
-      <c r="D10" t="s">
-        <v>388</v>
-      </c>
-      <c r="E10" t="s">
-        <v>389</v>
-      </c>
-      <c r="F10" t="s">
-        <v>381</v>
-      </c>
-    </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>390</v>
+      <c r="A11" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>392</v>
+      <c r="A12" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="B12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:6">
       <c r="A13" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C13" t="s">
-        <v>399</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>400</v>
+        <v>403</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:5">
       <c r="A14" t="s">
-        <v>401</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>402</v>
+        <v>405</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>406</v>
       </c>
       <c r="C14" t="s">
-        <v>403</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>405</v>
+      <c r="A15" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="B15" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>408</v>
+      <c r="A16" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E16" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B17" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C17" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B18" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E18" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F18" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:4">
       <c r="A19" t="s">
-        <v>418</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="C19" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D19" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E20" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G20" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>426</v>
+      <c r="A21" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:6">
       <c r="A22" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B22" t="s">
-        <v>431</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B23" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E23" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>438</v>
+      <c r="A24" s="4" t="s">
+        <v>442</v>
       </c>
       <c r="B24" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D24" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E24" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F24" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:6">
       <c r="A25" t="s">
-        <v>442</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="C25" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D25" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F25" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="3" t="s">
-        <v>447</v>
+      <c r="A26" s="4" t="s">
+        <v>451</v>
       </c>
       <c r="B26" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F26" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>451</v>
+      <c r="A27" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="C27" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D27" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E27" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H27" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" ht="45" spans="1:8">
       <c r="A28" t="s">
-        <v>456</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:6">
       <c r="A29" t="s">
-        <v>459</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>460</v>
+        <v>463</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="E29" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F29" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>463</v>
+      <c r="A30" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="B30" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C30" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E30" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B31" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="3" t="s">
-        <v>469</v>
+      <c r="A32" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="B32" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F32" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B33" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C33" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:2">
       <c r="A34" t="s">
-        <v>474</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>475</v>
+        <v>478</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>476</v>
+      <c r="A35" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="B35" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C35" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D35" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F35" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>481</v>
+      <c r="A36" s="4" t="s">
+        <v>485</v>
       </c>
       <c r="B36" t="s">
-        <v>482</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>483</v>
+        <v>486</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:6">
       <c r="A37" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B37" t="s">
-        <v>485</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>486</v>
+        <v>489</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B38" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D38" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E38" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F38" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B39" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D39" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -7322,575 +8628,575 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:8">
       <c r="A4" s="7" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" ht="31.5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" ht="31.5" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" ht="31.5" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:8">
       <c r="A16" s="7" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" ht="47.25" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" ht="47.25" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" ht="31.5" spans="1:6">
       <c r="A24" s="7" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="7" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" ht="31.5" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:7">
       <c r="A38" s="7" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:6">
       <c r="A40" s="7" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -7944,694 +9250,694 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="7" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" ht="47.25" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" ht="31.5" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" ht="47.25" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" ht="31.5" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" ht="47.25" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" ht="47.25" spans="1:6">
       <c r="A24" s="7" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="27" ht="31.5" spans="1:8">
       <c r="A27" s="7" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="7" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="30" ht="31.5" spans="1:4">
       <c r="A30" s="7" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" ht="31.5" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:4">
       <c r="A32" s="7" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="7" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="7" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="7" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="7" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:6">
       <c r="A42" s="7" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="46" ht="31.5" spans="1:6">
       <c r="A46" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>834</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="47" ht="31.5" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -8683,620 +9989,620 @@
       </c>
     </row>
     <row r="2" ht="30" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>839</v>
+      <c r="A2" s="4" t="s">
+        <v>843</v>
       </c>
       <c r="B2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E2" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="B3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C3" t="s">
+        <v>851</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="F3" t="s">
         <v>843</v>
-      </c>
-      <c r="F2" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="3" ht="30" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="B3" t="s">
-        <v>846</v>
-      </c>
-      <c r="C3" t="s">
-        <v>847</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>848</v>
-      </c>
-      <c r="F3" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B4" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C4" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E4" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="G4" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>854</v>
+      <c r="A5" s="4" t="s">
+        <v>858</v>
       </c>
       <c r="B5" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="G5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>859</v>
+      <c r="A6" s="4" t="s">
+        <v>863</v>
       </c>
       <c r="B6" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D6" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="E6" t="s">
-        <v>862</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
+        <v>868</v>
+      </c>
+      <c r="B7" t="s">
         <v>864</v>
       </c>
-      <c r="B7" t="s">
-        <v>860</v>
-      </c>
       <c r="D7" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E7" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="F7" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>867</v>
+      <c r="A8" s="4" t="s">
+        <v>871</v>
       </c>
       <c r="B8" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D8" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E8" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:8">
-      <c r="A9" s="3" t="s">
-        <v>871</v>
+      <c r="A9" s="4" t="s">
+        <v>875</v>
       </c>
       <c r="B9" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D9" t="s">
-        <v>873</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>874</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>875</v>
+        <v>877</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="10" ht="45" spans="1:8">
       <c r="A10" t="s">
-        <v>876</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>877</v>
+        <v>880</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>881</v>
       </c>
       <c r="C10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="H10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="11" ht="45" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>880</v>
+      <c r="A11" s="4" t="s">
+        <v>884</v>
       </c>
       <c r="B11" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D11" t="s">
-        <v>882</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:6">
       <c r="A12" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B12" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D12" t="s">
-        <v>886</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>887</v>
+        <v>890</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>891</v>
       </c>
       <c r="F12" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="B13" t="s">
+        <v>894</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="14" ht="45" spans="1:6">
+      <c r="A14" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="B14" t="s">
+        <v>898</v>
+      </c>
+      <c r="C14" t="s">
+        <v>899</v>
+      </c>
+      <c r="D14" t="s">
+        <v>900</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:6">
+      <c r="A15" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="B15" t="s">
+        <v>903</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="E15" t="s">
+        <v>905</v>
+      </c>
+      <c r="F15" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="13" ht="30" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="B13" t="s">
-        <v>890</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="14" ht="45" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="B14" t="s">
-        <v>894</v>
-      </c>
-      <c r="C14" t="s">
-        <v>895</v>
-      </c>
-      <c r="D14" t="s">
-        <v>896</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="B15" t="s">
-        <v>899</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="E15" t="s">
-        <v>901</v>
-      </c>
-      <c r="F15" t="s">
-        <v>884</v>
-      </c>
-    </row>
     <row r="16" ht="30" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>902</v>
+      <c r="A16" s="4" t="s">
+        <v>906</v>
       </c>
       <c r="B16" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="D16" t="s">
-        <v>904</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>905</v>
+        <v>908</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>909</v>
       </c>
       <c r="H16" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="B17" t="s">
+        <v>912</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="D17" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="17" ht="30" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="B17" t="s">
-        <v>908</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="D17" t="s">
-        <v>902</v>
-      </c>
       <c r="E17" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>911</v>
+      <c r="A18" s="4" t="s">
+        <v>915</v>
       </c>
       <c r="B18" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D18" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E18" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H18" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B19" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="F19" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>919</v>
+      <c r="A20" s="4" t="s">
+        <v>923</v>
       </c>
       <c r="B20" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D20" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E20" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>923</v>
+      <c r="A21" s="4" t="s">
+        <v>927</v>
       </c>
       <c r="B21" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="E21" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="F21" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B22" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C22" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D22" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>931</v>
+      <c r="A23" s="4" t="s">
+        <v>935</v>
       </c>
       <c r="B23" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C23" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="E23" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:6">
       <c r="A24" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B24" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E24" t="s">
-        <v>937</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>938</v>
+        <v>941</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B25" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="H25" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>942</v>
+      <c r="A26" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="B26" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D26" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E26" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>946</v>
+      <c r="A27" s="4" t="s">
+        <v>950</v>
       </c>
       <c r="B27" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C27" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D27" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E27" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="F27" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="G27" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="H27" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B28" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D28" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:5">
       <c r="A29" t="s">
-        <v>955</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>960</v>
       </c>
       <c r="C29" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D29" t="s">
-        <v>842</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>958</v>
+        <v>846</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>959</v>
+      <c r="A30" s="4" t="s">
+        <v>963</v>
       </c>
       <c r="B30" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C30" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D30" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="E30" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="31" ht="45" spans="1:8">
-      <c r="A31" s="3" t="s">
-        <v>964</v>
+      <c r="A31" s="4" t="s">
+        <v>968</v>
       </c>
       <c r="B31" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C31" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E31" t="s">
-        <v>968</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>973</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>971</v>
+      <c r="A32" s="4" t="s">
+        <v>975</v>
       </c>
       <c r="B32" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C32" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:5">
       <c r="A33" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B33" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C33" t="s">
-        <v>976</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>977</v>
+        <v>980</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="3" t="s">
-        <v>978</v>
+      <c r="A34" s="4" t="s">
+        <v>982</v>
       </c>
       <c r="B34" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D34" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="F34" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>980</v>
+      <c r="A35" s="4" t="s">
+        <v>984</v>
       </c>
       <c r="B35" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D35" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="F35" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:6">
-      <c r="A36" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>984</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>985</v>
+      <c r="A36" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>989</v>
       </c>
       <c r="E36" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F36" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:6">
       <c r="A37" t="s">
-        <v>987</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>988</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>993</v>
       </c>
       <c r="F37" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>990</v>
+      <c r="A38" s="4" t="s">
+        <v>994</v>
       </c>
       <c r="B38" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="E38" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="B39" t="s">
+        <v>998</v>
+      </c>
+      <c r="D39" t="s">
+        <v>999</v>
+      </c>
+      <c r="F39" t="s">
         <v>994</v>
       </c>
-      <c r="D39" t="s">
-        <v>995</v>
-      </c>
-      <c r="F39" t="s">
-        <v>990</v>
-      </c>
     </row>
     <row r="40" ht="60" spans="1:6">
-      <c r="A40" s="3" t="s">
-        <v>996</v>
+      <c r="A40" s="4" t="s">
+        <v>1000</v>
       </c>
       <c r="B40" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C40" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="E40" t="s">
-        <v>999</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="B41" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C41" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
   </sheetData>
@@ -9348,604 +10654,603 @@
       </c>
     </row>
     <row r="2" ht="45" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>1004</v>
+      <c r="A2" s="4" t="s">
+        <v>1008</v>
       </c>
       <c r="B2" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D2" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>1008</v>
+      <c r="A3" s="4" t="s">
+        <v>1012</v>
       </c>
       <c r="B3" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D3" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="E3" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="F3" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B4" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="D4" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="E4" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="F4" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1018</v>
+      <c r="A5" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1022</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="B6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="D6" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="E6" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="F6" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1025</v>
+      <c r="A7" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>1029</v>
       </c>
       <c r="D7" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1028</v>
+      <c r="A8" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1032</v>
       </c>
       <c r="C8" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>1030</v>
+      <c r="A9" s="4" t="s">
+        <v>1034</v>
       </c>
       <c r="B9" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E9" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>1033</v>
+      <c r="A10" s="4" t="s">
+        <v>1037</v>
       </c>
       <c r="B10" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C10" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D10" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>1038</v>
+      <c r="A11" s="4" t="s">
+        <v>1042</v>
       </c>
       <c r="B11" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:8">
       <c r="A12" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C12" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="E12" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="H12" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:8">
       <c r="A13" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B13" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C13" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="H13" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>1050</v>
+      <c r="A14" s="4" t="s">
+        <v>1054</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C14" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="H14" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3" t="s">
-        <v>1054</v>
+      <c r="A15" s="4" t="s">
+        <v>1058</v>
       </c>
       <c r="B15" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C15" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="D15" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="G15" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:5">
       <c r="A16" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B16" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C16" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>1063</v>
+      <c r="A17" s="4" t="s">
+        <v>1067</v>
       </c>
       <c r="B17" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="C17" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="E17" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="18" ht="75" spans="1:6">
       <c r="A18" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B18" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="D18" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>1071</v>
+      <c r="A19" s="4" t="s">
+        <v>1075</v>
       </c>
       <c r="B19" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C19" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="E19" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="F19" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B20" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="E20" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:8">
       <c r="A21" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B21" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C21" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="E21" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F21" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B22" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E22" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="B23" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D23" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B24" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C24" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E24" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B25" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D25" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E25" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:4">
       <c r="A26" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B26" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:6">
       <c r="A27" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B27" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E27" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B28" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C28" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F28" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="H28" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:6">
       <c r="A29" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="B29" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="E29" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="3" t="s">
-        <v>1111</v>
+      <c r="A30" s="4" t="s">
+        <v>1115</v>
       </c>
       <c r="B30" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D30" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F30" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:6">
       <c r="A31" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="F31" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:8">
-      <c r="A32" s="3" t="s">
-        <v>1117</v>
+      <c r="A32" s="4" t="s">
+        <v>1121</v>
       </c>
       <c r="B32" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D32" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="E32" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="3" t="s">
-        <v>1122</v>
+      <c r="A33" s="4" t="s">
+        <v>1126</v>
       </c>
       <c r="B33" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="E33" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="F33" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:6">
       <c r="A34" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B34" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>1127</v>
+        <v>1130</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>1131</v>
       </c>
       <c r="E34" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F35" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1125</v>
-      </c>
-    </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="3" t="s">
-        <v>1132</v>
+      <c r="A36" s="4" t="s">
+        <v>1136</v>
       </c>
       <c r="B36" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="D36" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="F36" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:6">
       <c r="A37" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="B37" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="E37" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="38" ht="30" spans="1:6">
       <c r="A38" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="B38" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="E38" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:8">
       <c r="A39" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B39" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E39" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:6">
       <c r="A40" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="C40" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D40"/>
+        <v>1153</v>
+      </c>
       <c r="F40" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B41" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C41" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="E41" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B42" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D42" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B43" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="E43" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="F43" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="G43" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -9998,494 +11303,494 @@
     </row>
     <row r="2" ht="30" spans="1:5">
       <c r="A2" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B2" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C2" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D2" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
       <c r="A3" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B3" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C3" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="E3" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:3">
       <c r="A4" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B5" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="B6" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D6" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="E6" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="F6" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B7" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="D7" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="G7" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="B8" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="D8" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="H8" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="B9" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="E9" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="F9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="B10" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C10" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D10" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="E10" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="F10" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="H10" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="B11" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="C11" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="E11" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="F11" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="B12" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="C12" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="D12" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E12" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="F12" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:8">
       <c r="A13" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="F13" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H13" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:6">
       <c r="A14" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B14" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="E14" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="B15" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C15" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="E15" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="F15" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="16" ht="30" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>1221</v>
+      <c r="A16" s="4" t="s">
+        <v>1225</v>
       </c>
       <c r="B16" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C16" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E16" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="H16" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>1225</v>
+      <c r="A17" s="4" t="s">
+        <v>1229</v>
       </c>
       <c r="B17" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="C17" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="18" ht="45" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>1229</v>
+      <c r="A18" s="4" t="s">
+        <v>1233</v>
       </c>
       <c r="B18" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="C18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="D18" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="H18" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>1235</v>
+      <c r="A19" s="4" t="s">
+        <v>1239</v>
       </c>
       <c r="B19" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C19" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="D19" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:5">
       <c r="A20" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C20" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="E20" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>1244</v>
+      <c r="A21" s="4" t="s">
+        <v>1248</v>
       </c>
       <c r="B21" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B22" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D22" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="F22" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:6">
       <c r="A23" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="E23" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="F23" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>1255</v>
+      <c r="A24" s="4" t="s">
+        <v>1259</v>
       </c>
       <c r="B24" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D24" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B25" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="F25" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:8">
-      <c r="A26" s="3" t="s">
-        <v>1261</v>
+      <c r="A26" s="4" t="s">
+        <v>1265</v>
       </c>
       <c r="B26" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C26" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>1265</v>
+      <c r="A27" s="4" t="s">
+        <v>1269</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="C27" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="H27" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="28" ht="45" spans="1:6">
       <c r="A28" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B28" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="B29" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="D29" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="F29" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="B30" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="F30" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:6">
       <c r="A31" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B31" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="F31" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:7">
       <c r="A32" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="B32" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="E32" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>1285</v>
+        <v>1288</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>1289</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="B33" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="E33" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="34" ht="60" spans="1:6">
       <c r="A34" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="B34" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D34" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -10538,287 +11843,287 @@
     </row>
     <row r="2" ht="30" spans="1:5">
       <c r="A2" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B2" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C2" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:6">
       <c r="A3" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="B3" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C3" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:6">
       <c r="A4" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B4" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="C4" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="30" spans="1:6">
       <c r="A5" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="B5" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="B6" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="C6" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="F6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="B7" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="F7" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:6">
       <c r="A8" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="B8" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D8" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B9" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C9" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D9" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:3">
       <c r="A10" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="C10" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:6">
       <c r="A11" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="B11" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C11" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="D11" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="B12" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="H12" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="B13" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="D13" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="F13" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:8">
       <c r="A14" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B14" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C14" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="15" ht="30" spans="1:6">
       <c r="A15" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="B15" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="E15" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="B16" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="C16" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B17" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="C17" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="E17" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="B18" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="D18" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="E18" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="F18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="B19" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="G19" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B20" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="E20" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="F20" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:8">
       <c r="A21" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="B21" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
     </row>
   </sheetData>

--- a/English/GRE/地基词/地基词.xlsx
+++ b/English/GRE/地基词/地基词.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12570" activeTab="11"/>
+    <workbookView windowWidth="27930" windowHeight="12570" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Links" sheetId="5" r:id="rId1"/>
@@ -19,13 +19,16 @@
     <sheet name="S09" sheetId="10" r:id="rId10"/>
     <sheet name="S10" sheetId="11" r:id="rId11"/>
     <sheet name="S11" sheetId="12" r:id="rId12"/>
+    <sheet name="S12" sheetId="13" r:id="rId13"/>
+    <sheet name="S13" sheetId="14" r:id="rId14"/>
+    <sheet name="S14" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="1824">
   <si>
     <t>GRE单词地基词全集精讲</t>
   </si>
@@ -4991,6 +4994,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>n.敏捷，</t>
     </r>
     <r>
@@ -5016,6 +5026,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>a.神秘的，</t>
     </r>
     <r>
@@ -5077,6 +5094,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>vt.欺骗，</t>
     </r>
     <r>
@@ -5108,6 +5132,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>n.浮标
 vt.</t>
     </r>
@@ -5205,6 +5236,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>a.</t>
     </r>
     <r>
@@ -5299,6 +5337,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>n.行人
 a.</t>
     </r>
@@ -5914,16 +5959,396 @@
     <t>tranquilize
 tranquilizer n.镇定剂</t>
   </si>
+  <si>
+    <t>abound</t>
+  </si>
+  <si>
+    <t>vi.大量存在</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">abound </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>with</t>
+    </r>
+  </si>
+  <si>
+    <t>abundant
+replete</t>
+  </si>
+  <si>
+    <t>coalesce</t>
+  </si>
+  <si>
+    <t>v.合并，结合</t>
+  </si>
+  <si>
+    <t>coalesce A,B and C into D</t>
+  </si>
+  <si>
+    <t>coalescent a.合并的
+coalition n.联合(coalition government)</t>
+  </si>
+  <si>
+    <t>decadence</t>
+  </si>
+  <si>
+    <t>n.颓废，堕落</t>
+  </si>
+  <si>
+    <t>decadent a.颓废的</t>
+  </si>
+  <si>
+    <t>corruption</t>
+  </si>
+  <si>
+    <t>degenerate</t>
+  </si>
+  <si>
+    <t>vt.堕落，恶化
+a.堕落的，颓废的</t>
+  </si>
+  <si>
+    <t>degenerate into sth</t>
+  </si>
+  <si>
+    <t>de = 向下</t>
+  </si>
+  <si>
+    <t>degeneracy n.
+degenerative a.</t>
+  </si>
+  <si>
+    <t>decadent</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n.折扣
+v.打折，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>认为...不重要/不对</t>
+    </r>
+  </si>
+  <si>
+    <t>dismiss
+disregard</t>
+  </si>
+  <si>
+    <t>discrete</t>
+  </si>
+  <si>
+    <t>a.离散的</t>
+  </si>
+  <si>
+    <t>discretion n.自由裁决权</t>
+  </si>
+  <si>
+    <t>discreet a.谨慎的</t>
+  </si>
+  <si>
+    <t>garrulous</t>
+  </si>
+  <si>
+    <t>a.饶舌的，话多的</t>
+  </si>
+  <si>
+    <t>gar = 嘎</t>
+  </si>
+  <si>
+    <t>chatty
+gabby
+loquacious</t>
+  </si>
+  <si>
+    <t>importunate</t>
+  </si>
+  <si>
+    <t>a.再三要求的</t>
+  </si>
+  <si>
+    <t>importunate man</t>
+  </si>
+  <si>
+    <t>importune v.强求</t>
+  </si>
+  <si>
+    <t>pester v.骚扰
+insistent
+persistent</t>
+  </si>
+  <si>
+    <t>intoxicate</t>
+  </si>
+  <si>
+    <t>vt.使醉酒，使入迷</t>
+  </si>
+  <si>
+    <t>toxic = 毒</t>
+  </si>
+  <si>
+    <t>mercurial</t>
+  </si>
+  <si>
+    <t>a.水银的，多变的，活泼的</t>
+  </si>
+  <si>
+    <t>mercury</t>
+  </si>
+  <si>
+    <t>capricious
+fickle</t>
+  </si>
+  <si>
+    <t>neutralize</t>
+  </si>
+  <si>
+    <t>vt.使中立，使无效</t>
+  </si>
+  <si>
+    <t>neutralize the fear</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>overt</t>
+  </si>
+  <si>
+    <t>a.明显的，公然的</t>
+  </si>
+  <si>
+    <t>overt support for sth</t>
+  </si>
+  <si>
+    <t>overtly</t>
+  </si>
+  <si>
+    <t>perfunctory</t>
+  </si>
+  <si>
+    <t>a.敷衍的，例行公事的</t>
+  </si>
+  <si>
+    <t>a perfunctory nod</t>
+  </si>
+  <si>
+    <t>per = 完全
+funct = function</t>
+  </si>
+  <si>
+    <t>proliferate</t>
+  </si>
+  <si>
+    <t>v.繁殖，激增</t>
+  </si>
+  <si>
+    <t>proli = 子孙
+fer = fertile = 生育</t>
+  </si>
+  <si>
+    <t>proliferation n.</t>
+  </si>
+  <si>
+    <t>surge
+ballon</t>
+  </si>
+  <si>
+    <t>repository</t>
+  </si>
+  <si>
+    <t>n.仓库，知识库</t>
+  </si>
+  <si>
+    <t>posit = pose = 放</t>
+  </si>
+  <si>
+    <t>repertoire n.指令集</t>
+  </si>
+  <si>
+    <t>serene</t>
+  </si>
+  <si>
+    <t>a.宁静的，平静的</t>
+  </si>
+  <si>
+    <t>scene = 场景</t>
+  </si>
+  <si>
+    <t>serenity n.宁静</t>
+  </si>
+  <si>
+    <t>stagnate</t>
+  </si>
+  <si>
+    <t>vi.停滞</t>
+  </si>
+  <si>
+    <t>profits have stagnated</t>
+  </si>
+  <si>
+    <t>stand</t>
+  </si>
+  <si>
+    <t>stagnation n.
+stagnant a.停滞的，萧条的</t>
+  </si>
+  <si>
+    <t>undermine</t>
+  </si>
+  <si>
+    <t>vt.破坏，逐渐削弱</t>
+  </si>
+  <si>
+    <t>undermine authority</t>
+  </si>
+  <si>
+    <t>mine = 挖矿</t>
+  </si>
+  <si>
+    <t>undergird (gird加固)</t>
+  </si>
+  <si>
+    <t>aberrant</t>
+  </si>
+  <si>
+    <t>a.异常的，反常的</t>
+  </si>
+  <si>
+    <t>aberrant behaviors</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>aberration n. (注意去掉n)
+aberrance n.
+errant a.行为不当的</t>
+  </si>
+  <si>
+    <t>abnormal
+deviant
+anomalous
+irregular
+atypical</t>
+  </si>
+  <si>
+    <t>authoritarian</t>
+  </si>
+  <si>
+    <t>a.独裁主义的</t>
+  </si>
+  <si>
+    <t>authority</t>
+  </si>
+  <si>
+    <t>authoritative a.权威的</t>
+  </si>
+  <si>
+    <t>blithe</t>
+  </si>
+  <si>
+    <t>a.不在意的，漫不经心的</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>cavalier
+insouciant</t>
+  </si>
+  <si>
+    <t>blur</t>
+  </si>
+  <si>
+    <t>vt.使模糊</t>
+  </si>
+  <si>
+    <t>blur the boundary between</t>
+  </si>
+  <si>
+    <t>blurred a.</t>
+  </si>
+  <si>
+    <t>catalyst</t>
+  </si>
+  <si>
+    <t>n.催化剂</t>
+  </si>
+  <si>
+    <t>a catalyst for change</t>
+  </si>
+  <si>
+    <t>cata = 向下
+lyst = lose</t>
+  </si>
+  <si>
+    <t>catalyse v.催化
+catalysis n.催化作用</t>
+  </si>
+  <si>
+    <t>charismatic</t>
+  </si>
+  <si>
+    <t>a.魅力超凡的</t>
+  </si>
+  <si>
+    <t>charisma n.魅力</t>
+  </si>
+  <si>
+    <t>conundrum</t>
+  </si>
+  <si>
+    <t>n.谜题</t>
+  </si>
+  <si>
+    <t>drum = 鼓</t>
+  </si>
+  <si>
+    <t>enigma</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -5949,6 +6374,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -5965,6 +6413,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -5973,32 +6428,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -6012,41 +6443,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -6062,14 +6473,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -6077,11 +6502,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6120,7 +6545,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6132,61 +6641,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6204,25 +6665,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6240,67 +6725,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6311,6 +6736,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -6339,30 +6773,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -6373,26 +6783,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6411,157 +6801,192 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6576,9 +7001,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6601,11 +7023,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="48" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6932,422 +7354,422 @@
   <dimension ref="A1:B52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="14.2333333333333" style="10" customWidth="1"/>
-    <col min="2" max="2" width="17.1166666666667" style="11" customWidth="1"/>
+    <col min="1" max="1" width="14.2333333333333" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.1166666666667" style="10" customWidth="1"/>
     <col min="3" max="6" width="47.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="11"/>
+    </row>
+    <row r="2" ht="15" spans="1:2">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>11</v>
       </c>
     </row>
@@ -7358,6 +7780,19 @@
   <hyperlinks>
     <hyperlink ref="A1:B1" r:id="rId1" display="GRE单词地基词全集精讲"/>
     <hyperlink ref="A13" location="S11!A1" display="Section11"/>
+    <hyperlink ref="A3" location="S01!A1" display="Section01"/>
+    <hyperlink ref="A4" location="S02!A1" display="Section02"/>
+    <hyperlink ref="A5" location="S03!A1" display="Section03"/>
+    <hyperlink ref="A14" location="S12!A1" display="Section12"/>
+    <hyperlink ref="A12" location="S10!A1" display="Section10"/>
+    <hyperlink ref="A11" location="S09!A1" display="Section09"/>
+    <hyperlink ref="A10" location="S08!A1" display="Section08"/>
+    <hyperlink ref="A9" location="S07!A1" display="Section07"/>
+    <hyperlink ref="A8" location="S06!A1" display="Section06"/>
+    <hyperlink ref="A7" location="S05!A1" display="Section05"/>
+    <hyperlink ref="A6" location="S04!A1" display="Section04"/>
+    <hyperlink ref="A15" location="S13!A1" display="Section13"/>
+    <hyperlink ref="A16" location="S14!A1" display="Section14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -7411,7 +7846,7 @@
       <c r="B2" t="s">
         <v>1324</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>1325</v>
       </c>
       <c r="D2" t="s">
@@ -7431,7 +7866,7 @@
       <c r="D3" t="s">
         <v>1330</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>1331</v>
       </c>
     </row>
@@ -7448,7 +7883,7 @@
       <c r="E4" t="s">
         <v>1334</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>1335</v>
       </c>
     </row>
@@ -7484,7 +7919,7 @@
       <c r="B7" t="s">
         <v>1343</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>1344</v>
       </c>
       <c r="F7" t="s">
@@ -7495,13 +7930,13 @@
       <c r="A8" t="s">
         <v>1346</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>1347</v>
       </c>
       <c r="D8" t="s">
         <v>1348</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>1349</v>
       </c>
       <c r="H8" t="s">
@@ -7535,7 +7970,7 @@
       <c r="D10" t="s">
         <v>1356</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -7577,10 +8012,10 @@
       <c r="A13" t="s">
         <v>1367</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>1368</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>1369</v>
       </c>
     </row>
@@ -7588,7 +8023,7 @@
       <c r="A14" t="s">
         <v>1370</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>1371</v>
       </c>
       <c r="D14" t="s">
@@ -7605,10 +8040,10 @@
       <c r="B15" t="s">
         <v>1375</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>1376</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -7659,7 +8094,7 @@
       <c r="D18" t="s">
         <v>1391</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>1392</v>
       </c>
     </row>
@@ -7673,7 +8108,7 @@
       <c r="C19" t="s">
         <v>1395</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>1396</v>
       </c>
       <c r="F19" t="s">
@@ -7687,7 +8122,7 @@
       <c r="B20" t="s">
         <v>1398</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -7712,7 +8147,7 @@
       <c r="A22" t="s">
         <v>1403</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>1404</v>
       </c>
       <c r="C22" t="s">
@@ -7743,7 +8178,7 @@
       <c r="C24" t="s">
         <v>1411</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>1412</v>
       </c>
     </row>
@@ -7777,7 +8212,7 @@
       <c r="E26" t="s">
         <v>1420</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -7788,10 +8223,10 @@
       <c r="B27" t="s">
         <v>1423</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>1424</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -7836,7 +8271,7 @@
       <c r="B30" t="s">
         <v>1435</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -7906,10 +8341,10 @@
       <c r="B35" t="s">
         <v>1452</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>1453</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>1454</v>
       </c>
     </row>
@@ -7951,7 +8386,7 @@
       <c r="D38" t="s">
         <v>1461</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -8013,7 +8448,7 @@
       <c r="C2" t="s">
         <v>1465</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>1466</v>
       </c>
     </row>
@@ -8030,7 +8465,7 @@
       <c r="D3" t="s">
         <v>1470</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>1471</v>
       </c>
     </row>
@@ -8047,7 +8482,7 @@
       <c r="E4" t="s">
         <v>1475</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>1476</v>
       </c>
     </row>
@@ -8061,7 +8496,7 @@
       <c r="E5" t="s">
         <v>1479</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>1480</v>
       </c>
     </row>
@@ -8072,13 +8507,13 @@
       <c r="B6" s="4" t="s">
         <v>1482</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>1483</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>1484</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>1485</v>
       </c>
     </row>
@@ -8086,10 +8521,10 @@
       <c r="A7" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>1487</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>1488</v>
       </c>
       <c r="D7" t="s">
@@ -8106,13 +8541,13 @@
       <c r="B8" t="s">
         <v>1492</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>1493</v>
       </c>
       <c r="F8" t="s">
         <v>469</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -8123,7 +8558,7 @@
       <c r="B9" t="s">
         <v>1496</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>1497</v>
       </c>
       <c r="G9" t="s">
@@ -8143,7 +8578,7 @@
       <c r="E10" t="s">
         <v>1501</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>1502</v>
       </c>
     </row>
@@ -8160,7 +8595,7 @@
       <c r="E11" t="s">
         <v>1506</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -8216,13 +8651,13 @@
       <c r="C15" t="s">
         <v>1520</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>1521</v>
       </c>
       <c r="E15" t="s">
         <v>1522</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="5" t="s">
         <v>1523</v>
       </c>
     </row>
@@ -8256,7 +8691,7 @@
       <c r="E17" t="s">
         <v>1532</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>1533</v>
       </c>
     </row>
@@ -8264,13 +8699,13 @@
       <c r="A18" t="s">
         <v>1534</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>1535</v>
       </c>
       <c r="C18" t="s">
         <v>1536</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>1537</v>
       </c>
     </row>
@@ -8284,7 +8719,7 @@
       <c r="F19" t="s">
         <v>176</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="5" t="s">
         <v>1540</v>
       </c>
     </row>
@@ -8301,7 +8736,7 @@
       <c r="D20" t="s">
         <v>1544</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -8326,10 +8761,10 @@
       <c r="C22" t="s">
         <v>1551</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="5" t="s">
         <v>1552</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="5" t="s">
         <v>1553</v>
       </c>
     </row>
@@ -8340,7 +8775,7 @@
       <c r="B23" t="s">
         <v>1555</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>1556</v>
       </c>
       <c r="D23" t="s">
@@ -8366,7 +8801,7 @@
       <c r="D24" t="s">
         <v>1563</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="5" t="s">
         <v>1564</v>
       </c>
     </row>
@@ -8429,7 +8864,7 @@
       <c r="D2" t="s">
         <v>1567</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>1568</v>
       </c>
     </row>
@@ -8443,7 +8878,7 @@
       <c r="E3" t="s">
         <v>1571</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
@@ -8460,7 +8895,7 @@
       <c r="D4" t="s">
         <v>1576</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>1577</v>
       </c>
     </row>
@@ -8496,10 +8931,10 @@
       <c r="B7" t="s">
         <v>1585</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>1586</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>1587</v>
       </c>
     </row>
@@ -8507,7 +8942,7 @@
       <c r="A8" s="2" t="s">
         <v>1588</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>1589</v>
       </c>
       <c r="E8" t="s">
@@ -8524,7 +8959,7 @@
       <c r="B9" t="s">
         <v>1592</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>1593</v>
       </c>
       <c r="E9" t="s">
@@ -8535,7 +8970,7 @@
       <c r="A10" t="s">
         <v>1595</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>1596</v>
       </c>
       <c r="C10" t="s">
@@ -8544,7 +8979,7 @@
       <c r="D10" t="s">
         <v>1598</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>1599</v>
       </c>
     </row>
@@ -8561,7 +8996,7 @@
       <c r="D11" t="s">
         <v>1603</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>1604</v>
       </c>
     </row>
@@ -8589,7 +9024,7 @@
       <c r="E13" t="s">
         <v>1611</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>1612</v>
       </c>
     </row>
@@ -8606,10 +9041,10 @@
       <c r="E14" t="s">
         <v>1615</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>1616</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>1617</v>
       </c>
     </row>
@@ -8648,7 +9083,7 @@
       <c r="B17" t="s">
         <v>1627</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>1628</v>
       </c>
       <c r="D17" t="s">
@@ -8657,7 +9092,7 @@
       <c r="E17" t="s">
         <v>1630</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>1631</v>
       </c>
       <c r="H17" t="s">
@@ -8674,7 +9109,7 @@
       <c r="D18" t="s">
         <v>1635</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>1636</v>
       </c>
     </row>
@@ -8685,7 +9120,7 @@
       <c r="B19" t="s">
         <v>1638</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>1639</v>
       </c>
       <c r="E19" t="s">
@@ -8727,13 +9162,13 @@
       <c r="B22" t="s">
         <v>1650</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>1651</v>
       </c>
       <c r="D22" t="s">
         <v>1652</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="5" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -8750,7 +9185,7 @@
       <c r="D23" t="s">
         <v>1657</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>1658</v>
       </c>
       <c r="F23" t="s">
@@ -8764,7 +9199,7 @@
       <c r="B24" t="s">
         <v>1661</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="5" t="s">
         <v>1662</v>
       </c>
       <c r="H24" t="s">
@@ -8798,7 +9233,7 @@
       <c r="D26" t="s">
         <v>1671</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="5" t="s">
         <v>1672</v>
       </c>
       <c r="G26" t="s">
@@ -8815,7 +9250,7 @@
       <c r="E27" t="s">
         <v>1675</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="5" t="s">
         <v>1676</v>
       </c>
     </row>
@@ -8835,7 +9270,7 @@
       <c r="E28" t="s">
         <v>1681</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>1682</v>
       </c>
       <c r="H28" t="s">
@@ -8849,10 +9284,10 @@
       <c r="B29" t="s">
         <v>1685</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="5" t="s">
         <v>1686</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="5" t="s">
         <v>1687</v>
       </c>
     </row>
@@ -8866,7 +9301,7 @@
       <c r="C30" t="s">
         <v>1690</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="5" t="s">
         <v>1691</v>
       </c>
       <c r="F30" t="s">
@@ -8911,7 +9346,7 @@
       <c r="E33" t="s">
         <v>1702</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="5" t="s">
         <v>1703</v>
       </c>
       <c r="G33" t="s">
@@ -8922,13 +9357,13 @@
       <c r="A34" s="2" t="s">
         <v>1705</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>1706</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>1707</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="5" t="s">
         <v>1708</v>
       </c>
     </row>
@@ -8959,8 +9394,533 @@
       <c r="D36" t="s">
         <v>1716</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>1717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="12.6833333333333" customWidth="1"/>
+    <col min="2" max="2" width="24.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.0333333333333" customWidth="1"/>
+    <col min="4" max="4" width="16.4416666666667" customWidth="1"/>
+    <col min="5" max="5" width="30.1" customWidth="1"/>
+    <col min="6" max="6" width="14.7083333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.2416666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:6">
+      <c r="A2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:6">
+      <c r="A6" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D7" t="s">
+        <v>857</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="8" ht="45" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="9" ht="45" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="16" ht="30" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1778</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:5">
+      <c r="A19" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="11.15" customWidth="1"/>
+    <col min="2" max="2" width="24.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.8666666666667" customWidth="1"/>
+    <col min="4" max="4" width="15.9583333333333" customWidth="1"/>
+    <col min="5" max="5" width="25.475" customWidth="1"/>
+    <col min="6" max="6" width="15.3833333333333" customWidth="1"/>
+    <col min="7" max="7" width="15.8666666666667" customWidth="1"/>
+    <col min="8" max="8" width="21.3416666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" ht="75" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -9013,7 +9973,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9024,10 +9984,10 @@
       </c>
     </row>
     <row r="3" ht="31.5" spans="1:5">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -9038,13 +9998,13 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:7">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -9052,7 +10012,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>72</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9069,7 +10029,7 @@
       <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -9080,7 +10040,7 @@
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9092,12 +10052,12 @@
       <c r="E7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -9120,7 +10080,7 @@
       <c r="C9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>92</v>
       </c>
     </row>
@@ -9134,10 +10094,10 @@
       <c r="C10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9148,13 +10108,13 @@
       <c r="B11" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>102</v>
       </c>
     </row>
@@ -9179,7 +10139,7 @@
       <c r="C13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -9196,7 +10156,7 @@
       <c r="C14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -9204,16 +10164,16 @@
       </c>
     </row>
     <row r="15" ht="47.25" spans="1:6">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>117</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>119</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -9221,7 +10181,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -9252,13 +10212,13 @@
       </c>
     </row>
     <row r="18" ht="31.5" spans="1:6">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>132</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -9266,13 +10226,13 @@
       </c>
     </row>
     <row r="19" ht="31.5" spans="1:7">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>136</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -9297,10 +10257,10 @@
       <c r="C21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -9328,15 +10288,15 @@
       <c r="B23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>154</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -9370,7 +10330,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>163</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -9384,7 +10344,7 @@
       </c>
     </row>
     <row r="27" ht="47.25" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>167</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -9393,15 +10353,15 @@
       <c r="C27" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="28" ht="31.5" spans="1:6">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -9410,7 +10370,7 @@
       <c r="D28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>175</v>
       </c>
     </row>
@@ -9421,7 +10381,7 @@
       <c r="B29" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>178</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -9429,7 +10389,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>180</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -9460,13 +10420,13 @@
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:6">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>188</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>190</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -9506,12 +10466,12 @@
       <c r="B34" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:4">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>201</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -9520,12 +10480,12 @@
       <c r="C35" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>205</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -9554,15 +10514,15 @@
       <c r="D37" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:6">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>216</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -9573,7 +10533,7 @@
       </c>
     </row>
     <row r="39" ht="31.5" spans="1:8">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>219</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -9585,7 +10545,7 @@
       <c r="D39" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="8" t="s">
         <v>223</v>
       </c>
       <c r="H39" s="1" t="s">
@@ -9602,10 +10562,10 @@
       <c r="E40" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="8" t="s">
         <v>229</v>
       </c>
     </row>
@@ -9619,7 +10579,7 @@
       <c r="E41" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="8" t="s">
         <v>233</v>
       </c>
     </row>
@@ -9644,13 +10604,13 @@
       </c>
     </row>
     <row r="43" ht="31.5" spans="1:6">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>240</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="8" t="s">
         <v>242</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -9664,10 +10624,10 @@
       <c r="B44" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="8" t="s">
         <v>247</v>
       </c>
       <c r="H44" s="1" t="s">
@@ -9675,13 +10635,13 @@
       </c>
     </row>
     <row r="45" ht="31.5" spans="1:6">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>249</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="8" t="s">
         <v>251</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -9692,7 +10652,7 @@
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>253</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -9704,7 +10664,7 @@
       <c r="D46" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="7" t="s">
         <v>257</v>
       </c>
     </row>
@@ -9715,7 +10675,7 @@
       <c r="B47" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="8" t="s">
         <v>260</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -9723,7 +10683,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>261</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -9734,7 +10694,7 @@
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>264</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -9751,10 +10711,10 @@
       </c>
     </row>
     <row r="50" ht="31.5" spans="1:8">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>270</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -9768,7 +10728,7 @@
       </c>
     </row>
     <row r="51" ht="47.25" spans="1:6">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>274</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -9777,12 +10737,12 @@
       <c r="C51" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="8" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>278</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -9791,7 +10751,7 @@
       <c r="C52" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="8" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9816,7 +10776,7 @@
       <c r="B54" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="8" t="s">
         <v>288</v>
       </c>
       <c r="H54" s="1" t="s">
@@ -9847,7 +10807,7 @@
       <c r="E56" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="8" t="s">
         <v>297</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -9855,13 +10815,13 @@
       </c>
     </row>
     <row r="57" ht="31.5" spans="1:7">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>299</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="8" t="s">
         <v>301</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -9872,13 +10832,13 @@
       <c r="A58" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="8" t="s">
         <v>306</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -9946,7 +10906,7 @@
       <c r="E2" t="s">
         <v>310</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>311</v>
       </c>
     </row>
@@ -9963,7 +10923,7 @@
       <c r="D3" t="s">
         <v>315</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>316</v>
       </c>
     </row>
@@ -9991,7 +10951,7 @@
       <c r="B5" t="s">
         <v>322</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>323</v>
       </c>
     </row>
@@ -9999,13 +10959,13 @@
       <c r="A6" t="s">
         <v>324</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>325</v>
       </c>
       <c r="C6" t="s">
         <v>326</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>327</v>
       </c>
     </row>
@@ -10013,7 +10973,7 @@
       <c r="A7" t="s">
         <v>328</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>329</v>
       </c>
       <c r="C7" t="s">
@@ -10033,7 +10993,7 @@
       <c r="B8" t="s">
         <v>334</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>335</v>
       </c>
     </row>
@@ -10109,7 +11069,7 @@
       <c r="C13" t="s">
         <v>354</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>355</v>
       </c>
     </row>
@@ -10117,13 +11077,13 @@
       <c r="A14" t="s">
         <v>356</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>357</v>
       </c>
       <c r="C14" t="s">
         <v>358</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>359</v>
       </c>
     </row>
@@ -10181,7 +11141,7 @@
       <c r="A19" t="s">
         <v>373</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>374</v>
       </c>
       <c r="C19" t="s">
@@ -10215,7 +11175,7 @@
       <c r="C21" t="s">
         <v>383</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>384</v>
       </c>
     </row>
@@ -10226,7 +11186,7 @@
       <c r="B22" t="s">
         <v>386</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>387</v>
       </c>
       <c r="F22" t="s">
@@ -10268,7 +11228,7 @@
       <c r="A25" t="s">
         <v>397</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>398</v>
       </c>
       <c r="C25" t="s">
@@ -10296,7 +11256,7 @@
       <c r="A27" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>406</v>
       </c>
       <c r="C27" t="s">
@@ -10316,10 +11276,10 @@
       <c r="A28" t="s">
         <v>411</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="5" t="s">
         <v>413</v>
       </c>
     </row>
@@ -10327,7 +11287,7 @@
       <c r="A29" t="s">
         <v>414</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>415</v>
       </c>
       <c r="E29" t="s">
@@ -10385,7 +11345,7 @@
       <c r="A34" t="s">
         <v>429</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>430</v>
       </c>
     </row>
@@ -10413,7 +11373,7 @@
       <c r="B36" t="s">
         <v>437</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>438</v>
       </c>
     </row>
@@ -10424,7 +11384,7 @@
       <c r="B37" t="s">
         <v>440</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>441</v>
       </c>
     </row>
@@ -10506,7 +11466,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>449</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10526,7 +11486,7 @@
       <c r="A3" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>455</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10534,10 +11494,10 @@
       </c>
     </row>
     <row r="4" ht="31.5" spans="1:8">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -10554,7 +11514,7 @@
       <c r="A5" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>463</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -10565,7 +11525,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>466</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -10576,7 +11536,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>469</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10593,7 +11553,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>474</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -10621,7 +11581,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>482</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -10669,12 +11629,12 @@
       <c r="C13" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>496</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10703,12 +11663,12 @@
       <c r="D15" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:8">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>506</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10720,18 +11680,18 @@
       <c r="F16" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="17" ht="47.25" spans="1:5">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>511</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>513</v>
       </c>
     </row>
@@ -10764,7 +11724,7 @@
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>522</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10773,7 +11733,7 @@
       <c r="D20" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>525</v>
       </c>
     </row>
@@ -10784,15 +11744,15 @@
       <c r="B21" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>530</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10806,7 +11766,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>534</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10817,30 +11777,30 @@
       </c>
     </row>
     <row r="24" ht="31.5" spans="1:6">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>539</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>542</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>544</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -10857,10 +11817,10 @@
       <c r="B26" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>550</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -10877,7 +11837,7 @@
       <c r="C27" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>555</v>
       </c>
     </row>
@@ -10893,18 +11853,18 @@
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:5">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>559</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>562</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -10958,7 +11918,7 @@
       <c r="D33" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>576</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -10986,13 +11946,13 @@
       </c>
     </row>
     <row r="35" ht="31.5" spans="1:6">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>583</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>585</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -11000,7 +11960,7 @@
       </c>
     </row>
     <row r="36" ht="31.5" spans="1:6">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>587</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -11012,7 +11972,7 @@
       <c r="D36" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="8" t="s">
         <v>591</v>
       </c>
     </row>
@@ -11031,7 +11991,7 @@
       </c>
     </row>
     <row r="38" ht="31.5" spans="1:7">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>596</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -11040,7 +12000,7 @@
       <c r="E38" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="8" t="s">
         <v>598</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -11065,13 +12025,13 @@
       </c>
     </row>
     <row r="40" ht="31.5" spans="1:6">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>605</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="8" t="s">
         <v>607</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -11128,7 +12088,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>609</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -11145,7 +12105,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>614</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11168,24 +12128,24 @@
       <c r="B4" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="5" ht="47.25" spans="1:7">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>621</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>623</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>625</v>
       </c>
     </row>
@@ -11201,21 +12161,21 @@
       </c>
     </row>
     <row r="7" ht="31.5" spans="1:5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>630</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>633</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -11247,12 +12207,12 @@
       <c r="C9" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="10" ht="47.25" spans="1:6">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>644</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -11261,7 +12221,7 @@
       <c r="E10" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>647</v>
       </c>
     </row>
@@ -11280,7 +12240,7 @@
       </c>
     </row>
     <row r="12" ht="31.5" spans="1:6">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>652</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -11292,12 +12252,12 @@
       <c r="E12" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>657</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -11339,7 +12299,7 @@
       </c>
     </row>
     <row r="16" ht="31.5" spans="1:6">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>669</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -11351,12 +12311,12 @@
       <c r="E16" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>674</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -11370,7 +12330,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>678</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -11384,7 +12344,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>681</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -11401,7 +12361,7 @@
       </c>
     </row>
     <row r="20" ht="31.5" spans="1:6">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>684</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -11413,7 +12373,7 @@
       <c r="E20" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>688</v>
       </c>
     </row>
@@ -11432,7 +12392,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>693</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -11446,13 +12406,13 @@
       </c>
     </row>
     <row r="23" ht="47.25" spans="1:7">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>697</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>699</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -11463,7 +12423,7 @@
       </c>
     </row>
     <row r="24" ht="47.25" spans="1:6">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>702</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -11472,7 +12432,7 @@
       <c r="D24" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>705</v>
       </c>
     </row>
@@ -11502,7 +12462,7 @@
       </c>
     </row>
     <row r="27" ht="31.5" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>712</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -11511,7 +12471,7 @@
       <c r="C27" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>715</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -11522,7 +12482,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>718</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -11542,7 +12502,7 @@
       </c>
     </row>
     <row r="29" ht="31.5" spans="1:6">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>722</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -11554,18 +12514,18 @@
       <c r="D29" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="30" ht="31.5" spans="1:4">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>728</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>729</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -11573,7 +12533,7 @@
       </c>
     </row>
     <row r="31" ht="31.5" spans="1:6">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>731</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -11582,29 +12542,29 @@
       <c r="D31" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="32" ht="31.5" spans="1:4">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>735</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="33" ht="31.5" spans="1:6">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>740</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -11615,7 +12575,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>742</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -11640,7 +12600,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>749</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -11651,7 +12611,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>751</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -11665,7 +12625,7 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>755</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -11682,7 +12642,7 @@
       <c r="A39" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>759</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -11693,7 +12653,7 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>761</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -11704,7 +12664,7 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>763</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -11721,7 +12681,7 @@
       </c>
     </row>
     <row r="42" ht="31" customHeight="1" spans="1:6">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>768</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -11733,7 +12693,7 @@
       <c r="D42" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="8" t="s">
         <v>772</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -11750,7 +12710,7 @@
       <c r="D43" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="8" t="s">
         <v>776</v>
       </c>
     </row>
@@ -11789,7 +12749,7 @@
       </c>
     </row>
     <row r="46" ht="31.5" spans="1:6">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>786</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -11798,7 +12758,7 @@
       <c r="C46" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>789</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -11809,13 +12769,13 @@
       <c r="A47" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>793</v>
       </c>
     </row>
@@ -11880,7 +12840,7 @@
       <c r="D2" t="s">
         <v>797</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>798</v>
       </c>
       <c r="F2" t="s">
@@ -11897,7 +12857,7 @@
       <c r="C3" t="s">
         <v>802</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>803</v>
       </c>
       <c r="F3" t="s">
@@ -11951,7 +12911,7 @@
       <c r="E6" t="s">
         <v>817</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>818</v>
       </c>
     </row>
@@ -11996,10 +12956,10 @@
       <c r="D9" t="s">
         <v>828</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>830</v>
       </c>
     </row>
@@ -12007,7 +12967,7 @@
       <c r="A10" t="s">
         <v>831</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>832</v>
       </c>
       <c r="C10" t="s">
@@ -12027,7 +12987,7 @@
       <c r="D11" t="s">
         <v>837</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>838</v>
       </c>
     </row>
@@ -12041,7 +13001,7 @@
       <c r="D12" t="s">
         <v>841</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>842</v>
       </c>
       <c r="F12" t="s">
@@ -12055,10 +13015,10 @@
       <c r="B13" t="s">
         <v>845</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>847</v>
       </c>
     </row>
@@ -12075,7 +13035,7 @@
       <c r="D14" t="s">
         <v>851</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>852</v>
       </c>
     </row>
@@ -12086,7 +13046,7 @@
       <c r="B15" t="s">
         <v>854</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>855</v>
       </c>
       <c r="E15" t="s">
@@ -12106,7 +13066,7 @@
       <c r="D16" t="s">
         <v>859</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>860</v>
       </c>
       <c r="H16" t="s">
@@ -12120,7 +13080,7 @@
       <c r="B17" t="s">
         <v>863</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>864</v>
       </c>
       <c r="D17" t="s">
@@ -12224,7 +13184,7 @@
       <c r="E24" t="s">
         <v>892</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>893</v>
       </c>
     </row>
@@ -12294,7 +13254,7 @@
       <c r="A29" t="s">
         <v>910</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>911</v>
       </c>
       <c r="C29" t="s">
@@ -12303,7 +13263,7 @@
       <c r="D29" t="s">
         <v>797</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>913</v>
       </c>
     </row>
@@ -12340,10 +13300,10 @@
       <c r="E31" t="s">
         <v>923</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="5" t="s">
         <v>925</v>
       </c>
     </row>
@@ -12368,7 +13328,7 @@
       <c r="C33" t="s">
         <v>931</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>932</v>
       </c>
     </row>
@@ -12404,10 +13364,10 @@
       <c r="A36" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>940</v>
       </c>
       <c r="E36" t="s">
@@ -12421,10 +13381,10 @@
       <c r="A37" t="s">
         <v>942</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>944</v>
       </c>
       <c r="F37" t="s">
@@ -12469,7 +13429,7 @@
       <c r="E40" t="s">
         <v>954</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>955</v>
       </c>
     </row>
@@ -12542,7 +13502,7 @@
       <c r="D2" t="s">
         <v>961</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>962</v>
       </c>
     </row>
@@ -12587,7 +13547,7 @@
       <c r="B5" s="4" t="s">
         <v>973</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>974</v>
       </c>
     </row>
@@ -12654,7 +13614,7 @@
       <c r="D10" t="s">
         <v>991</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>992</v>
       </c>
     </row>
@@ -12665,7 +13625,7 @@
       <c r="B11" t="s">
         <v>994</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>995</v>
       </c>
     </row>
@@ -12682,7 +13642,7 @@
       <c r="E12" t="s">
         <v>998</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>999</v>
       </c>
       <c r="H12" t="s">
@@ -12699,7 +13659,7 @@
       <c r="C13" t="s">
         <v>1002</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="H13" t="s">
@@ -12710,7 +13670,7 @@
       <c r="A14" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>1006</v>
       </c>
       <c r="C14" t="s">
@@ -12750,7 +13710,7 @@
       <c r="C16" t="s">
         <v>1016</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>1017</v>
       </c>
     </row>
@@ -12778,7 +13738,7 @@
       <c r="D18" t="s">
         <v>1024</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>1025</v>
       </c>
     </row>
@@ -12826,7 +13786,7 @@
       <c r="F21" t="s">
         <v>258</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -12887,7 +13847,7 @@
       <c r="B26" t="s">
         <v>1053</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>1054</v>
       </c>
     </row>
@@ -12901,7 +13861,7 @@
       <c r="E27" t="s">
         <v>1057</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>1058</v>
       </c>
     </row>
@@ -12932,7 +13892,7 @@
       <c r="E29" t="s">
         <v>1064</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>1065</v>
       </c>
     </row>
@@ -12954,7 +13914,7 @@
       <c r="A31" t="s">
         <v>1070</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>1071</v>
       </c>
       <c r="F31" t="s">
@@ -12974,7 +13934,7 @@
       <c r="E32" t="s">
         <v>1075</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="5" t="s">
         <v>1076</v>
       </c>
     </row>
@@ -13005,7 +13965,7 @@
       <c r="E34" t="s">
         <v>1083</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>1084</v>
       </c>
     </row>
@@ -13044,7 +14004,7 @@
       <c r="E37" t="s">
         <v>1092</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -13058,7 +14018,7 @@
       <c r="E38" t="s">
         <v>1096</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -13072,7 +14032,7 @@
       <c r="E39" t="s">
         <v>1100</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="5" t="s">
         <v>1101</v>
       </c>
     </row>
@@ -13080,7 +14040,7 @@
       <c r="A40" t="s">
         <v>1102</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>1103</v>
       </c>
       <c r="C40" t="s">
@@ -13193,7 +14153,7 @@
       <c r="D2" t="s">
         <v>1119</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -13210,7 +14170,7 @@
       <c r="E3" t="s">
         <v>1124</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -13218,7 +14178,7 @@
       <c r="A4" t="s">
         <v>1126</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>1127</v>
       </c>
       <c r="C4" t="s">
@@ -13356,10 +14316,10 @@
       <c r="A13" t="s">
         <v>1164</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>1165</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>1166</v>
       </c>
       <c r="F13" t="s">
@@ -13379,7 +14339,7 @@
       <c r="E14" t="s">
         <v>1170</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>1171</v>
       </c>
     </row>
@@ -13413,7 +14373,7 @@
       <c r="E16" t="s">
         <v>671</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>1179</v>
       </c>
       <c r="H16" t="s">
@@ -13430,7 +14390,7 @@
       <c r="C17" t="s">
         <v>1182</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>1183</v>
       </c>
     </row>
@@ -13447,7 +14407,7 @@
       <c r="D18" t="s">
         <v>1187</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>1188</v>
       </c>
       <c r="H18" t="s">
@@ -13467,7 +14427,7 @@
       <c r="D19" t="s">
         <v>1193</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>1194</v>
       </c>
     </row>
@@ -13475,7 +14435,7 @@
       <c r="A20" t="s">
         <v>1195</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>1196</v>
       </c>
       <c r="C20" t="s">
@@ -13514,7 +14474,7 @@
       <c r="A23" t="s">
         <v>1206</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>1207</v>
       </c>
       <c r="E23" t="s">
@@ -13534,7 +14494,7 @@
       <c r="D24" t="s">
         <v>1212</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -13559,7 +14519,7 @@
       <c r="C26" t="s">
         <v>1218</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="5" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -13567,13 +14527,13 @@
       <c r="A27" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>1221</v>
       </c>
       <c r="C27" t="s">
         <v>1222</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>1223</v>
       </c>
       <c r="H27" t="s">
@@ -13587,7 +14547,7 @@
       <c r="B28" t="s">
         <v>1226</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -13623,7 +14583,7 @@
       <c r="B31" t="s">
         <v>1234</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>1235</v>
       </c>
       <c r="F31" t="s">
@@ -13640,10 +14600,10 @@
       <c r="E32" t="s">
         <v>1238</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>1239</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>1240</v>
       </c>
     </row>
@@ -13668,7 +14628,7 @@
       <c r="D34" t="s">
         <v>1245</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>1246</v>
       </c>
     </row>
@@ -13730,10 +14690,10 @@
       <c r="C2" t="s">
         <v>1249</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1250</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -13747,10 +14707,10 @@
       <c r="C3" t="s">
         <v>1254</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>1256</v>
       </c>
     </row>
@@ -13764,11 +14724,11 @@
       <c r="C4" t="s">
         <v>1259</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
         <v>1260</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" ht="30" spans="1:6">
       <c r="A5" t="s">
@@ -13777,7 +14737,7 @@
       <c r="B5" t="s">
         <v>1262</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>1263</v>
       </c>
       <c r="F5" t="s">
@@ -13819,7 +14779,7 @@
       <c r="D8" t="s">
         <v>1272</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>1273</v>
       </c>
     </row>
@@ -13841,7 +14801,7 @@
       <c r="A10" t="s">
         <v>1278</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>1279</v>
       </c>
       <c r="C10" t="s">
@@ -13861,7 +14821,7 @@
       <c r="D11" t="s">
         <v>1284</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -13900,10 +14860,10 @@
       <c r="C14" t="s">
         <v>1295</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>1296</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>1297</v>
       </c>
     </row>
@@ -13917,7 +14877,7 @@
       <c r="E15" t="s">
         <v>1300</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>1301</v>
       </c>
     </row>
@@ -14001,7 +14961,7 @@
       <c r="B21" t="s">
         <v>1321</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>1322</v>
       </c>
     </row>
